--- a/data/processed/team/subway_merged_base.xlsx
+++ b/data/processed/team/subway_merged_base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N247"/>
+  <dimension ref="A1:L247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,16 +486,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>WL</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
@@ -539,12 +529,6 @@
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -587,12 +571,6 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -635,12 +613,6 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -683,13 +655,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -731,12 +697,6 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -779,12 +739,6 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -827,12 +781,6 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -875,12 +823,6 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -923,12 +865,6 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -971,12 +907,6 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1019,12 +949,6 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1067,12 +991,6 @@
         <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1115,12 +1033,6 @@
         <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1163,12 +1075,6 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1211,13 +1117,7 @@
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1259,12 +1159,6 @@
         <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1307,12 +1201,6 @@
         <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1355,12 +1243,6 @@
         <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1403,12 +1285,6 @@
         <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1451,12 +1327,6 @@
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1499,12 +1369,6 @@
         <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1547,12 +1411,6 @@
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1595,12 +1453,6 @@
         <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1643,12 +1495,6 @@
         <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1691,13 +1537,7 @@
         <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1739,12 +1579,6 @@
         <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1787,12 +1621,6 @@
         <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1835,12 +1663,6 @@
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1883,12 +1705,6 @@
         <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1931,13 +1747,7 @@
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1979,12 +1789,6 @@
         <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2027,12 +1831,6 @@
         <v>4</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2075,12 +1873,6 @@
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2123,12 +1915,6 @@
         <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2171,12 +1957,6 @@
         <v>4</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2219,12 +1999,6 @@
         <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2267,13 +2041,7 @@
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2315,12 +2083,6 @@
         <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2363,12 +2125,6 @@
         <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2411,12 +2167,6 @@
         <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2459,12 +2209,6 @@
         <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2507,12 +2251,6 @@
         <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2555,12 +2293,6 @@
         <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2603,12 +2335,6 @@
         <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2651,12 +2377,6 @@
         <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2699,12 +2419,6 @@
         <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2747,12 +2461,6 @@
         <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2795,12 +2503,6 @@
         <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2843,12 +2545,6 @@
         <v>4</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2891,12 +2587,6 @@
         <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2939,12 +2629,6 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2987,12 +2671,6 @@
         <v>4</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3035,12 +2713,6 @@
         <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3083,12 +2755,6 @@
         <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3131,12 +2797,6 @@
         <v>4</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3179,12 +2839,6 @@
         <v>5</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3227,12 +2881,6 @@
         <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3275,12 +2923,6 @@
         <v>4</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3323,12 +2965,6 @@
         <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3371,12 +3007,6 @@
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3419,12 +3049,6 @@
         <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3467,12 +3091,6 @@
         <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3515,12 +3133,6 @@
         <v>3</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3563,12 +3175,6 @@
         <v>3</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3611,12 +3217,6 @@
         <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3659,12 +3259,6 @@
         <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3707,12 +3301,6 @@
         <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3755,12 +3343,6 @@
         <v>3</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3803,13 +3385,7 @@
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -3851,12 +3427,6 @@
         <v>4</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3899,12 +3469,6 @@
         <v>3</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3947,12 +3511,6 @@
         <v>3</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3995,12 +3553,6 @@
         <v>4</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4043,12 +3595,6 @@
         <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4091,12 +3637,6 @@
         <v>5</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4139,12 +3679,6 @@
         <v>8</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4187,12 +3721,6 @@
         <v>4</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4235,12 +3763,6 @@
         <v>3</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4283,12 +3805,6 @@
         <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4331,12 +3847,6 @@
         <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4379,12 +3889,6 @@
         <v>3</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4427,12 +3931,6 @@
         <v>8</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4475,12 +3973,6 @@
         <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4523,12 +4015,6 @@
         <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4571,12 +4057,6 @@
         <v>3</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4619,12 +4099,6 @@
         <v>4</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4667,13 +4141,7 @@
         <v>4</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -4715,12 +4183,6 @@
         <v>2</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4763,12 +4225,6 @@
         <v>3</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4811,12 +4267,6 @@
         <v>3</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4859,13 +4309,7 @@
         <v>4</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
-      </c>
-      <c r="N92" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -4907,13 +4351,7 @@
         <v>4</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -4955,12 +4393,6 @@
         <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5003,12 +4435,6 @@
         <v>6</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5051,12 +4477,6 @@
         <v>3</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5099,12 +4519,6 @@
         <v>3</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5147,12 +4561,6 @@
         <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5195,12 +4603,6 @@
         <v>3</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5243,12 +4645,6 @@
         <v>3</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5291,12 +4687,6 @@
         <v>3</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5339,12 +4729,6 @@
         <v>4</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5387,12 +4771,6 @@
         <v>3</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5435,12 +4813,6 @@
         <v>6</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5483,12 +4855,6 @@
         <v>3</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5531,12 +4897,6 @@
         <v>4</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5579,12 +4939,6 @@
         <v>3</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5627,12 +4981,6 @@
         <v>6</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5675,12 +5023,6 @@
         <v>2</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5723,12 +5065,6 @@
         <v>3</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5771,12 +5107,6 @@
         <v>5</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5819,12 +5149,6 @@
         <v>3</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5867,12 +5191,6 @@
         <v>3</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5915,12 +5233,6 @@
         <v>3</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5963,12 +5275,6 @@
         <v>3</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6011,12 +5317,6 @@
         <v>3</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6059,12 +5359,6 @@
         <v>3</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6107,13 +5401,7 @@
         <v>3</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>1</v>
-      </c>
-      <c r="N118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
@@ -6155,12 +5443,6 @@
         <v>3</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6203,12 +5485,6 @@
         <v>2</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6251,12 +5527,6 @@
         <v>4</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6299,12 +5569,6 @@
         <v>3</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6347,12 +5611,6 @@
         <v>2</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6395,12 +5653,6 @@
         <v>3</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6443,12 +5695,6 @@
         <v>3</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6491,12 +5737,6 @@
         <v>2</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6539,12 +5779,6 @@
         <v>3</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6587,13 +5821,7 @@
         <v>3</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>2</v>
-      </c>
-      <c r="N128" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
@@ -6635,12 +5863,6 @@
         <v>4</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6683,12 +5905,6 @@
         <v>2</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6731,12 +5947,6 @@
         <v>5</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6779,12 +5989,6 @@
         <v>1</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6827,12 +6031,6 @@
         <v>4</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6875,12 +6073,6 @@
         <v>3</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6923,12 +6115,6 @@
         <v>3</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6971,12 +6157,6 @@
         <v>3</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7019,13 +6199,7 @@
         <v>4</v>
       </c>
       <c r="L137" t="n">
-        <v>2</v>
-      </c>
-      <c r="M137" t="n">
-        <v>2</v>
-      </c>
-      <c r="N137" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138">
@@ -7067,12 +6241,6 @@
         <v>3</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7115,12 +6283,6 @@
         <v>2</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7163,13 +6325,7 @@
         <v>3</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141">
@@ -7211,12 +6367,6 @@
         <v>3</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7259,12 +6409,6 @@
         <v>2</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7307,12 +6451,6 @@
         <v>2</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7355,12 +6493,6 @@
         <v>3</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7403,12 +6535,6 @@
         <v>3</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7451,12 +6577,6 @@
         <v>3</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7499,12 +6619,6 @@
         <v>5</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7547,12 +6661,6 @@
         <v>2</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7595,13 +6703,7 @@
         <v>4</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>3</v>
-      </c>
-      <c r="N149" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150">
@@ -7643,12 +6745,6 @@
         <v>2</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7691,12 +6787,6 @@
         <v>3</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7739,13 +6829,7 @@
         <v>3</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
-        <v>6</v>
-      </c>
-      <c r="N152" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
@@ -7787,12 +6871,6 @@
         <v>4</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" t="n">
         <v>18</v>
       </c>
     </row>
@@ -7835,12 +6913,6 @@
         <v>5</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7883,12 +6955,6 @@
         <v>3</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" t="n">
         <v>22</v>
       </c>
     </row>
@@ -7931,12 +6997,6 @@
         <v>5</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7979,13 +7039,7 @@
         <v>4</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>1</v>
-      </c>
-      <c r="N157" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158">
@@ -8027,12 +7081,6 @@
         <v>3</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8075,12 +7123,6 @@
         <v>3</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0</v>
-      </c>
-      <c r="N159" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8123,13 +7165,7 @@
         <v>4</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>1</v>
-      </c>
-      <c r="N160" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161">
@@ -8171,12 +7207,6 @@
         <v>2</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8219,12 +7249,6 @@
         <v>3</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="n">
         <v>13</v>
       </c>
     </row>
@@ -8267,12 +7291,6 @@
         <v>3</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8315,12 +7333,6 @@
         <v>5</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" t="n">
         <v>11</v>
       </c>
     </row>
@@ -8363,12 +7375,6 @@
         <v>3</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0</v>
-      </c>
-      <c r="N165" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8411,12 +7417,6 @@
         <v>4</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
-      </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="n">
         <v>16</v>
       </c>
     </row>
@@ -8459,12 +7459,6 @@
         <v>4</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" t="n">
         <v>16</v>
       </c>
     </row>
@@ -8507,12 +7501,6 @@
         <v>4</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8555,12 +7543,6 @@
         <v>4</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" t="n">
-        <v>0</v>
-      </c>
-      <c r="N169" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8603,13 +7585,7 @@
         <v>3</v>
       </c>
       <c r="L170" t="n">
-        <v>2</v>
-      </c>
-      <c r="M170" t="n">
-        <v>1</v>
-      </c>
-      <c r="N170" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171">
@@ -8651,12 +7627,6 @@
         <v>3</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" t="n">
-        <v>0</v>
-      </c>
-      <c r="N171" t="n">
         <v>11</v>
       </c>
     </row>
@@ -8699,13 +7669,7 @@
         <v>3</v>
       </c>
       <c r="L172" t="n">
-        <v>2</v>
-      </c>
-      <c r="M172" t="n">
-        <v>2</v>
-      </c>
-      <c r="N172" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173">
@@ -8747,12 +7711,6 @@
         <v>3</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" t="n">
-        <v>0</v>
-      </c>
-      <c r="N173" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8795,12 +7753,6 @@
         <v>3</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" t="n">
-        <v>0</v>
-      </c>
-      <c r="N174" t="n">
         <v>17</v>
       </c>
     </row>
@@ -8843,12 +7795,6 @@
         <v>2</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" t="n">
-        <v>0</v>
-      </c>
-      <c r="N175" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8891,12 +7837,6 @@
         <v>3</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
-      </c>
-      <c r="M176" t="n">
-        <v>0</v>
-      </c>
-      <c r="N176" t="n">
         <v>13</v>
       </c>
     </row>
@@ -8939,12 +7879,6 @@
         <v>3</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8987,12 +7921,6 @@
         <v>3</v>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0</v>
-      </c>
-      <c r="N178" t="n">
         <v>9</v>
       </c>
     </row>
@@ -9035,12 +7963,6 @@
         <v>4</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
-      </c>
-      <c r="N179" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9083,12 +8005,6 @@
         <v>4</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
         <v>20</v>
       </c>
     </row>
@@ -9131,12 +8047,6 @@
         <v>3</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
         <v>9</v>
       </c>
     </row>
@@ -9179,12 +8089,6 @@
         <v>3</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
         <v>13</v>
       </c>
     </row>
@@ -9227,12 +8131,6 @@
         <v>3</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
         <v>8</v>
       </c>
     </row>
@@ -9275,12 +8173,6 @@
         <v>4</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
-      </c>
-      <c r="M184" t="n">
-        <v>0</v>
-      </c>
-      <c r="N184" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9323,12 +8215,6 @@
         <v>4</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
-      </c>
-      <c r="M185" t="n">
-        <v>0</v>
-      </c>
-      <c r="N185" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9371,12 +8257,6 @@
         <v>3</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M186" t="n">
-        <v>0</v>
-      </c>
-      <c r="N186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9419,12 +8299,6 @@
         <v>4</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" t="n">
-        <v>0</v>
-      </c>
-      <c r="N187" t="n">
         <v>8</v>
       </c>
     </row>
@@ -9467,12 +8341,6 @@
         <v>3</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" t="n">
         <v>7</v>
       </c>
     </row>
@@ -9515,12 +8383,6 @@
         <v>4</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
-      </c>
-      <c r="M189" t="n">
-        <v>0</v>
-      </c>
-      <c r="N189" t="n">
         <v>16</v>
       </c>
     </row>
@@ -9563,12 +8425,6 @@
         <v>4</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" t="n">
-        <v>0</v>
-      </c>
-      <c r="N190" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9611,12 +8467,6 @@
         <v>4</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
-      </c>
-      <c r="M191" t="n">
-        <v>0</v>
-      </c>
-      <c r="N191" t="n">
         <v>30</v>
       </c>
     </row>
@@ -9659,12 +8509,6 @@
         <v>2</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9707,12 +8551,6 @@
         <v>3</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="n">
         <v>21</v>
       </c>
     </row>
@@ -9755,12 +8593,6 @@
         <v>3</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" t="n">
         <v>15</v>
       </c>
     </row>
@@ -9803,12 +8635,6 @@
         <v>4</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" t="n">
-        <v>0</v>
-      </c>
-      <c r="N195" t="n">
         <v>20</v>
       </c>
     </row>
@@ -9851,12 +8677,6 @@
         <v>6</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" t="n">
-        <v>0</v>
-      </c>
-      <c r="N196" t="n">
         <v>22</v>
       </c>
     </row>
@@ -9899,12 +8719,6 @@
         <v>8</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="n">
         <v>34</v>
       </c>
     </row>
@@ -9947,12 +8761,6 @@
         <v>3</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
         <v>35</v>
       </c>
     </row>
@@ -9995,12 +8803,6 @@
         <v>4</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
         <v>18</v>
       </c>
     </row>
@@ -10043,12 +8845,6 @@
         <v>4</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
-      </c>
-      <c r="M200" t="n">
-        <v>0</v>
-      </c>
-      <c r="N200" t="n">
         <v>22</v>
       </c>
     </row>
@@ -10091,12 +8887,6 @@
         <v>5</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="n">
         <v>17</v>
       </c>
     </row>
@@ -10139,12 +8929,6 @@
         <v>4</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
-      </c>
-      <c r="M202" t="n">
-        <v>0</v>
-      </c>
-      <c r="N202" t="n">
         <v>17</v>
       </c>
     </row>
@@ -10187,12 +8971,6 @@
         <v>4</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
-      </c>
-      <c r="M203" t="n">
-        <v>0</v>
-      </c>
-      <c r="N203" t="n">
         <v>26</v>
       </c>
     </row>
@@ -10235,12 +9013,6 @@
         <v>4</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
-      </c>
-      <c r="M204" t="n">
-        <v>0</v>
-      </c>
-      <c r="N204" t="n">
         <v>14</v>
       </c>
     </row>
@@ -10283,12 +9055,6 @@
         <v>4</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
-      </c>
-      <c r="M205" t="n">
-        <v>0</v>
-      </c>
-      <c r="N205" t="n">
         <v>18</v>
       </c>
     </row>
@@ -10331,12 +9097,6 @@
         <v>4</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M206" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" t="n">
         <v>26</v>
       </c>
     </row>
@@ -10379,12 +9139,6 @@
         <v>4</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
         <v>31</v>
       </c>
     </row>
@@ -10427,12 +9181,6 @@
         <v>4</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
         <v>16</v>
       </c>
     </row>
@@ -10475,12 +9223,6 @@
         <v>3</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
         <v>21</v>
       </c>
     </row>
@@ -10523,12 +9265,6 @@
         <v>4</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
         <v>20</v>
       </c>
     </row>
@@ -10571,12 +9307,6 @@
         <v>9</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
         <v>43</v>
       </c>
     </row>
@@ -10619,13 +9349,7 @@
         <v>4</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>1</v>
-      </c>
-      <c r="N212" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="213">
@@ -10667,13 +9391,7 @@
         <v>10</v>
       </c>
       <c r="L213" t="n">
-        <v>4</v>
-      </c>
-      <c r="M213" t="n">
-        <v>4</v>
-      </c>
-      <c r="N213" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="214">
@@ -10715,12 +9433,6 @@
         <v>7</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" t="n">
         <v>24</v>
       </c>
     </row>
@@ -10763,13 +9475,7 @@
         <v>5</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
-      </c>
-      <c r="M215" t="n">
-        <v>1</v>
-      </c>
-      <c r="N215" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216">
@@ -10811,12 +9517,6 @@
         <v>4</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" t="n">
         <v>18</v>
       </c>
     </row>
@@ -10859,12 +9559,6 @@
         <v>5</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" t="n">
         <v>31</v>
       </c>
     </row>
@@ -10907,12 +9601,6 @@
         <v>7</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" t="n">
         <v>32</v>
       </c>
     </row>
@@ -10955,12 +9643,6 @@
         <v>9</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" t="n">
         <v>44</v>
       </c>
     </row>
@@ -11003,13 +9685,7 @@
         <v>7</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
-      </c>
-      <c r="M220" t="n">
-        <v>1</v>
-      </c>
-      <c r="N220" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="221">
@@ -11051,12 +9727,6 @@
         <v>5</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
         <v>16</v>
       </c>
     </row>
@@ -11099,12 +9769,6 @@
         <v>7</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
         <v>20</v>
       </c>
     </row>
@@ -11147,13 +9811,7 @@
         <v>9</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
-      </c>
-      <c r="M223" t="n">
-        <v>2</v>
-      </c>
-      <c r="N223" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="224">
@@ -11195,13 +9853,7 @@
         <v>9</v>
       </c>
       <c r="L224" t="n">
-        <v>2</v>
-      </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -11243,13 +9895,7 @@
         <v>7</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
-      </c>
-      <c r="M225" t="n">
-        <v>2</v>
-      </c>
-      <c r="N225" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226">
@@ -11291,12 +9937,6 @@
         <v>5</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
-      </c>
-      <c r="M226" t="n">
-        <v>0</v>
-      </c>
-      <c r="N226" t="n">
         <v>26</v>
       </c>
     </row>
@@ -11339,13 +9979,7 @@
         <v>10</v>
       </c>
       <c r="L227" t="n">
-        <v>8</v>
-      </c>
-      <c r="M227" t="n">
-        <v>0</v>
-      </c>
-      <c r="N227" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="228">
@@ -11387,12 +10021,6 @@
         <v>6</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M228" t="n">
-        <v>0</v>
-      </c>
-      <c r="N228" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11435,12 +10063,6 @@
         <v>5</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
-      </c>
-      <c r="M229" t="n">
-        <v>0</v>
-      </c>
-      <c r="N229" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11483,13 +10105,7 @@
         <v>4</v>
       </c>
       <c r="L230" t="n">
-        <v>2</v>
-      </c>
-      <c r="M230" t="n">
-        <v>5</v>
-      </c>
-      <c r="N230" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
@@ -11531,13 +10147,7 @@
         <v>8</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
-      </c>
-      <c r="M231" t="n">
-        <v>4</v>
-      </c>
-      <c r="N231" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -11579,12 +10189,6 @@
         <v>6</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
-      </c>
-      <c r="M232" t="n">
-        <v>0</v>
-      </c>
-      <c r="N232" t="n">
         <v>19</v>
       </c>
     </row>
@@ -11627,12 +10231,6 @@
         <v>4</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
-      </c>
-      <c r="M233" t="n">
-        <v>0</v>
-      </c>
-      <c r="N233" t="n">
         <v>20</v>
       </c>
     </row>
@@ -11675,12 +10273,6 @@
         <v>3</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
-      </c>
-      <c r="M234" t="n">
-        <v>0</v>
-      </c>
-      <c r="N234" t="n">
         <v>13</v>
       </c>
     </row>
@@ -11723,13 +10315,7 @@
         <v>8</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
-      </c>
-      <c r="M235" t="n">
-        <v>1</v>
-      </c>
-      <c r="N235" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="236">
@@ -11771,12 +10357,6 @@
         <v>8</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
-      </c>
-      <c r="M236" t="n">
-        <v>0</v>
-      </c>
-      <c r="N236" t="n">
         <v>30</v>
       </c>
     </row>
@@ -11819,12 +10399,6 @@
         <v>5</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
-      </c>
-      <c r="M237" t="n">
-        <v>0</v>
-      </c>
-      <c r="N237" t="n">
         <v>21</v>
       </c>
     </row>
@@ -11867,12 +10441,6 @@
         <v>4</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
-      </c>
-      <c r="M238" t="n">
-        <v>0</v>
-      </c>
-      <c r="N238" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11915,12 +10483,6 @@
         <v>4</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
-      </c>
-      <c r="M239" t="n">
-        <v>0</v>
-      </c>
-      <c r="N239" t="n">
         <v>17</v>
       </c>
     </row>
@@ -11963,13 +10525,7 @@
         <v>7</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>1</v>
-      </c>
-      <c r="N240" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="241">
@@ -12011,13 +10567,7 @@
         <v>7</v>
       </c>
       <c r="L241" t="n">
-        <v>2</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242">
@@ -12059,12 +10609,6 @@
         <v>6</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
         <v>22</v>
       </c>
     </row>
@@ -12107,12 +10651,6 @@
         <v>5</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="n">
         <v>15</v>
       </c>
     </row>
@@ -12155,12 +10693,6 @@
         <v>4</v>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
-      </c>
-      <c r="M244" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" t="n">
         <v>27</v>
       </c>
     </row>
@@ -12203,12 +10735,6 @@
         <v>4</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
-      </c>
-      <c r="M245" t="n">
-        <v>0</v>
-      </c>
-      <c r="N245" t="n">
         <v>12</v>
       </c>
     </row>
@@ -12251,12 +10777,6 @@
         <v>6</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
-      </c>
-      <c r="M246" t="n">
-        <v>0</v>
-      </c>
-      <c r="N246" t="n">
         <v>30</v>
       </c>
     </row>
@@ -12299,13 +10819,7 @@
         <v>7</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
-      </c>
-      <c r="M247" t="n">
-        <v>1</v>
-      </c>
-      <c r="N247" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/team/subway_merged_base.xlsx
+++ b/data/processed/team/subway_merged_base.xlsx
@@ -9985,7 +9985,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>서울역</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">

--- a/data/processed/team/subway_merged_base.xlsx
+++ b/data/processed/team/subway_merged_base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L247"/>
+  <dimension ref="A1:L246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,7 +3685,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>총신대입구</t>
+          <t>한성대입구</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3694,40 +3694,40 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>564012</v>
+        <v>422016</v>
       </c>
       <c r="D78" t="n">
-        <v>159811</v>
+        <v>76857</v>
       </c>
       <c r="E78" t="n">
-        <v>610462</v>
+        <v>409204</v>
       </c>
       <c r="F78" t="n">
-        <v>167328</v>
+        <v>75462</v>
       </c>
       <c r="G78" t="n">
-        <v>1174474</v>
+        <v>831220</v>
       </c>
       <c r="H78" t="n">
-        <v>327139</v>
+        <v>152319</v>
       </c>
       <c r="I78" t="n">
-        <v>27.85</v>
+        <v>18.32</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한성대입구</t>
+          <t>혜화</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3736,40 +3736,40 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>422016</v>
+        <v>1093159</v>
       </c>
       <c r="D79" t="n">
-        <v>76857</v>
+        <v>134964</v>
       </c>
       <c r="E79" t="n">
-        <v>409204</v>
+        <v>1101259</v>
       </c>
       <c r="F79" t="n">
-        <v>75462</v>
+        <v>132704</v>
       </c>
       <c r="G79" t="n">
-        <v>831220</v>
+        <v>2194418</v>
       </c>
       <c r="H79" t="n">
-        <v>152319</v>
+        <v>267668</v>
       </c>
       <c r="I79" t="n">
-        <v>18.32</v>
+        <v>12.2</v>
       </c>
       <c r="J79" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" t="n">
         <v>2</v>
       </c>
-      <c r="K79" t="n">
-        <v>3</v>
-      </c>
       <c r="L79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>혜화</t>
+          <t>회현</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3778,82 +3778,82 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1093159</v>
+        <v>790571</v>
       </c>
       <c r="D80" t="n">
-        <v>134964</v>
+        <v>203810</v>
       </c>
       <c r="E80" t="n">
-        <v>1101259</v>
+        <v>821961</v>
       </c>
       <c r="F80" t="n">
-        <v>132704</v>
+        <v>203499</v>
       </c>
       <c r="G80" t="n">
-        <v>2194418</v>
+        <v>1612532</v>
       </c>
       <c r="H80" t="n">
-        <v>267668</v>
+        <v>407309</v>
       </c>
       <c r="I80" t="n">
-        <v>12.2</v>
+        <v>25.26</v>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K80" t="n">
         <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>회현</t>
+          <t>강동</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>790571</v>
+        <v>533364</v>
       </c>
       <c r="D81" t="n">
-        <v>203810</v>
+        <v>114472</v>
       </c>
       <c r="E81" t="n">
-        <v>821961</v>
+        <v>516922</v>
       </c>
       <c r="F81" t="n">
-        <v>203499</v>
+        <v>111842</v>
       </c>
       <c r="G81" t="n">
-        <v>1612532</v>
+        <v>1050286</v>
       </c>
       <c r="H81" t="n">
-        <v>407309</v>
+        <v>226314</v>
       </c>
       <c r="I81" t="n">
-        <v>25.26</v>
+        <v>21.55</v>
       </c>
       <c r="J81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강동</t>
+          <t>강일</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3862,40 +3862,40 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>533364</v>
+        <v>170232</v>
       </c>
       <c r="D82" t="n">
-        <v>114472</v>
+        <v>45780</v>
       </c>
       <c r="E82" t="n">
-        <v>516922</v>
+        <v>156100</v>
       </c>
       <c r="F82" t="n">
-        <v>111842</v>
+        <v>43927</v>
       </c>
       <c r="G82" t="n">
-        <v>1050286</v>
+        <v>326332</v>
       </c>
       <c r="H82" t="n">
-        <v>226314</v>
+        <v>89707</v>
       </c>
       <c r="I82" t="n">
-        <v>21.55</v>
+        <v>27.49</v>
       </c>
       <c r="J82" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L82" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강일</t>
+          <t>개롱</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3904,40 +3904,40 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>170232</v>
+        <v>190212</v>
       </c>
       <c r="D83" t="n">
-        <v>45780</v>
+        <v>53640</v>
       </c>
       <c r="E83" t="n">
-        <v>156100</v>
+        <v>196781</v>
       </c>
       <c r="F83" t="n">
-        <v>43927</v>
+        <v>55256</v>
       </c>
       <c r="G83" t="n">
-        <v>326332</v>
+        <v>386993</v>
       </c>
       <c r="H83" t="n">
-        <v>89707</v>
+        <v>108896</v>
       </c>
       <c r="I83" t="n">
-        <v>27.49</v>
+        <v>28.14</v>
       </c>
       <c r="J83" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L83" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>개롱</t>
+          <t>개화산</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>190212</v>
+        <v>172565</v>
       </c>
       <c r="D84" t="n">
-        <v>53640</v>
+        <v>43852</v>
       </c>
       <c r="E84" t="n">
-        <v>196781</v>
+        <v>164917</v>
       </c>
       <c r="F84" t="n">
-        <v>55256</v>
+        <v>42730</v>
       </c>
       <c r="G84" t="n">
-        <v>386993</v>
+        <v>337482</v>
       </c>
       <c r="H84" t="n">
-        <v>108896</v>
+        <v>86582</v>
       </c>
       <c r="I84" t="n">
-        <v>28.14</v>
+        <v>25.66</v>
       </c>
       <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>2</v>
       </c>
-      <c r="K84" t="n">
-        <v>3</v>
-      </c>
       <c r="L84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>개화산</t>
+          <t>거여</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3988,40 +3988,40 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>172565</v>
+        <v>291759</v>
       </c>
       <c r="D85" t="n">
-        <v>43852</v>
+        <v>70164</v>
       </c>
       <c r="E85" t="n">
-        <v>164917</v>
+        <v>282342</v>
       </c>
       <c r="F85" t="n">
-        <v>42730</v>
+        <v>68179</v>
       </c>
       <c r="G85" t="n">
-        <v>337482</v>
+        <v>574101</v>
       </c>
       <c r="H85" t="n">
-        <v>86582</v>
+        <v>138343</v>
       </c>
       <c r="I85" t="n">
-        <v>25.66</v>
+        <v>24.1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>거여</t>
+          <t>고덕</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4030,40 +4030,40 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>291759</v>
+        <v>299295</v>
       </c>
       <c r="D86" t="n">
-        <v>70164</v>
+        <v>79625</v>
       </c>
       <c r="E86" t="n">
-        <v>282342</v>
+        <v>292521</v>
       </c>
       <c r="F86" t="n">
-        <v>68179</v>
+        <v>78156</v>
       </c>
       <c r="G86" t="n">
-        <v>574101</v>
+        <v>591816</v>
       </c>
       <c r="H86" t="n">
-        <v>138343</v>
+        <v>157781</v>
       </c>
       <c r="I86" t="n">
-        <v>24.1</v>
+        <v>26.66</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>고덕</t>
+          <t>광나루</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4072,40 +4072,40 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>299295</v>
+        <v>375202</v>
       </c>
       <c r="D87" t="n">
-        <v>79625</v>
+        <v>73599</v>
       </c>
       <c r="E87" t="n">
-        <v>292521</v>
+        <v>353884</v>
       </c>
       <c r="F87" t="n">
-        <v>78156</v>
+        <v>71628</v>
       </c>
       <c r="G87" t="n">
-        <v>591816</v>
+        <v>729086</v>
       </c>
       <c r="H87" t="n">
-        <v>157781</v>
+        <v>145227</v>
       </c>
       <c r="I87" t="n">
-        <v>26.66</v>
+        <v>19.92</v>
       </c>
       <c r="J87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K87" t="n">
         <v>4</v>
       </c>
       <c r="L87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>광나루</t>
+          <t>광화문</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4114,40 +4114,40 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>375202</v>
+        <v>957048</v>
       </c>
       <c r="D88" t="n">
-        <v>73599</v>
+        <v>100036</v>
       </c>
       <c r="E88" t="n">
-        <v>353884</v>
+        <v>1006443</v>
       </c>
       <c r="F88" t="n">
-        <v>71628</v>
+        <v>99151</v>
       </c>
       <c r="G88" t="n">
-        <v>729086</v>
+        <v>1963491</v>
       </c>
       <c r="H88" t="n">
-        <v>145227</v>
+        <v>199187</v>
       </c>
       <c r="I88" t="n">
-        <v>19.92</v>
+        <v>10.14</v>
       </c>
       <c r="J88" t="n">
         <v>4</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>광화문</t>
+          <t>굽은다리</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4156,40 +4156,40 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>957048</v>
+        <v>288736</v>
       </c>
       <c r="D89" t="n">
-        <v>100036</v>
+        <v>83933</v>
       </c>
       <c r="E89" t="n">
-        <v>1006443</v>
+        <v>275879</v>
       </c>
       <c r="F89" t="n">
-        <v>99151</v>
+        <v>78941</v>
       </c>
       <c r="G89" t="n">
-        <v>1963491</v>
+        <v>564615</v>
       </c>
       <c r="H89" t="n">
-        <v>199187</v>
+        <v>162874</v>
       </c>
       <c r="I89" t="n">
-        <v>10.14</v>
+        <v>28.85</v>
       </c>
       <c r="J89" t="n">
         <v>4</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>굽은다리</t>
+          <t>길동</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4198,40 +4198,40 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>288736</v>
+        <v>247837</v>
       </c>
       <c r="D90" t="n">
-        <v>83933</v>
+        <v>82177</v>
       </c>
       <c r="E90" t="n">
-        <v>275879</v>
+        <v>254202</v>
       </c>
       <c r="F90" t="n">
-        <v>78941</v>
+        <v>83931</v>
       </c>
       <c r="G90" t="n">
-        <v>564615</v>
+        <v>502039</v>
       </c>
       <c r="H90" t="n">
-        <v>162874</v>
+        <v>166108</v>
       </c>
       <c r="I90" t="n">
-        <v>28.85</v>
+        <v>33.09</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K90" t="n">
         <v>3</v>
       </c>
       <c r="L90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>길동</t>
+          <t>까치산</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4240,40 +4240,40 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>247837</v>
+        <v>814059</v>
       </c>
       <c r="D91" t="n">
-        <v>82177</v>
+        <v>164710</v>
       </c>
       <c r="E91" t="n">
-        <v>254202</v>
+        <v>781516</v>
       </c>
       <c r="F91" t="n">
-        <v>83931</v>
+        <v>165992</v>
       </c>
       <c r="G91" t="n">
-        <v>502039</v>
+        <v>1595575</v>
       </c>
       <c r="H91" t="n">
-        <v>166108</v>
+        <v>330702</v>
       </c>
       <c r="I91" t="n">
-        <v>33.09</v>
+        <v>20.73</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>까치산</t>
+          <t>답십리</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4282,40 +4282,40 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>814059</v>
+        <v>458993</v>
       </c>
       <c r="D92" t="n">
-        <v>164710</v>
+        <v>86954</v>
       </c>
       <c r="E92" t="n">
-        <v>781516</v>
+        <v>416125</v>
       </c>
       <c r="F92" t="n">
-        <v>165992</v>
+        <v>83704</v>
       </c>
       <c r="G92" t="n">
-        <v>1595575</v>
+        <v>875118</v>
       </c>
       <c r="H92" t="n">
-        <v>330702</v>
+        <v>170658</v>
       </c>
       <c r="I92" t="n">
-        <v>20.73</v>
+        <v>19.5</v>
       </c>
       <c r="J92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K92" t="n">
         <v>4</v>
       </c>
       <c r="L92" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>답십리</t>
+          <t>둔촌동</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4324,40 +4324,40 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>458993</v>
+        <v>296332</v>
       </c>
       <c r="D93" t="n">
-        <v>86954</v>
+        <v>78666</v>
       </c>
       <c r="E93" t="n">
-        <v>416125</v>
+        <v>294564</v>
       </c>
       <c r="F93" t="n">
-        <v>83704</v>
+        <v>79119</v>
       </c>
       <c r="G93" t="n">
-        <v>875118</v>
+        <v>590896</v>
       </c>
       <c r="H93" t="n">
-        <v>170658</v>
+        <v>157785</v>
       </c>
       <c r="I93" t="n">
-        <v>19.5</v>
+        <v>26.7</v>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>둔촌동</t>
+          <t>마곡</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4366,40 +4366,40 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>296332</v>
+        <v>347361</v>
       </c>
       <c r="D94" t="n">
-        <v>78666</v>
+        <v>52044</v>
       </c>
       <c r="E94" t="n">
-        <v>294564</v>
+        <v>351461</v>
       </c>
       <c r="F94" t="n">
-        <v>79119</v>
+        <v>50645</v>
       </c>
       <c r="G94" t="n">
-        <v>590896</v>
+        <v>698822</v>
       </c>
       <c r="H94" t="n">
-        <v>157785</v>
+        <v>102689</v>
       </c>
       <c r="I94" t="n">
-        <v>26.7</v>
+        <v>14.69</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L94" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>마곡</t>
+          <t>마장</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>347361</v>
+        <v>172049</v>
       </c>
       <c r="D95" t="n">
-        <v>52044</v>
+        <v>43789</v>
       </c>
       <c r="E95" t="n">
-        <v>351461</v>
+        <v>161650</v>
       </c>
       <c r="F95" t="n">
-        <v>50645</v>
+        <v>42637</v>
       </c>
       <c r="G95" t="n">
-        <v>698822</v>
+        <v>333699</v>
       </c>
       <c r="H95" t="n">
-        <v>102689</v>
+        <v>86426</v>
       </c>
       <c r="I95" t="n">
-        <v>14.69</v>
+        <v>25.9</v>
       </c>
       <c r="J95" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L95" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>마장</t>
+          <t>마천</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4450,40 +4450,40 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>172049</v>
+        <v>214340</v>
       </c>
       <c r="D96" t="n">
-        <v>43789</v>
+        <v>59538</v>
       </c>
       <c r="E96" t="n">
-        <v>161650</v>
+        <v>198016</v>
       </c>
       <c r="F96" t="n">
-        <v>42637</v>
+        <v>60889</v>
       </c>
       <c r="G96" t="n">
-        <v>333699</v>
+        <v>412356</v>
       </c>
       <c r="H96" t="n">
-        <v>86426</v>
+        <v>120427</v>
       </c>
       <c r="I96" t="n">
-        <v>25.9</v>
+        <v>29.2</v>
       </c>
       <c r="J96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K96" t="n">
         <v>3</v>
       </c>
       <c r="L96" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>마천</t>
+          <t>마포</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4492,40 +4492,40 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>214340</v>
+        <v>415591</v>
       </c>
       <c r="D97" t="n">
-        <v>59538</v>
+        <v>66098</v>
       </c>
       <c r="E97" t="n">
-        <v>198016</v>
+        <v>422710</v>
       </c>
       <c r="F97" t="n">
-        <v>60889</v>
+        <v>65596</v>
       </c>
       <c r="G97" t="n">
-        <v>412356</v>
+        <v>838301</v>
       </c>
       <c r="H97" t="n">
-        <v>120427</v>
+        <v>131694</v>
       </c>
       <c r="I97" t="n">
-        <v>29.2</v>
+        <v>15.71</v>
       </c>
       <c r="J97" t="n">
         <v>10</v>
       </c>
       <c r="K97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>마포</t>
+          <t>명일</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>415591</v>
+        <v>252942</v>
       </c>
       <c r="D98" t="n">
-        <v>66098</v>
+        <v>73518</v>
       </c>
       <c r="E98" t="n">
-        <v>422710</v>
+        <v>255248</v>
       </c>
       <c r="F98" t="n">
-        <v>65596</v>
+        <v>75135</v>
       </c>
       <c r="G98" t="n">
-        <v>838301</v>
+        <v>508190</v>
       </c>
       <c r="H98" t="n">
-        <v>131694</v>
+        <v>148653</v>
       </c>
       <c r="I98" t="n">
-        <v>15.71</v>
+        <v>29.25</v>
       </c>
       <c r="J98" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>명일</t>
+          <t>목동</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4576,40 +4576,40 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>252942</v>
+        <v>477823</v>
       </c>
       <c r="D99" t="n">
-        <v>73518</v>
+        <v>87895</v>
       </c>
       <c r="E99" t="n">
-        <v>255248</v>
+        <v>509824</v>
       </c>
       <c r="F99" t="n">
-        <v>75135</v>
+        <v>89392</v>
       </c>
       <c r="G99" t="n">
-        <v>508190</v>
+        <v>987647</v>
       </c>
       <c r="H99" t="n">
-        <v>148653</v>
+        <v>177287</v>
       </c>
       <c r="I99" t="n">
-        <v>29.25</v>
+        <v>17.95</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K99" t="n">
         <v>3</v>
       </c>
       <c r="L99" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>목동</t>
+          <t>발산</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4618,40 +4618,40 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>477823</v>
+        <v>646724</v>
       </c>
       <c r="D100" t="n">
-        <v>87895</v>
+        <v>113341</v>
       </c>
       <c r="E100" t="n">
-        <v>509824</v>
+        <v>668751</v>
       </c>
       <c r="F100" t="n">
-        <v>89392</v>
+        <v>109595</v>
       </c>
       <c r="G100" t="n">
-        <v>987647</v>
+        <v>1315475</v>
       </c>
       <c r="H100" t="n">
-        <v>177287</v>
+        <v>222936</v>
       </c>
       <c r="I100" t="n">
-        <v>17.95</v>
+        <v>16.95</v>
       </c>
       <c r="J100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>3</v>
       </c>
       <c r="L100" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>발산</t>
+          <t>방이</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4660,40 +4660,40 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>646724</v>
+        <v>216835</v>
       </c>
       <c r="D101" t="n">
-        <v>113341</v>
+        <v>52521</v>
       </c>
       <c r="E101" t="n">
-        <v>668751</v>
+        <v>221174</v>
       </c>
       <c r="F101" t="n">
-        <v>109595</v>
+        <v>52503</v>
       </c>
       <c r="G101" t="n">
-        <v>1315475</v>
+        <v>438009</v>
       </c>
       <c r="H101" t="n">
-        <v>222936</v>
+        <v>105024</v>
       </c>
       <c r="I101" t="n">
-        <v>16.95</v>
+        <v>23.98</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>방이</t>
+          <t>방화</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4702,40 +4702,40 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>216835</v>
+        <v>203041</v>
       </c>
       <c r="D102" t="n">
-        <v>52521</v>
+        <v>57926</v>
       </c>
       <c r="E102" t="n">
-        <v>221174</v>
+        <v>194670</v>
       </c>
       <c r="F102" t="n">
-        <v>52503</v>
+        <v>56879</v>
       </c>
       <c r="G102" t="n">
-        <v>438009</v>
+        <v>397711</v>
       </c>
       <c r="H102" t="n">
-        <v>105024</v>
+        <v>114805</v>
       </c>
       <c r="I102" t="n">
-        <v>23.98</v>
+        <v>28.87</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L102" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>방화</t>
+          <t>상일동</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4744,40 +4744,40 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>203041</v>
+        <v>419058</v>
       </c>
       <c r="D103" t="n">
-        <v>57926</v>
+        <v>96105</v>
       </c>
       <c r="E103" t="n">
-        <v>194670</v>
+        <v>397475</v>
       </c>
       <c r="F103" t="n">
-        <v>56879</v>
+        <v>94654</v>
       </c>
       <c r="G103" t="n">
-        <v>397711</v>
+        <v>816533</v>
       </c>
       <c r="H103" t="n">
-        <v>114805</v>
+        <v>190759</v>
       </c>
       <c r="I103" t="n">
-        <v>28.87</v>
+        <v>23.36</v>
       </c>
       <c r="J103" t="n">
+        <v>16</v>
+      </c>
+      <c r="K103" t="n">
         <v>6</v>
       </c>
-      <c r="K103" t="n">
-        <v>3</v>
-      </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>상일동</t>
+          <t>서대문</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4786,40 +4786,40 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>419058</v>
+        <v>549925</v>
       </c>
       <c r="D104" t="n">
-        <v>96105</v>
+        <v>73647</v>
       </c>
       <c r="E104" t="n">
-        <v>397475</v>
+        <v>552121</v>
       </c>
       <c r="F104" t="n">
-        <v>94654</v>
+        <v>69654</v>
       </c>
       <c r="G104" t="n">
-        <v>816533</v>
+        <v>1102046</v>
       </c>
       <c r="H104" t="n">
-        <v>190759</v>
+        <v>143301</v>
       </c>
       <c r="I104" t="n">
-        <v>23.36</v>
+        <v>13</v>
       </c>
       <c r="J104" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L104" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>서대문</t>
+          <t>송정</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4828,40 +4828,40 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>549925</v>
+        <v>187616</v>
       </c>
       <c r="D105" t="n">
-        <v>73647</v>
+        <v>51923</v>
       </c>
       <c r="E105" t="n">
-        <v>552121</v>
+        <v>177560</v>
       </c>
       <c r="F105" t="n">
-        <v>69654</v>
+        <v>49900</v>
       </c>
       <c r="G105" t="n">
-        <v>1102046</v>
+        <v>365176</v>
       </c>
       <c r="H105" t="n">
-        <v>143301</v>
+        <v>101823</v>
       </c>
       <c r="I105" t="n">
-        <v>13</v>
+        <v>27.88</v>
       </c>
       <c r="J105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L105" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>송정</t>
+          <t>신금호</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4870,40 +4870,40 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>187616</v>
+        <v>184048</v>
       </c>
       <c r="D106" t="n">
-        <v>51923</v>
+        <v>40032</v>
       </c>
       <c r="E106" t="n">
-        <v>177560</v>
+        <v>194994</v>
       </c>
       <c r="F106" t="n">
-        <v>49900</v>
+        <v>45260</v>
       </c>
       <c r="G106" t="n">
-        <v>365176</v>
+        <v>379042</v>
       </c>
       <c r="H106" t="n">
-        <v>101823</v>
+        <v>85292</v>
       </c>
       <c r="I106" t="n">
-        <v>27.88</v>
+        <v>22.5</v>
       </c>
       <c r="J106" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L106" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>신금호</t>
+          <t>신길</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4912,31 +4912,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>184048</v>
+        <v>140429</v>
       </c>
       <c r="D107" t="n">
-        <v>40032</v>
+        <v>12815</v>
       </c>
       <c r="E107" t="n">
-        <v>194994</v>
+        <v>144543</v>
       </c>
       <c r="F107" t="n">
-        <v>45260</v>
+        <v>13241</v>
       </c>
       <c r="G107" t="n">
-        <v>379042</v>
+        <v>284972</v>
       </c>
       <c r="H107" t="n">
-        <v>85292</v>
+        <v>26056</v>
       </c>
       <c r="I107" t="n">
-        <v>22.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L107" t="n">
         <v>15</v>
@@ -4945,7 +4945,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>신길</t>
+          <t>신정</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4954,40 +4954,40 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>140429</v>
+        <v>386339</v>
       </c>
       <c r="D108" t="n">
-        <v>12815</v>
+        <v>67243</v>
       </c>
       <c r="E108" t="n">
-        <v>144543</v>
+        <v>322966</v>
       </c>
       <c r="F108" t="n">
-        <v>13241</v>
+        <v>65125</v>
       </c>
       <c r="G108" t="n">
-        <v>284972</v>
+        <v>709305</v>
       </c>
       <c r="H108" t="n">
-        <v>26056</v>
+        <v>132368</v>
       </c>
       <c r="I108" t="n">
-        <v>9.140000000000001</v>
+        <v>18.66</v>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K108" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L108" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>신정</t>
+          <t>아차산</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4996,40 +4996,40 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>386339</v>
+        <v>443991</v>
       </c>
       <c r="D109" t="n">
-        <v>67243</v>
+        <v>107459</v>
       </c>
       <c r="E109" t="n">
-        <v>322966</v>
+        <v>431490</v>
       </c>
       <c r="F109" t="n">
-        <v>65125</v>
+        <v>104831</v>
       </c>
       <c r="G109" t="n">
-        <v>709305</v>
+        <v>875481</v>
       </c>
       <c r="H109" t="n">
-        <v>132368</v>
+        <v>212290</v>
       </c>
       <c r="I109" t="n">
-        <v>18.66</v>
+        <v>24.25</v>
       </c>
       <c r="J109" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>아차산</t>
+          <t>애오개</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5038,31 +5038,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>443991</v>
+        <v>191333</v>
       </c>
       <c r="D110" t="n">
-        <v>107459</v>
+        <v>40245</v>
       </c>
       <c r="E110" t="n">
-        <v>431490</v>
+        <v>187395</v>
       </c>
       <c r="F110" t="n">
-        <v>104831</v>
+        <v>38796</v>
       </c>
       <c r="G110" t="n">
-        <v>875481</v>
+        <v>378728</v>
       </c>
       <c r="H110" t="n">
-        <v>212290</v>
+        <v>79041</v>
       </c>
       <c r="I110" t="n">
-        <v>24.25</v>
+        <v>20.87</v>
       </c>
       <c r="J110" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L110" t="n">
         <v>11</v>
@@ -5071,7 +5071,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>애오개</t>
+          <t>양평</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5080,31 +5080,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>191333</v>
+        <v>217500</v>
       </c>
       <c r="D111" t="n">
-        <v>40245</v>
+        <v>31548</v>
       </c>
       <c r="E111" t="n">
-        <v>187395</v>
+        <v>211295</v>
       </c>
       <c r="F111" t="n">
-        <v>38796</v>
+        <v>31034</v>
       </c>
       <c r="G111" t="n">
-        <v>378728</v>
+        <v>428795</v>
       </c>
       <c r="H111" t="n">
-        <v>79041</v>
+        <v>62582</v>
       </c>
       <c r="I111" t="n">
-        <v>20.87</v>
+        <v>14.59</v>
       </c>
       <c r="J111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L111" t="n">
         <v>11</v>
@@ -5113,7 +5113,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>양평</t>
+          <t>여의나루</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5122,40 +5122,40 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>217500</v>
+        <v>412094</v>
       </c>
       <c r="D112" t="n">
-        <v>31548</v>
+        <v>33235</v>
       </c>
       <c r="E112" t="n">
-        <v>211295</v>
+        <v>470524</v>
       </c>
       <c r="F112" t="n">
-        <v>31034</v>
+        <v>32782</v>
       </c>
       <c r="G112" t="n">
-        <v>428795</v>
+        <v>882618</v>
       </c>
       <c r="H112" t="n">
-        <v>62582</v>
+        <v>66017</v>
       </c>
       <c r="I112" t="n">
-        <v>14.59</v>
+        <v>7.48</v>
       </c>
       <c r="J112" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K112" t="n">
         <v>3</v>
       </c>
       <c r="L112" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>여의나루</t>
+          <t>영등포시장</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5164,40 +5164,40 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>412094</v>
+        <v>337898</v>
       </c>
       <c r="D113" t="n">
-        <v>33235</v>
+        <v>79894</v>
       </c>
       <c r="E113" t="n">
-        <v>470524</v>
+        <v>342868</v>
       </c>
       <c r="F113" t="n">
-        <v>32782</v>
+        <v>81581</v>
       </c>
       <c r="G113" t="n">
-        <v>882618</v>
+        <v>680766</v>
       </c>
       <c r="H113" t="n">
-        <v>66017</v>
+        <v>161475</v>
       </c>
       <c r="I113" t="n">
-        <v>7.48</v>
+        <v>23.72</v>
       </c>
       <c r="J113" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K113" t="n">
         <v>3</v>
       </c>
       <c r="L113" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>영등포시장</t>
+          <t>오목교</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5206,40 +5206,40 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>337898</v>
+        <v>619344</v>
       </c>
       <c r="D114" t="n">
-        <v>79894</v>
+        <v>93232</v>
       </c>
       <c r="E114" t="n">
-        <v>342868</v>
+        <v>653117</v>
       </c>
       <c r="F114" t="n">
-        <v>81581</v>
+        <v>92509</v>
       </c>
       <c r="G114" t="n">
-        <v>680766</v>
+        <v>1272461</v>
       </c>
       <c r="H114" t="n">
-        <v>161475</v>
+        <v>185741</v>
       </c>
       <c r="I114" t="n">
-        <v>23.72</v>
+        <v>14.6</v>
       </c>
       <c r="J114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K114" t="n">
         <v>3</v>
       </c>
       <c r="L114" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>오목교</t>
+          <t>올림픽공원</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5248,40 +5248,40 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>619344</v>
+        <v>162308</v>
       </c>
       <c r="D115" t="n">
-        <v>93232</v>
+        <v>41571</v>
       </c>
       <c r="E115" t="n">
-        <v>653117</v>
+        <v>144586</v>
       </c>
       <c r="F115" t="n">
-        <v>92509</v>
+        <v>36964</v>
       </c>
       <c r="G115" t="n">
-        <v>1272461</v>
+        <v>306894</v>
       </c>
       <c r="H115" t="n">
-        <v>185741</v>
+        <v>78535</v>
       </c>
       <c r="I115" t="n">
-        <v>14.6</v>
+        <v>25.59</v>
       </c>
       <c r="J115" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K115" t="n">
         <v>3</v>
       </c>
       <c r="L115" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>올림픽공원</t>
+          <t>우장산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5290,25 +5290,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>162308</v>
+        <v>427755</v>
       </c>
       <c r="D116" t="n">
-        <v>41571</v>
+        <v>101202</v>
       </c>
       <c r="E116" t="n">
-        <v>144586</v>
+        <v>423688</v>
       </c>
       <c r="F116" t="n">
-        <v>36964</v>
+        <v>105280</v>
       </c>
       <c r="G116" t="n">
-        <v>306894</v>
+        <v>851443</v>
       </c>
       <c r="H116" t="n">
-        <v>78535</v>
+        <v>206482</v>
       </c>
       <c r="I116" t="n">
-        <v>25.59</v>
+        <v>24.25</v>
       </c>
       <c r="J116" t="n">
         <v>4</v>
@@ -5323,7 +5323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>우장산</t>
+          <t>장한평</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5332,25 +5332,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>427755</v>
+        <v>551537</v>
       </c>
       <c r="D117" t="n">
-        <v>101202</v>
+        <v>101379</v>
       </c>
       <c r="E117" t="n">
-        <v>423688</v>
+        <v>544629</v>
       </c>
       <c r="F117" t="n">
-        <v>105280</v>
+        <v>103383</v>
       </c>
       <c r="G117" t="n">
-        <v>851443</v>
+        <v>1096166</v>
       </c>
       <c r="H117" t="n">
-        <v>206482</v>
+        <v>204762</v>
       </c>
       <c r="I117" t="n">
-        <v>24.25</v>
+        <v>18.68</v>
       </c>
       <c r="J117" t="n">
         <v>4</v>
@@ -5365,7 +5365,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>장한평</t>
+          <t>행당</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5374,40 +5374,40 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>551537</v>
+        <v>233829</v>
       </c>
       <c r="D118" t="n">
-        <v>101379</v>
+        <v>53073</v>
       </c>
       <c r="E118" t="n">
-        <v>544629</v>
+        <v>207738</v>
       </c>
       <c r="F118" t="n">
-        <v>103383</v>
+        <v>48025</v>
       </c>
       <c r="G118" t="n">
-        <v>1096166</v>
+        <v>441567</v>
       </c>
       <c r="H118" t="n">
-        <v>204762</v>
+        <v>101098</v>
       </c>
       <c r="I118" t="n">
-        <v>18.68</v>
+        <v>22.9</v>
       </c>
       <c r="J118" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K118" t="n">
         <v>3</v>
       </c>
       <c r="L118" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>행당</t>
+          <t>화곡</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5416,82 +5416,82 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>233829</v>
+        <v>826102</v>
       </c>
       <c r="D119" t="n">
-        <v>53073</v>
+        <v>155956</v>
       </c>
       <c r="E119" t="n">
-        <v>207738</v>
+        <v>769286</v>
       </c>
       <c r="F119" t="n">
-        <v>48025</v>
+        <v>149325</v>
       </c>
       <c r="G119" t="n">
-        <v>441567</v>
+        <v>1595388</v>
       </c>
       <c r="H119" t="n">
-        <v>101098</v>
+        <v>305281</v>
       </c>
       <c r="I119" t="n">
-        <v>22.9</v>
+        <v>19.14</v>
       </c>
       <c r="J119" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>화곡</t>
+          <t>고려대</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>826102</v>
+        <v>260067</v>
       </c>
       <c r="D120" t="n">
-        <v>155956</v>
+        <v>36577</v>
       </c>
       <c r="E120" t="n">
-        <v>769286</v>
+        <v>249432</v>
       </c>
       <c r="F120" t="n">
-        <v>149325</v>
+        <v>35940</v>
       </c>
       <c r="G120" t="n">
-        <v>1595388</v>
+        <v>509499</v>
       </c>
       <c r="H120" t="n">
-        <v>305281</v>
+        <v>72517</v>
       </c>
       <c r="I120" t="n">
-        <v>19.14</v>
+        <v>14.23</v>
       </c>
       <c r="J120" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L120" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>고려대</t>
+          <t>광흥창</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5500,40 +5500,40 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>260067</v>
+        <v>271530</v>
       </c>
       <c r="D121" t="n">
-        <v>36577</v>
+        <v>56070</v>
       </c>
       <c r="E121" t="n">
-        <v>249432</v>
+        <v>260009</v>
       </c>
       <c r="F121" t="n">
-        <v>35940</v>
+        <v>55268</v>
       </c>
       <c r="G121" t="n">
-        <v>509499</v>
+        <v>531539</v>
       </c>
       <c r="H121" t="n">
-        <v>72517</v>
+        <v>111338</v>
       </c>
       <c r="I121" t="n">
-        <v>14.23</v>
+        <v>20.95</v>
       </c>
       <c r="J121" t="n">
+        <v>9</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" t="n">
         <v>12</v>
-      </c>
-      <c r="K121" t="n">
-        <v>4</v>
-      </c>
-      <c r="L121" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>광흥창</t>
+          <t>구산</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5542,40 +5542,40 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>271530</v>
+        <v>237080</v>
       </c>
       <c r="D122" t="n">
-        <v>56070</v>
+        <v>57105</v>
       </c>
       <c r="E122" t="n">
-        <v>260009</v>
+        <v>180593</v>
       </c>
       <c r="F122" t="n">
-        <v>55268</v>
+        <v>59481</v>
       </c>
       <c r="G122" t="n">
-        <v>531539</v>
+        <v>417673</v>
       </c>
       <c r="H122" t="n">
-        <v>111338</v>
+        <v>116586</v>
       </c>
       <c r="I122" t="n">
-        <v>20.95</v>
+        <v>27.91</v>
       </c>
       <c r="J122" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L122" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>구산</t>
+          <t>녹사평</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5584,40 +5584,40 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>237080</v>
+        <v>157571</v>
       </c>
       <c r="D123" t="n">
-        <v>57105</v>
+        <v>18590</v>
       </c>
       <c r="E123" t="n">
-        <v>180593</v>
+        <v>160969</v>
       </c>
       <c r="F123" t="n">
-        <v>59481</v>
+        <v>18149</v>
       </c>
       <c r="G123" t="n">
-        <v>417673</v>
+        <v>318540</v>
       </c>
       <c r="H123" t="n">
-        <v>116586</v>
+        <v>36739</v>
       </c>
       <c r="I123" t="n">
-        <v>27.91</v>
+        <v>11.53</v>
       </c>
       <c r="J123" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L123" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>녹사평</t>
+          <t>대흥</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5626,40 +5626,40 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>157571</v>
+        <v>270622</v>
       </c>
       <c r="D124" t="n">
-        <v>18590</v>
+        <v>49384</v>
       </c>
       <c r="E124" t="n">
-        <v>160969</v>
+        <v>281582</v>
       </c>
       <c r="F124" t="n">
-        <v>18149</v>
+        <v>49193</v>
       </c>
       <c r="G124" t="n">
-        <v>318540</v>
+        <v>552204</v>
       </c>
       <c r="H124" t="n">
-        <v>36739</v>
+        <v>98577</v>
       </c>
       <c r="I124" t="n">
-        <v>11.53</v>
+        <v>17.85</v>
       </c>
       <c r="J124" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K124" t="n">
         <v>3</v>
       </c>
       <c r="L124" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>대흥</t>
+          <t>독바위</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5668,40 +5668,40 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>270622</v>
+        <v>80401</v>
       </c>
       <c r="D125" t="n">
-        <v>49384</v>
+        <v>21437</v>
       </c>
       <c r="E125" t="n">
-        <v>281582</v>
+        <v>84959</v>
       </c>
       <c r="F125" t="n">
-        <v>49193</v>
+        <v>26395</v>
       </c>
       <c r="G125" t="n">
-        <v>552204</v>
+        <v>165360</v>
       </c>
       <c r="H125" t="n">
-        <v>98577</v>
+        <v>47832</v>
       </c>
       <c r="I125" t="n">
-        <v>17.85</v>
+        <v>28.93</v>
       </c>
       <c r="J125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>독바위</t>
+          <t>돌곶이</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5710,40 +5710,40 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>80401</v>
+        <v>304544</v>
       </c>
       <c r="D126" t="n">
-        <v>21437</v>
+        <v>66060</v>
       </c>
       <c r="E126" t="n">
-        <v>84959</v>
+        <v>280650</v>
       </c>
       <c r="F126" t="n">
-        <v>26395</v>
+        <v>65110</v>
       </c>
       <c r="G126" t="n">
-        <v>165360</v>
+        <v>585194</v>
       </c>
       <c r="H126" t="n">
-        <v>47832</v>
+        <v>131170</v>
       </c>
       <c r="I126" t="n">
-        <v>28.93</v>
+        <v>22.41</v>
       </c>
       <c r="J126" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L126" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>돌곶이</t>
+          <t>디지털미디어시티</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5752,40 +5752,40 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>304544</v>
+        <v>414387</v>
       </c>
       <c r="D127" t="n">
-        <v>66060</v>
+        <v>61725</v>
       </c>
       <c r="E127" t="n">
-        <v>280650</v>
+        <v>446335</v>
       </c>
       <c r="F127" t="n">
-        <v>65110</v>
+        <v>62422</v>
       </c>
       <c r="G127" t="n">
-        <v>585194</v>
+        <v>860722</v>
       </c>
       <c r="H127" t="n">
-        <v>131170</v>
+        <v>124147</v>
       </c>
       <c r="I127" t="n">
-        <v>22.41</v>
+        <v>14.42</v>
       </c>
       <c r="J127" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K127" t="n">
         <v>3</v>
       </c>
       <c r="L127" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>디지털미디어시티</t>
+          <t>마포구청</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5794,40 +5794,40 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>414387</v>
+        <v>424134</v>
       </c>
       <c r="D128" t="n">
-        <v>61725</v>
+        <v>84007</v>
       </c>
       <c r="E128" t="n">
-        <v>446335</v>
+        <v>380124</v>
       </c>
       <c r="F128" t="n">
-        <v>62422</v>
+        <v>76784</v>
       </c>
       <c r="G128" t="n">
-        <v>860722</v>
+        <v>804258</v>
       </c>
       <c r="H128" t="n">
-        <v>124147</v>
+        <v>160791</v>
       </c>
       <c r="I128" t="n">
-        <v>14.42</v>
+        <v>19.99</v>
       </c>
       <c r="J128" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L128" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>마포구청</t>
+          <t>망원</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5836,40 +5836,40 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>424134</v>
+        <v>463783</v>
       </c>
       <c r="D129" t="n">
-        <v>84007</v>
+        <v>85481</v>
       </c>
       <c r="E129" t="n">
-        <v>380124</v>
+        <v>495333</v>
       </c>
       <c r="F129" t="n">
-        <v>76784</v>
+        <v>89100</v>
       </c>
       <c r="G129" t="n">
-        <v>804258</v>
+        <v>959116</v>
       </c>
       <c r="H129" t="n">
-        <v>160791</v>
+        <v>174581</v>
       </c>
       <c r="I129" t="n">
-        <v>19.99</v>
+        <v>18.2</v>
       </c>
       <c r="J129" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>망원</t>
+          <t>버티고개</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5878,40 +5878,40 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>463783</v>
+        <v>64186</v>
       </c>
       <c r="D130" t="n">
-        <v>85481</v>
+        <v>14604</v>
       </c>
       <c r="E130" t="n">
-        <v>495333</v>
+        <v>64434</v>
       </c>
       <c r="F130" t="n">
-        <v>89100</v>
+        <v>16701</v>
       </c>
       <c r="G130" t="n">
-        <v>959116</v>
+        <v>128620</v>
       </c>
       <c r="H130" t="n">
-        <v>174581</v>
+        <v>31305</v>
       </c>
       <c r="I130" t="n">
-        <v>18.2</v>
+        <v>24.34</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L130" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>버티고개</t>
+          <t>보문</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5920,40 +5920,40 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>64186</v>
+        <v>233704</v>
       </c>
       <c r="D131" t="n">
-        <v>14604</v>
+        <v>33040</v>
       </c>
       <c r="E131" t="n">
-        <v>64434</v>
+        <v>216693</v>
       </c>
       <c r="F131" t="n">
-        <v>16701</v>
+        <v>31271</v>
       </c>
       <c r="G131" t="n">
-        <v>128620</v>
+        <v>450397</v>
       </c>
       <c r="H131" t="n">
-        <v>31305</v>
+        <v>64311</v>
       </c>
       <c r="I131" t="n">
-        <v>24.34</v>
+        <v>14.28</v>
       </c>
       <c r="J131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>보문</t>
+          <t>봉화산</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5962,40 +5962,40 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>233704</v>
+        <v>251693</v>
       </c>
       <c r="D132" t="n">
-        <v>33040</v>
+        <v>52991</v>
       </c>
       <c r="E132" t="n">
-        <v>216693</v>
+        <v>237028</v>
       </c>
       <c r="F132" t="n">
-        <v>31271</v>
+        <v>52273</v>
       </c>
       <c r="G132" t="n">
-        <v>450397</v>
+        <v>488721</v>
       </c>
       <c r="H132" t="n">
-        <v>64311</v>
+        <v>105264</v>
       </c>
       <c r="I132" t="n">
-        <v>14.28</v>
+        <v>21.54</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L132" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>봉화산</t>
+          <t>상수</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6004,40 +6004,40 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>251693</v>
+        <v>309088</v>
       </c>
       <c r="D133" t="n">
-        <v>52991</v>
+        <v>22332</v>
       </c>
       <c r="E133" t="n">
-        <v>237028</v>
+        <v>349342</v>
       </c>
       <c r="F133" t="n">
-        <v>52273</v>
+        <v>22523</v>
       </c>
       <c r="G133" t="n">
-        <v>488721</v>
+        <v>658430</v>
       </c>
       <c r="H133" t="n">
-        <v>105264</v>
+        <v>44855</v>
       </c>
       <c r="I133" t="n">
-        <v>21.54</v>
+        <v>6.81</v>
       </c>
       <c r="J133" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L133" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>상수</t>
+          <t>상월곡</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6046,40 +6046,40 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>309088</v>
+        <v>191565</v>
       </c>
       <c r="D134" t="n">
-        <v>22332</v>
+        <v>43040</v>
       </c>
       <c r="E134" t="n">
-        <v>349342</v>
+        <v>175356</v>
       </c>
       <c r="F134" t="n">
-        <v>22523</v>
+        <v>41637</v>
       </c>
       <c r="G134" t="n">
-        <v>658430</v>
+        <v>366921</v>
       </c>
       <c r="H134" t="n">
-        <v>44855</v>
+        <v>84677</v>
       </c>
       <c r="I134" t="n">
-        <v>6.81</v>
+        <v>23.08</v>
       </c>
       <c r="J134" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K134" t="n">
         <v>3</v>
       </c>
       <c r="L134" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>상월곡</t>
+          <t>새절</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6088,40 +6088,40 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>191565</v>
+        <v>370343</v>
       </c>
       <c r="D135" t="n">
-        <v>43040</v>
+        <v>92437</v>
       </c>
       <c r="E135" t="n">
-        <v>175356</v>
+        <v>345979</v>
       </c>
       <c r="F135" t="n">
-        <v>41637</v>
+        <v>92578</v>
       </c>
       <c r="G135" t="n">
-        <v>366921</v>
+        <v>716322</v>
       </c>
       <c r="H135" t="n">
-        <v>84677</v>
+        <v>185015</v>
       </c>
       <c r="I135" t="n">
-        <v>23.08</v>
+        <v>25.83</v>
       </c>
       <c r="J135" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K135" t="n">
         <v>3</v>
       </c>
       <c r="L135" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>새절</t>
+          <t>석계</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6130,40 +6130,40 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>370343</v>
+        <v>361930</v>
       </c>
       <c r="D136" t="n">
-        <v>92437</v>
+        <v>83289</v>
       </c>
       <c r="E136" t="n">
-        <v>345979</v>
+        <v>370835</v>
       </c>
       <c r="F136" t="n">
-        <v>92578</v>
+        <v>82848</v>
       </c>
       <c r="G136" t="n">
-        <v>716322</v>
+        <v>732765</v>
       </c>
       <c r="H136" t="n">
-        <v>185015</v>
+        <v>166137</v>
       </c>
       <c r="I136" t="n">
-        <v>25.83</v>
+        <v>22.67</v>
       </c>
       <c r="J136" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L136" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>석계</t>
+          <t>안암</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6172,40 +6172,40 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>361930</v>
+        <v>375092</v>
       </c>
       <c r="D137" t="n">
-        <v>83289</v>
+        <v>38686</v>
       </c>
       <c r="E137" t="n">
-        <v>370835</v>
+        <v>375991</v>
       </c>
       <c r="F137" t="n">
-        <v>82848</v>
+        <v>38045</v>
       </c>
       <c r="G137" t="n">
-        <v>732765</v>
+        <v>751083</v>
       </c>
       <c r="H137" t="n">
-        <v>166137</v>
+        <v>76731</v>
       </c>
       <c r="I137" t="n">
-        <v>22.67</v>
+        <v>10.22</v>
       </c>
       <c r="J137" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L137" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>안암</t>
+          <t>역촌</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6214,40 +6214,40 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>375092</v>
+        <v>111649</v>
       </c>
       <c r="D138" t="n">
-        <v>38686</v>
+        <v>35325</v>
       </c>
       <c r="E138" t="n">
-        <v>375991</v>
+        <v>131103</v>
       </c>
       <c r="F138" t="n">
-        <v>38045</v>
+        <v>34793</v>
       </c>
       <c r="G138" t="n">
-        <v>751083</v>
+        <v>242752</v>
       </c>
       <c r="H138" t="n">
-        <v>76731</v>
+        <v>70118</v>
       </c>
       <c r="I138" t="n">
-        <v>10.22</v>
+        <v>28.88</v>
       </c>
       <c r="J138" t="n">
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>역촌</t>
+          <t>월곡</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6256,40 +6256,40 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>111649</v>
+        <v>348950</v>
       </c>
       <c r="D139" t="n">
-        <v>35325</v>
+        <v>71839</v>
       </c>
       <c r="E139" t="n">
-        <v>131103</v>
+        <v>338516</v>
       </c>
       <c r="F139" t="n">
-        <v>34793</v>
+        <v>71162</v>
       </c>
       <c r="G139" t="n">
-        <v>242752</v>
+        <v>687466</v>
       </c>
       <c r="H139" t="n">
-        <v>70118</v>
+        <v>143001</v>
       </c>
       <c r="I139" t="n">
-        <v>28.88</v>
+        <v>20.8</v>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>월곡</t>
+          <t>월드컵경기장</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6298,25 +6298,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>348950</v>
+        <v>185256</v>
       </c>
       <c r="D140" t="n">
-        <v>71839</v>
+        <v>59852</v>
       </c>
       <c r="E140" t="n">
-        <v>338516</v>
+        <v>202141</v>
       </c>
       <c r="F140" t="n">
-        <v>71162</v>
+        <v>58781</v>
       </c>
       <c r="G140" t="n">
-        <v>687466</v>
+        <v>387397</v>
       </c>
       <c r="H140" t="n">
-        <v>143001</v>
+        <v>118633</v>
       </c>
       <c r="I140" t="n">
-        <v>20.8</v>
+        <v>30.62</v>
       </c>
       <c r="J140" t="n">
         <v>12</v>
@@ -6331,7 +6331,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>월드컵경기장</t>
+          <t>응암</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6340,40 +6340,40 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>185256</v>
+        <v>516764</v>
       </c>
       <c r="D141" t="n">
-        <v>59852</v>
+        <v>127624</v>
       </c>
       <c r="E141" t="n">
-        <v>202141</v>
+        <v>511157</v>
       </c>
       <c r="F141" t="n">
-        <v>58781</v>
+        <v>126704</v>
       </c>
       <c r="G141" t="n">
-        <v>387397</v>
+        <v>1027921</v>
       </c>
       <c r="H141" t="n">
-        <v>118633</v>
+        <v>254328</v>
       </c>
       <c r="I141" t="n">
-        <v>30.62</v>
+        <v>24.74</v>
       </c>
       <c r="J141" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L141" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>응암</t>
+          <t>이태원</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6382,25 +6382,25 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>516764</v>
+        <v>358734</v>
       </c>
       <c r="D142" t="n">
-        <v>127624</v>
+        <v>31504</v>
       </c>
       <c r="E142" t="n">
-        <v>511157</v>
+        <v>391713</v>
       </c>
       <c r="F142" t="n">
-        <v>126704</v>
+        <v>31889</v>
       </c>
       <c r="G142" t="n">
-        <v>1027921</v>
+        <v>750447</v>
       </c>
       <c r="H142" t="n">
-        <v>254328</v>
+        <v>63393</v>
       </c>
       <c r="I142" t="n">
-        <v>24.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J142" t="n">
         <v>4</v>
@@ -6415,7 +6415,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>이태원</t>
+          <t>증산</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6424,40 +6424,40 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>358734</v>
+        <v>284376</v>
       </c>
       <c r="D143" t="n">
-        <v>31504</v>
+        <v>74103</v>
       </c>
       <c r="E143" t="n">
-        <v>391713</v>
+        <v>282585</v>
       </c>
       <c r="F143" t="n">
-        <v>31889</v>
+        <v>74764</v>
       </c>
       <c r="G143" t="n">
-        <v>750447</v>
+        <v>566961</v>
       </c>
       <c r="H143" t="n">
-        <v>63393</v>
+        <v>148867</v>
       </c>
       <c r="I143" t="n">
-        <v>8.449999999999999</v>
+        <v>26.26</v>
       </c>
       <c r="J143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L143" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>증산</t>
+          <t>창신</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6466,40 +6466,40 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>284376</v>
+        <v>103270</v>
       </c>
       <c r="D144" t="n">
-        <v>74103</v>
+        <v>19926</v>
       </c>
       <c r="E144" t="n">
-        <v>282585</v>
+        <v>87145</v>
       </c>
       <c r="F144" t="n">
-        <v>74764</v>
+        <v>18921</v>
       </c>
       <c r="G144" t="n">
-        <v>566961</v>
+        <v>190415</v>
       </c>
       <c r="H144" t="n">
-        <v>148867</v>
+        <v>38847</v>
       </c>
       <c r="I144" t="n">
-        <v>26.26</v>
+        <v>20.4</v>
       </c>
       <c r="J144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K144" t="n">
         <v>3</v>
       </c>
       <c r="L144" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>창신</t>
+          <t>한강진</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6508,40 +6508,40 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>103270</v>
+        <v>302426</v>
       </c>
       <c r="D145" t="n">
-        <v>19926</v>
+        <v>20614</v>
       </c>
       <c r="E145" t="n">
-        <v>87145</v>
+        <v>354942</v>
       </c>
       <c r="F145" t="n">
-        <v>18921</v>
+        <v>20632</v>
       </c>
       <c r="G145" t="n">
-        <v>190415</v>
+        <v>657368</v>
       </c>
       <c r="H145" t="n">
-        <v>38847</v>
+        <v>41246</v>
       </c>
       <c r="I145" t="n">
-        <v>20.4</v>
+        <v>6.27</v>
       </c>
       <c r="J145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K145" t="n">
         <v>3</v>
       </c>
       <c r="L145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한강진</t>
+          <t>화랑대</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6550,40 +6550,40 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>302426</v>
+        <v>342753</v>
       </c>
       <c r="D146" t="n">
-        <v>20614</v>
+        <v>51768</v>
       </c>
       <c r="E146" t="n">
-        <v>354942</v>
+        <v>273727</v>
       </c>
       <c r="F146" t="n">
-        <v>20632</v>
+        <v>46797</v>
       </c>
       <c r="G146" t="n">
-        <v>657368</v>
+        <v>616480</v>
       </c>
       <c r="H146" t="n">
-        <v>41246</v>
+        <v>98565</v>
       </c>
       <c r="I146" t="n">
-        <v>6.27</v>
+        <v>15.99</v>
       </c>
       <c r="J146" t="n">
         <v>4</v>
       </c>
       <c r="K146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L146" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>화랑대</t>
+          <t>효창공원앞</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6592,82 +6592,82 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>342753</v>
+        <v>218774</v>
       </c>
       <c r="D147" t="n">
-        <v>51768</v>
+        <v>39969</v>
       </c>
       <c r="E147" t="n">
-        <v>273727</v>
+        <v>199665</v>
       </c>
       <c r="F147" t="n">
-        <v>46797</v>
+        <v>37000</v>
       </c>
       <c r="G147" t="n">
-        <v>616480</v>
+        <v>418439</v>
       </c>
       <c r="H147" t="n">
-        <v>98565</v>
+        <v>76969</v>
       </c>
       <c r="I147" t="n">
-        <v>15.99</v>
+        <v>18.39</v>
       </c>
       <c r="J147" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>효창공원앞</t>
+          <t>가산디지털단지</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>218774</v>
+        <v>1154477</v>
       </c>
       <c r="D148" t="n">
-        <v>39969</v>
+        <v>98985</v>
       </c>
       <c r="E148" t="n">
-        <v>199665</v>
+        <v>1150220</v>
       </c>
       <c r="F148" t="n">
-        <v>37000</v>
+        <v>93082</v>
       </c>
       <c r="G148" t="n">
-        <v>418439</v>
+        <v>2304697</v>
       </c>
       <c r="H148" t="n">
-        <v>76969</v>
+        <v>192067</v>
       </c>
       <c r="I148" t="n">
-        <v>18.39</v>
+        <v>8.33</v>
       </c>
       <c r="J148" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>가산디지털단지</t>
+          <t>강남구청</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6676,40 +6676,40 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1154477</v>
+        <v>453643</v>
       </c>
       <c r="D149" t="n">
-        <v>98985</v>
+        <v>54065</v>
       </c>
       <c r="E149" t="n">
-        <v>1150220</v>
+        <v>502605</v>
       </c>
       <c r="F149" t="n">
-        <v>93082</v>
+        <v>55199</v>
       </c>
       <c r="G149" t="n">
-        <v>2304697</v>
+        <v>956248</v>
       </c>
       <c r="H149" t="n">
-        <v>192067</v>
+        <v>109264</v>
       </c>
       <c r="I149" t="n">
-        <v>8.33</v>
+        <v>11.43</v>
       </c>
       <c r="J149" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L149" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>강남구청</t>
+          <t>공릉</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6718,40 +6718,40 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>453643</v>
+        <v>359567</v>
       </c>
       <c r="D150" t="n">
-        <v>54065</v>
+        <v>77921</v>
       </c>
       <c r="E150" t="n">
-        <v>502605</v>
+        <v>354017</v>
       </c>
       <c r="F150" t="n">
-        <v>55199</v>
+        <v>78409</v>
       </c>
       <c r="G150" t="n">
-        <v>956248</v>
+        <v>713584</v>
       </c>
       <c r="H150" t="n">
-        <v>109264</v>
+        <v>156330</v>
       </c>
       <c r="I150" t="n">
-        <v>11.43</v>
+        <v>21.91</v>
       </c>
       <c r="J150" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L150" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>공릉</t>
+          <t>남구로</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6760,40 +6760,40 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>359567</v>
+        <v>420412</v>
       </c>
       <c r="D151" t="n">
-        <v>77921</v>
+        <v>65887</v>
       </c>
       <c r="E151" t="n">
-        <v>354017</v>
+        <v>439155</v>
       </c>
       <c r="F151" t="n">
-        <v>78409</v>
+        <v>66688</v>
       </c>
       <c r="G151" t="n">
-        <v>713584</v>
+        <v>859567</v>
       </c>
       <c r="H151" t="n">
-        <v>156330</v>
+        <v>132575</v>
       </c>
       <c r="I151" t="n">
-        <v>21.91</v>
+        <v>15.42</v>
       </c>
       <c r="J151" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K151" t="n">
         <v>3</v>
       </c>
       <c r="L151" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>남구로</t>
+          <t>남성</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6802,40 +6802,40 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>420412</v>
+        <v>331097</v>
       </c>
       <c r="D152" t="n">
-        <v>65887</v>
+        <v>78978</v>
       </c>
       <c r="E152" t="n">
-        <v>439155</v>
+        <v>313447</v>
       </c>
       <c r="F152" t="n">
-        <v>66688</v>
+        <v>79144</v>
       </c>
       <c r="G152" t="n">
-        <v>859567</v>
+        <v>644544</v>
       </c>
       <c r="H152" t="n">
-        <v>132575</v>
+        <v>158122</v>
       </c>
       <c r="I152" t="n">
-        <v>15.42</v>
+        <v>24.53</v>
       </c>
       <c r="J152" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L152" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>남성</t>
+          <t>내방</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6844,40 +6844,40 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>331097</v>
+        <v>410799</v>
       </c>
       <c r="D153" t="n">
-        <v>78978</v>
+        <v>76953</v>
       </c>
       <c r="E153" t="n">
-        <v>313447</v>
+        <v>413573</v>
       </c>
       <c r="F153" t="n">
-        <v>79144</v>
+        <v>74244</v>
       </c>
       <c r="G153" t="n">
-        <v>644544</v>
+        <v>824372</v>
       </c>
       <c r="H153" t="n">
-        <v>158122</v>
+        <v>151197</v>
       </c>
       <c r="I153" t="n">
-        <v>24.53</v>
+        <v>18.34</v>
       </c>
       <c r="J153" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L153" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>내방</t>
+          <t>논현</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6886,40 +6886,40 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>410799</v>
+        <v>512327</v>
       </c>
       <c r="D154" t="n">
-        <v>76953</v>
+        <v>45626</v>
       </c>
       <c r="E154" t="n">
-        <v>413573</v>
+        <v>531407</v>
       </c>
       <c r="F154" t="n">
-        <v>74244</v>
+        <v>44584</v>
       </c>
       <c r="G154" t="n">
-        <v>824372</v>
+        <v>1043734</v>
       </c>
       <c r="H154" t="n">
-        <v>151197</v>
+        <v>90210</v>
       </c>
       <c r="I154" t="n">
-        <v>18.34</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L154" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>논현</t>
+          <t>도봉산</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6928,40 +6928,40 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>512327</v>
+        <v>263297</v>
       </c>
       <c r="D155" t="n">
-        <v>45626</v>
+        <v>52765</v>
       </c>
       <c r="E155" t="n">
-        <v>531407</v>
+        <v>312768</v>
       </c>
       <c r="F155" t="n">
-        <v>44584</v>
+        <v>74776</v>
       </c>
       <c r="G155" t="n">
-        <v>1043734</v>
+        <v>576065</v>
       </c>
       <c r="H155" t="n">
-        <v>90210</v>
+        <v>127541</v>
       </c>
       <c r="I155" t="n">
-        <v>8.640000000000001</v>
+        <v>22.14</v>
       </c>
       <c r="J155" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L155" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>도봉산</t>
+          <t>마들</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6970,40 +6970,40 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>263297</v>
+        <v>382194</v>
       </c>
       <c r="D156" t="n">
-        <v>52765</v>
+        <v>96782</v>
       </c>
       <c r="E156" t="n">
-        <v>312768</v>
+        <v>358622</v>
       </c>
       <c r="F156" t="n">
-        <v>74776</v>
+        <v>94945</v>
       </c>
       <c r="G156" t="n">
-        <v>576065</v>
+        <v>740816</v>
       </c>
       <c r="H156" t="n">
-        <v>127541</v>
+        <v>191727</v>
       </c>
       <c r="I156" t="n">
-        <v>22.14</v>
+        <v>25.88</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L156" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>마들</t>
+          <t>먹골</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7012,40 +7012,40 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>382194</v>
+        <v>299231</v>
       </c>
       <c r="D157" t="n">
-        <v>96782</v>
+        <v>71685</v>
       </c>
       <c r="E157" t="n">
-        <v>358622</v>
+        <v>295255</v>
       </c>
       <c r="F157" t="n">
-        <v>94945</v>
+        <v>73234</v>
       </c>
       <c r="G157" t="n">
-        <v>740816</v>
+        <v>594486</v>
       </c>
       <c r="H157" t="n">
-        <v>191727</v>
+        <v>144919</v>
       </c>
       <c r="I157" t="n">
-        <v>25.88</v>
+        <v>24.38</v>
       </c>
       <c r="J157" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L157" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>먹골</t>
+          <t>면목</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7054,25 +7054,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>299231</v>
+        <v>440555</v>
       </c>
       <c r="D158" t="n">
-        <v>71685</v>
+        <v>101218</v>
       </c>
       <c r="E158" t="n">
-        <v>295255</v>
+        <v>422568</v>
       </c>
       <c r="F158" t="n">
-        <v>73234</v>
+        <v>103791</v>
       </c>
       <c r="G158" t="n">
-        <v>594486</v>
+        <v>863123</v>
       </c>
       <c r="H158" t="n">
-        <v>144919</v>
+        <v>205009</v>
       </c>
       <c r="I158" t="n">
-        <v>24.38</v>
+        <v>23.75</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
@@ -7087,7 +7087,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>면목</t>
+          <t>반포</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7096,40 +7096,40 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>440555</v>
+        <v>187796</v>
       </c>
       <c r="D159" t="n">
-        <v>101218</v>
+        <v>40370</v>
       </c>
       <c r="E159" t="n">
-        <v>422568</v>
+        <v>180173</v>
       </c>
       <c r="F159" t="n">
-        <v>103791</v>
+        <v>38386</v>
       </c>
       <c r="G159" t="n">
-        <v>863123</v>
+        <v>367969</v>
       </c>
       <c r="H159" t="n">
-        <v>205009</v>
+        <v>78756</v>
       </c>
       <c r="I159" t="n">
-        <v>23.75</v>
+        <v>21.4</v>
       </c>
       <c r="J159" t="n">
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>반포</t>
+          <t>보라매</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7138,40 +7138,40 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>187796</v>
+        <v>198046</v>
       </c>
       <c r="D160" t="n">
-        <v>40370</v>
+        <v>33269</v>
       </c>
       <c r="E160" t="n">
-        <v>180173</v>
+        <v>204920</v>
       </c>
       <c r="F160" t="n">
-        <v>38386</v>
+        <v>34464</v>
       </c>
       <c r="G160" t="n">
-        <v>367969</v>
+        <v>402966</v>
       </c>
       <c r="H160" t="n">
-        <v>78756</v>
+        <v>67733</v>
       </c>
       <c r="I160" t="n">
-        <v>21.4</v>
+        <v>16.81</v>
       </c>
       <c r="J160" t="n">
+        <v>4</v>
+      </c>
+      <c r="K160" t="n">
+        <v>2</v>
+      </c>
+      <c r="L160" t="n">
         <v>6</v>
-      </c>
-      <c r="K160" t="n">
-        <v>4</v>
-      </c>
-      <c r="L160" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>보라매</t>
+          <t>사가정</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7180,40 +7180,40 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>198046</v>
+        <v>470061</v>
       </c>
       <c r="D161" t="n">
-        <v>33269</v>
+        <v>107704</v>
       </c>
       <c r="E161" t="n">
-        <v>204920</v>
+        <v>471938</v>
       </c>
       <c r="F161" t="n">
-        <v>34464</v>
+        <v>108645</v>
       </c>
       <c r="G161" t="n">
-        <v>402966</v>
+        <v>941999</v>
       </c>
       <c r="H161" t="n">
-        <v>67733</v>
+        <v>216349</v>
       </c>
       <c r="I161" t="n">
-        <v>16.81</v>
+        <v>22.97</v>
       </c>
       <c r="J161" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L161" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>사가정</t>
+          <t>상도</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7222,40 +7222,40 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>470061</v>
+        <v>350932</v>
       </c>
       <c r="D162" t="n">
-        <v>107704</v>
+        <v>66852</v>
       </c>
       <c r="E162" t="n">
-        <v>471938</v>
+        <v>342231</v>
       </c>
       <c r="F162" t="n">
-        <v>108645</v>
+        <v>63792</v>
       </c>
       <c r="G162" t="n">
-        <v>941999</v>
+        <v>693163</v>
       </c>
       <c r="H162" t="n">
-        <v>216349</v>
+        <v>130644</v>
       </c>
       <c r="I162" t="n">
-        <v>22.97</v>
+        <v>18.85</v>
       </c>
       <c r="J162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K162" t="n">
         <v>3</v>
       </c>
       <c r="L162" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>상도</t>
+          <t>상봉</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7264,40 +7264,40 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>350932</v>
+        <v>508844</v>
       </c>
       <c r="D163" t="n">
-        <v>66852</v>
+        <v>79993</v>
       </c>
       <c r="E163" t="n">
-        <v>342231</v>
+        <v>490653</v>
       </c>
       <c r="F163" t="n">
-        <v>63792</v>
+        <v>76640</v>
       </c>
       <c r="G163" t="n">
-        <v>693163</v>
+        <v>999497</v>
       </c>
       <c r="H163" t="n">
-        <v>130644</v>
+        <v>156633</v>
       </c>
       <c r="I163" t="n">
-        <v>18.85</v>
+        <v>15.67</v>
       </c>
       <c r="J163" t="n">
+        <v>6</v>
+      </c>
+      <c r="K163" t="n">
+        <v>5</v>
+      </c>
+      <c r="L163" t="n">
         <v>11</v>
-      </c>
-      <c r="K163" t="n">
-        <v>3</v>
-      </c>
-      <c r="L163" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>상봉</t>
+          <t>수락산</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7306,40 +7306,40 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>508844</v>
+        <v>370617</v>
       </c>
       <c r="D164" t="n">
-        <v>79993</v>
+        <v>106791</v>
       </c>
       <c r="E164" t="n">
-        <v>490653</v>
+        <v>364921</v>
       </c>
       <c r="F164" t="n">
-        <v>76640</v>
+        <v>108072</v>
       </c>
       <c r="G164" t="n">
-        <v>999497</v>
+        <v>735538</v>
       </c>
       <c r="H164" t="n">
-        <v>156633</v>
+        <v>214863</v>
       </c>
       <c r="I164" t="n">
-        <v>15.67</v>
+        <v>29.21</v>
       </c>
       <c r="J164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K164" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L164" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>수락산</t>
+          <t>숭실대입구</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7348,40 +7348,40 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>370617</v>
+        <v>406478</v>
       </c>
       <c r="D165" t="n">
-        <v>106791</v>
+        <v>66974</v>
       </c>
       <c r="E165" t="n">
-        <v>364921</v>
+        <v>407617</v>
       </c>
       <c r="F165" t="n">
-        <v>108072</v>
+        <v>69178</v>
       </c>
       <c r="G165" t="n">
-        <v>735538</v>
+        <v>814095</v>
       </c>
       <c r="H165" t="n">
-        <v>214863</v>
+        <v>136152</v>
       </c>
       <c r="I165" t="n">
-        <v>29.21</v>
+        <v>16.72</v>
       </c>
       <c r="J165" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L165" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>숭실대입구</t>
+          <t>신대방삼거리</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7390,25 +7390,25 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>406478</v>
+        <v>433269</v>
       </c>
       <c r="D166" t="n">
-        <v>66974</v>
+        <v>95525</v>
       </c>
       <c r="E166" t="n">
-        <v>407617</v>
+        <v>414630</v>
       </c>
       <c r="F166" t="n">
-        <v>69178</v>
+        <v>98119</v>
       </c>
       <c r="G166" t="n">
-        <v>814095</v>
+        <v>847899</v>
       </c>
       <c r="H166" t="n">
-        <v>136152</v>
+        <v>193644</v>
       </c>
       <c r="I166" t="n">
-        <v>16.72</v>
+        <v>22.84</v>
       </c>
       <c r="J166" t="n">
         <v>12</v>
@@ -7423,7 +7423,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>신대방삼거리</t>
+          <t>신풍</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7432,40 +7432,40 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>433269</v>
+        <v>332724</v>
       </c>
       <c r="D167" t="n">
-        <v>95525</v>
+        <v>77373</v>
       </c>
       <c r="E167" t="n">
-        <v>414630</v>
+        <v>312174</v>
       </c>
       <c r="F167" t="n">
-        <v>98119</v>
+        <v>75981</v>
       </c>
       <c r="G167" t="n">
-        <v>847899</v>
+        <v>644898</v>
       </c>
       <c r="H167" t="n">
-        <v>193644</v>
+        <v>153354</v>
       </c>
       <c r="I167" t="n">
-        <v>22.84</v>
+        <v>23.78</v>
       </c>
       <c r="J167" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K167" t="n">
         <v>4</v>
       </c>
       <c r="L167" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>신풍</t>
+          <t>어린이대공원</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7474,40 +7474,40 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>332724</v>
+        <v>472469</v>
       </c>
       <c r="D168" t="n">
-        <v>77373</v>
+        <v>46385</v>
       </c>
       <c r="E168" t="n">
-        <v>312174</v>
+        <v>477982</v>
       </c>
       <c r="F168" t="n">
-        <v>75981</v>
+        <v>46060</v>
       </c>
       <c r="G168" t="n">
-        <v>644898</v>
+        <v>950451</v>
       </c>
       <c r="H168" t="n">
-        <v>153354</v>
+        <v>92445</v>
       </c>
       <c r="I168" t="n">
-        <v>23.78</v>
+        <v>9.73</v>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K168" t="n">
         <v>4</v>
       </c>
       <c r="L168" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>어린이대공원</t>
+          <t>온수</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7516,40 +7516,40 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>472469</v>
+        <v>283565</v>
       </c>
       <c r="D169" t="n">
-        <v>46385</v>
+        <v>44422</v>
       </c>
       <c r="E169" t="n">
-        <v>477982</v>
+        <v>262616</v>
       </c>
       <c r="F169" t="n">
-        <v>46060</v>
+        <v>42015</v>
       </c>
       <c r="G169" t="n">
-        <v>950451</v>
+        <v>546181</v>
       </c>
       <c r="H169" t="n">
-        <v>92445</v>
+        <v>86437</v>
       </c>
       <c r="I169" t="n">
-        <v>9.73</v>
+        <v>15.83</v>
       </c>
       <c r="J169" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L169" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>온수</t>
+          <t>용마산</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7558,40 +7558,40 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>283565</v>
+        <v>169622</v>
       </c>
       <c r="D170" t="n">
-        <v>44422</v>
+        <v>37080</v>
       </c>
       <c r="E170" t="n">
-        <v>262616</v>
+        <v>167384</v>
       </c>
       <c r="F170" t="n">
-        <v>42015</v>
+        <v>40314</v>
       </c>
       <c r="G170" t="n">
-        <v>546181</v>
+        <v>337006</v>
       </c>
       <c r="H170" t="n">
-        <v>86437</v>
+        <v>77394</v>
       </c>
       <c r="I170" t="n">
-        <v>15.83</v>
+        <v>22.97</v>
       </c>
       <c r="J170" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K170" t="n">
         <v>3</v>
       </c>
       <c r="L170" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>용마산</t>
+          <t>자양</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7600,40 +7600,40 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>169622</v>
+        <v>310455</v>
       </c>
       <c r="D171" t="n">
-        <v>37080</v>
+        <v>54109</v>
       </c>
       <c r="E171" t="n">
-        <v>167384</v>
+        <v>303841</v>
       </c>
       <c r="F171" t="n">
-        <v>40314</v>
+        <v>53962</v>
       </c>
       <c r="G171" t="n">
-        <v>337006</v>
+        <v>614296</v>
       </c>
       <c r="H171" t="n">
-        <v>77394</v>
+        <v>108071</v>
       </c>
       <c r="I171" t="n">
-        <v>22.97</v>
+        <v>17.59</v>
       </c>
       <c r="J171" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K171" t="n">
         <v>3</v>
       </c>
       <c r="L171" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>이수</t>
+          <t>장승배기</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7642,40 +7642,40 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>479384</v>
+        <v>269643</v>
       </c>
       <c r="D172" t="n">
-        <v>85118</v>
+        <v>71128</v>
       </c>
       <c r="E172" t="n">
-        <v>463584</v>
+        <v>262732</v>
       </c>
       <c r="F172" t="n">
-        <v>80754</v>
+        <v>71963</v>
       </c>
       <c r="G172" t="n">
-        <v>942968</v>
+        <v>532375</v>
       </c>
       <c r="H172" t="n">
-        <v>165872</v>
+        <v>143091</v>
       </c>
       <c r="I172" t="n">
-        <v>17.59</v>
+        <v>26.88</v>
       </c>
       <c r="J172" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K172" t="n">
         <v>3</v>
       </c>
       <c r="L172" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>자양</t>
+          <t>장암</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7684,40 +7684,40 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>310455</v>
+        <v>78394</v>
       </c>
       <c r="D173" t="n">
-        <v>54109</v>
+        <v>14236</v>
       </c>
       <c r="E173" t="n">
-        <v>303841</v>
+        <v>36704</v>
       </c>
       <c r="F173" t="n">
-        <v>53962</v>
+        <v>10906</v>
       </c>
       <c r="G173" t="n">
-        <v>614296</v>
+        <v>115098</v>
       </c>
       <c r="H173" t="n">
-        <v>108071</v>
+        <v>25142</v>
       </c>
       <c r="I173" t="n">
-        <v>17.59</v>
+        <v>21.84</v>
       </c>
       <c r="J173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L173" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>장승배기</t>
+          <t>중계</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7726,40 +7726,40 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>269643</v>
+        <v>424768</v>
       </c>
       <c r="D174" t="n">
-        <v>71128</v>
+        <v>99732</v>
       </c>
       <c r="E174" t="n">
-        <v>262732</v>
+        <v>390462</v>
       </c>
       <c r="F174" t="n">
-        <v>71963</v>
+        <v>96522</v>
       </c>
       <c r="G174" t="n">
-        <v>532375</v>
+        <v>815230</v>
       </c>
       <c r="H174" t="n">
-        <v>143091</v>
+        <v>196254</v>
       </c>
       <c r="I174" t="n">
-        <v>26.88</v>
+        <v>24.07</v>
       </c>
       <c r="J174" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K174" t="n">
         <v>3</v>
       </c>
       <c r="L174" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>장암</t>
+          <t>중곡</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7768,40 +7768,40 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>78394</v>
+        <v>315107</v>
       </c>
       <c r="D175" t="n">
-        <v>14236</v>
+        <v>68009</v>
       </c>
       <c r="E175" t="n">
-        <v>36704</v>
+        <v>296208</v>
       </c>
       <c r="F175" t="n">
-        <v>10906</v>
+        <v>68724</v>
       </c>
       <c r="G175" t="n">
-        <v>115098</v>
+        <v>611315</v>
       </c>
       <c r="H175" t="n">
-        <v>25142</v>
+        <v>136733</v>
       </c>
       <c r="I175" t="n">
-        <v>21.84</v>
+        <v>22.37</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L175" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>중계</t>
+          <t>중화</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7810,40 +7810,40 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>424768</v>
+        <v>312055</v>
       </c>
       <c r="D176" t="n">
-        <v>99732</v>
+        <v>68968</v>
       </c>
       <c r="E176" t="n">
-        <v>390462</v>
+        <v>304743</v>
       </c>
       <c r="F176" t="n">
-        <v>96522</v>
+        <v>68653</v>
       </c>
       <c r="G176" t="n">
-        <v>815230</v>
+        <v>616798</v>
       </c>
       <c r="H176" t="n">
-        <v>196254</v>
+        <v>137621</v>
       </c>
       <c r="I176" t="n">
-        <v>24.07</v>
+        <v>22.31</v>
       </c>
       <c r="J176" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K176" t="n">
         <v>3</v>
       </c>
       <c r="L176" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>중곡</t>
+          <t>천왕</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7852,40 +7852,40 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>315107</v>
+        <v>330062</v>
       </c>
       <c r="D177" t="n">
-        <v>68009</v>
+        <v>63126</v>
       </c>
       <c r="E177" t="n">
-        <v>296208</v>
+        <v>316349</v>
       </c>
       <c r="F177" t="n">
-        <v>68724</v>
+        <v>63456</v>
       </c>
       <c r="G177" t="n">
-        <v>611315</v>
+        <v>646411</v>
       </c>
       <c r="H177" t="n">
-        <v>136733</v>
+        <v>126582</v>
       </c>
       <c r="I177" t="n">
-        <v>22.37</v>
+        <v>19.58</v>
       </c>
       <c r="J177" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L177" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>중화</t>
+          <t>청담</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7894,40 +7894,40 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>312055</v>
+        <v>524227</v>
       </c>
       <c r="D178" t="n">
-        <v>68968</v>
+        <v>79748</v>
       </c>
       <c r="E178" t="n">
-        <v>304743</v>
+        <v>571186</v>
       </c>
       <c r="F178" t="n">
-        <v>68653</v>
+        <v>76997</v>
       </c>
       <c r="G178" t="n">
-        <v>616798</v>
+        <v>1095413</v>
       </c>
       <c r="H178" t="n">
-        <v>137621</v>
+        <v>156745</v>
       </c>
       <c r="I178" t="n">
-        <v>22.31</v>
+        <v>14.31</v>
       </c>
       <c r="J178" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L178" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>천왕</t>
+          <t>하계</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7936,40 +7936,40 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>330062</v>
+        <v>526960</v>
       </c>
       <c r="D179" t="n">
-        <v>63126</v>
+        <v>118719</v>
       </c>
       <c r="E179" t="n">
-        <v>316349</v>
+        <v>493645</v>
       </c>
       <c r="F179" t="n">
-        <v>63456</v>
+        <v>114395</v>
       </c>
       <c r="G179" t="n">
-        <v>646411</v>
+        <v>1020605</v>
       </c>
       <c r="H179" t="n">
-        <v>126582</v>
+        <v>233114</v>
       </c>
       <c r="I179" t="n">
-        <v>19.58</v>
+        <v>22.84</v>
       </c>
       <c r="J179" t="n">
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>청담</t>
+          <t>학동</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7978,124 +7978,124 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>524227</v>
+        <v>637007</v>
       </c>
       <c r="D180" t="n">
-        <v>79748</v>
+        <v>65892</v>
       </c>
       <c r="E180" t="n">
-        <v>571186</v>
+        <v>664655</v>
       </c>
       <c r="F180" t="n">
-        <v>76997</v>
+        <v>62892</v>
       </c>
       <c r="G180" t="n">
-        <v>1095413</v>
+        <v>1301662</v>
       </c>
       <c r="H180" t="n">
-        <v>156745</v>
+        <v>128784</v>
       </c>
       <c r="I180" t="n">
-        <v>14.31</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L180" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>하계</t>
+          <t>강동구청</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>526960</v>
+        <v>301276</v>
       </c>
       <c r="D181" t="n">
-        <v>118719</v>
+        <v>70703</v>
       </c>
       <c r="E181" t="n">
-        <v>493645</v>
+        <v>308602</v>
       </c>
       <c r="F181" t="n">
-        <v>114395</v>
+        <v>71501</v>
       </c>
       <c r="G181" t="n">
-        <v>1020605</v>
+        <v>609878</v>
       </c>
       <c r="H181" t="n">
-        <v>233114</v>
+        <v>142204</v>
       </c>
       <c r="I181" t="n">
-        <v>22.84</v>
+        <v>23.32</v>
       </c>
       <c r="J181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K181" t="n">
         <v>3</v>
       </c>
       <c r="L181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>학동</t>
+          <t>몽촌토성</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>637007</v>
+        <v>206879</v>
       </c>
       <c r="D182" t="n">
-        <v>65892</v>
+        <v>36663</v>
       </c>
       <c r="E182" t="n">
-        <v>664655</v>
+        <v>210579</v>
       </c>
       <c r="F182" t="n">
-        <v>62892</v>
+        <v>36012</v>
       </c>
       <c r="G182" t="n">
-        <v>1301662</v>
+        <v>417458</v>
       </c>
       <c r="H182" t="n">
-        <v>128784</v>
+        <v>72675</v>
       </c>
       <c r="I182" t="n">
-        <v>9.890000000000001</v>
+        <v>17.41</v>
       </c>
       <c r="J182" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L182" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>강동구청</t>
+          <t>문정</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8104,40 +8104,40 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>301276</v>
+        <v>595690</v>
       </c>
       <c r="D183" t="n">
-        <v>70703</v>
+        <v>66160</v>
       </c>
       <c r="E183" t="n">
-        <v>308602</v>
+        <v>620153</v>
       </c>
       <c r="F183" t="n">
-        <v>71501</v>
+        <v>66019</v>
       </c>
       <c r="G183" t="n">
-        <v>609878</v>
+        <v>1215843</v>
       </c>
       <c r="H183" t="n">
-        <v>142204</v>
+        <v>132179</v>
       </c>
       <c r="I183" t="n">
-        <v>23.32</v>
+        <v>10.87</v>
       </c>
       <c r="J183" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L183" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>몽촌토성</t>
+          <t>석촌</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8146,40 +8146,40 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>206879</v>
+        <v>244204</v>
       </c>
       <c r="D184" t="n">
-        <v>36663</v>
+        <v>56741</v>
       </c>
       <c r="E184" t="n">
-        <v>210579</v>
+        <v>284699</v>
       </c>
       <c r="F184" t="n">
-        <v>36012</v>
+        <v>59743</v>
       </c>
       <c r="G184" t="n">
-        <v>417458</v>
+        <v>528903</v>
       </c>
       <c r="H184" t="n">
-        <v>72675</v>
+        <v>116484</v>
       </c>
       <c r="I184" t="n">
-        <v>17.41</v>
+        <v>22.02</v>
       </c>
       <c r="J184" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L184" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>문정</t>
+          <t>송파</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8188,40 +8188,40 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>595690</v>
+        <v>275169</v>
       </c>
       <c r="D185" t="n">
-        <v>66160</v>
+        <v>69511</v>
       </c>
       <c r="E185" t="n">
-        <v>620153</v>
+        <v>269774</v>
       </c>
       <c r="F185" t="n">
-        <v>66019</v>
+        <v>68579</v>
       </c>
       <c r="G185" t="n">
-        <v>1215843</v>
+        <v>544943</v>
       </c>
       <c r="H185" t="n">
-        <v>132179</v>
+        <v>138090</v>
       </c>
       <c r="I185" t="n">
-        <v>10.87</v>
+        <v>25.34</v>
       </c>
       <c r="J185" t="n">
+        <v>4</v>
+      </c>
+      <c r="K185" t="n">
+        <v>4</v>
+      </c>
+      <c r="L185" t="n">
         <v>8</v>
-      </c>
-      <c r="K185" t="n">
-        <v>4</v>
-      </c>
-      <c r="L185" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>석촌</t>
+          <t>암사</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8230,40 +8230,40 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>244204</v>
+        <v>510235</v>
       </c>
       <c r="D186" t="n">
-        <v>56741</v>
+        <v>112483</v>
       </c>
       <c r="E186" t="n">
-        <v>284699</v>
+        <v>461278</v>
       </c>
       <c r="F186" t="n">
-        <v>59743</v>
+        <v>110725</v>
       </c>
       <c r="G186" t="n">
-        <v>528903</v>
+        <v>971513</v>
       </c>
       <c r="H186" t="n">
-        <v>116484</v>
+        <v>223208</v>
       </c>
       <c r="I186" t="n">
-        <v>22.02</v>
+        <v>22.98</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K186" t="n">
         <v>3</v>
       </c>
       <c r="L186" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>송파</t>
+          <t>암사역사공원</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8272,40 +8272,40 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>275169</v>
+        <v>179560</v>
       </c>
       <c r="D187" t="n">
-        <v>69511</v>
+        <v>34333</v>
       </c>
       <c r="E187" t="n">
-        <v>269774</v>
+        <v>159043</v>
       </c>
       <c r="F187" t="n">
-        <v>68579</v>
+        <v>33319</v>
       </c>
       <c r="G187" t="n">
-        <v>544943</v>
+        <v>338603</v>
       </c>
       <c r="H187" t="n">
-        <v>138090</v>
+        <v>67652</v>
       </c>
       <c r="I187" t="n">
-        <v>25.34</v>
+        <v>19.98</v>
       </c>
       <c r="J187" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K187" t="n">
         <v>4</v>
       </c>
       <c r="L187" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>암사</t>
+          <t>장지</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8314,124 +8314,124 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>510235</v>
+        <v>499917</v>
       </c>
       <c r="D188" t="n">
-        <v>112483</v>
+        <v>90185</v>
       </c>
       <c r="E188" t="n">
-        <v>461278</v>
+        <v>462047</v>
       </c>
       <c r="F188" t="n">
-        <v>110725</v>
+        <v>85257</v>
       </c>
       <c r="G188" t="n">
-        <v>971513</v>
+        <v>961964</v>
       </c>
       <c r="H188" t="n">
-        <v>223208</v>
+        <v>175442</v>
       </c>
       <c r="I188" t="n">
-        <v>22.98</v>
+        <v>18.24</v>
       </c>
       <c r="J188" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L188" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>암사역사공원</t>
+          <t>가양</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>179560</v>
+        <v>640487</v>
       </c>
       <c r="D189" t="n">
-        <v>34333</v>
+        <v>143821</v>
       </c>
       <c r="E189" t="n">
-        <v>159043</v>
+        <v>624800</v>
       </c>
       <c r="F189" t="n">
-        <v>33319</v>
+        <v>140972</v>
       </c>
       <c r="G189" t="n">
-        <v>338603</v>
+        <v>1265287</v>
       </c>
       <c r="H189" t="n">
-        <v>67652</v>
+        <v>284793</v>
       </c>
       <c r="I189" t="n">
-        <v>19.98</v>
+        <v>22.51</v>
       </c>
       <c r="J189" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K189" t="n">
         <v>4</v>
       </c>
       <c r="L189" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>장지</t>
+          <t>개화</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>499917</v>
+        <v>77648</v>
       </c>
       <c r="D190" t="n">
-        <v>90185</v>
+        <v>13560</v>
       </c>
       <c r="E190" t="n">
-        <v>462047</v>
+        <v>53392</v>
       </c>
       <c r="F190" t="n">
-        <v>85257</v>
+        <v>10971</v>
       </c>
       <c r="G190" t="n">
-        <v>961964</v>
+        <v>131040</v>
       </c>
       <c r="H190" t="n">
-        <v>175442</v>
+        <v>24531</v>
       </c>
       <c r="I190" t="n">
-        <v>18.24</v>
+        <v>18.72</v>
       </c>
       <c r="J190" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K190" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L190" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>가양</t>
+          <t>공항시장</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8440,40 +8440,40 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>640487</v>
+        <v>87644</v>
       </c>
       <c r="D191" t="n">
-        <v>143821</v>
+        <v>24745</v>
       </c>
       <c r="E191" t="n">
-        <v>624800</v>
+        <v>93641</v>
       </c>
       <c r="F191" t="n">
-        <v>140972</v>
+        <v>26627</v>
       </c>
       <c r="G191" t="n">
-        <v>1265287</v>
+        <v>181285</v>
       </c>
       <c r="H191" t="n">
-        <v>284793</v>
+        <v>51372</v>
       </c>
       <c r="I191" t="n">
-        <v>22.51</v>
+        <v>28.34</v>
       </c>
       <c r="J191" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L191" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>개화</t>
+          <t>구반포</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8482,40 +8482,40 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>77648</v>
+        <v>40364</v>
       </c>
       <c r="D192" t="n">
-        <v>13560</v>
+        <v>9863</v>
       </c>
       <c r="E192" t="n">
-        <v>53392</v>
+        <v>38871</v>
       </c>
       <c r="F192" t="n">
-        <v>10971</v>
+        <v>9737</v>
       </c>
       <c r="G192" t="n">
-        <v>131040</v>
+        <v>79235</v>
       </c>
       <c r="H192" t="n">
-        <v>24531</v>
+        <v>19600</v>
       </c>
       <c r="I192" t="n">
-        <v>18.72</v>
+        <v>24.74</v>
       </c>
       <c r="J192" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L192" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>공항시장</t>
+          <t>국회의사당</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8524,40 +8524,40 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>87644</v>
+        <v>474200</v>
       </c>
       <c r="D193" t="n">
-        <v>24745</v>
+        <v>64371</v>
       </c>
       <c r="E193" t="n">
-        <v>93641</v>
+        <v>484139</v>
       </c>
       <c r="F193" t="n">
-        <v>26627</v>
+        <v>57952</v>
       </c>
       <c r="G193" t="n">
-        <v>181285</v>
+        <v>958339</v>
       </c>
       <c r="H193" t="n">
-        <v>51372</v>
+        <v>122323</v>
       </c>
       <c r="I193" t="n">
-        <v>28.34</v>
+        <v>12.76</v>
       </c>
       <c r="J193" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L193" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>구반포</t>
+          <t>노들</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8566,40 +8566,40 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>40364</v>
+        <v>147810</v>
       </c>
       <c r="D194" t="n">
-        <v>9863</v>
+        <v>34964</v>
       </c>
       <c r="E194" t="n">
-        <v>38871</v>
+        <v>124278</v>
       </c>
       <c r="F194" t="n">
-        <v>9737</v>
+        <v>32133</v>
       </c>
       <c r="G194" t="n">
-        <v>79235</v>
+        <v>272088</v>
       </c>
       <c r="H194" t="n">
-        <v>19600</v>
+        <v>67097</v>
       </c>
       <c r="I194" t="n">
-        <v>24.74</v>
+        <v>24.66</v>
       </c>
       <c r="J194" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K194" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L194" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>국회의사당</t>
+          <t>노량진</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8608,40 +8608,40 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>474200</v>
+        <v>773829</v>
       </c>
       <c r="D195" t="n">
-        <v>64371</v>
+        <v>91179</v>
       </c>
       <c r="E195" t="n">
-        <v>484139</v>
+        <v>763448</v>
       </c>
       <c r="F195" t="n">
-        <v>57952</v>
+        <v>90996</v>
       </c>
       <c r="G195" t="n">
-        <v>958339</v>
+        <v>1537277</v>
       </c>
       <c r="H195" t="n">
-        <v>122323</v>
+        <v>182175</v>
       </c>
       <c r="I195" t="n">
-        <v>12.76</v>
+        <v>11.85</v>
       </c>
       <c r="J195" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K195" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L195" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>노들</t>
+          <t>등촌</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8650,40 +8650,40 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>147810</v>
+        <v>349933</v>
       </c>
       <c r="D196" t="n">
-        <v>34964</v>
+        <v>90216</v>
       </c>
       <c r="E196" t="n">
-        <v>124278</v>
+        <v>335943</v>
       </c>
       <c r="F196" t="n">
-        <v>32133</v>
+        <v>91029</v>
       </c>
       <c r="G196" t="n">
-        <v>272088</v>
+        <v>685876</v>
       </c>
       <c r="H196" t="n">
-        <v>67097</v>
+        <v>181245</v>
       </c>
       <c r="I196" t="n">
-        <v>24.66</v>
+        <v>26.43</v>
       </c>
       <c r="J196" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K196" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L196" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>노량진</t>
+          <t>마곡나루</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8692,40 +8692,40 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>773829</v>
+        <v>399673</v>
       </c>
       <c r="D197" t="n">
-        <v>91179</v>
+        <v>40007</v>
       </c>
       <c r="E197" t="n">
-        <v>763448</v>
+        <v>392298</v>
       </c>
       <c r="F197" t="n">
-        <v>90996</v>
+        <v>38995</v>
       </c>
       <c r="G197" t="n">
-        <v>1537277</v>
+        <v>791971</v>
       </c>
       <c r="H197" t="n">
-        <v>182175</v>
+        <v>79002</v>
       </c>
       <c r="I197" t="n">
-        <v>11.85</v>
+        <v>9.98</v>
       </c>
       <c r="J197" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K197" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L197" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>등촌</t>
+          <t>사평</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8734,40 +8734,40 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>349933</v>
+        <v>117034</v>
       </c>
       <c r="D198" t="n">
-        <v>90216</v>
+        <v>25406</v>
       </c>
       <c r="E198" t="n">
-        <v>335943</v>
+        <v>112799</v>
       </c>
       <c r="F198" t="n">
-        <v>91029</v>
+        <v>25429</v>
       </c>
       <c r="G198" t="n">
-        <v>685876</v>
+        <v>229833</v>
       </c>
       <c r="H198" t="n">
-        <v>181245</v>
+        <v>50835</v>
       </c>
       <c r="I198" t="n">
-        <v>26.43</v>
+        <v>22.12</v>
       </c>
       <c r="J198" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L198" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>마곡나루</t>
+          <t>샛강</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8776,40 +8776,40 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>399673</v>
+        <v>183836</v>
       </c>
       <c r="D199" t="n">
-        <v>40007</v>
+        <v>30690</v>
       </c>
       <c r="E199" t="n">
-        <v>392298</v>
+        <v>181903</v>
       </c>
       <c r="F199" t="n">
-        <v>38995</v>
+        <v>30353</v>
       </c>
       <c r="G199" t="n">
-        <v>791971</v>
+        <v>365739</v>
       </c>
       <c r="H199" t="n">
-        <v>79002</v>
+        <v>61043</v>
       </c>
       <c r="I199" t="n">
-        <v>9.98</v>
+        <v>16.69</v>
       </c>
       <c r="J199" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L199" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>사평</t>
+          <t>선유도</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8818,40 +8818,40 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>117034</v>
+        <v>248011</v>
       </c>
       <c r="D200" t="n">
-        <v>25406</v>
+        <v>33075</v>
       </c>
       <c r="E200" t="n">
-        <v>112799</v>
+        <v>232403</v>
       </c>
       <c r="F200" t="n">
-        <v>25429</v>
+        <v>32261</v>
       </c>
       <c r="G200" t="n">
-        <v>229833</v>
+        <v>480414</v>
       </c>
       <c r="H200" t="n">
-        <v>50835</v>
+        <v>65336</v>
       </c>
       <c r="I200" t="n">
-        <v>22.12</v>
+        <v>13.6</v>
       </c>
       <c r="J200" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K200" t="n">
         <v>4</v>
       </c>
       <c r="L200" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>샛강</t>
+          <t>신논현</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8860,40 +8860,40 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>183836</v>
+        <v>916236</v>
       </c>
       <c r="D201" t="n">
-        <v>30690</v>
+        <v>56569</v>
       </c>
       <c r="E201" t="n">
-        <v>181903</v>
+        <v>916217</v>
       </c>
       <c r="F201" t="n">
-        <v>30353</v>
+        <v>55036</v>
       </c>
       <c r="G201" t="n">
-        <v>365739</v>
+        <v>1832453</v>
       </c>
       <c r="H201" t="n">
-        <v>61043</v>
+        <v>111605</v>
       </c>
       <c r="I201" t="n">
-        <v>16.69</v>
+        <v>6.09</v>
       </c>
       <c r="J201" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L201" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>선유도</t>
+          <t>신목동</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8902,40 +8902,40 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>248011</v>
+        <v>127417</v>
       </c>
       <c r="D202" t="n">
-        <v>33075</v>
+        <v>26008</v>
       </c>
       <c r="E202" t="n">
-        <v>232403</v>
+        <v>112498</v>
       </c>
       <c r="F202" t="n">
-        <v>32261</v>
+        <v>24721</v>
       </c>
       <c r="G202" t="n">
-        <v>480414</v>
+        <v>239915</v>
       </c>
       <c r="H202" t="n">
-        <v>65336</v>
+        <v>50729</v>
       </c>
       <c r="I202" t="n">
-        <v>13.6</v>
+        <v>21.14</v>
       </c>
       <c r="J202" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K202" t="n">
         <v>4</v>
       </c>
       <c r="L202" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>신논현</t>
+          <t>신반포</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8944,40 +8944,40 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>916236</v>
+        <v>125990</v>
       </c>
       <c r="D203" t="n">
-        <v>56569</v>
+        <v>29239</v>
       </c>
       <c r="E203" t="n">
-        <v>916217</v>
+        <v>124035</v>
       </c>
       <c r="F203" t="n">
-        <v>55036</v>
+        <v>29308</v>
       </c>
       <c r="G203" t="n">
-        <v>1832453</v>
+        <v>250025</v>
       </c>
       <c r="H203" t="n">
-        <v>111605</v>
+        <v>58547</v>
       </c>
       <c r="I203" t="n">
-        <v>6.09</v>
+        <v>23.42</v>
       </c>
       <c r="J203" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K203" t="n">
         <v>4</v>
       </c>
       <c r="L203" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>신목동</t>
+          <t>신방화</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8986,40 +8986,40 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>127417</v>
+        <v>202870</v>
       </c>
       <c r="D204" t="n">
-        <v>26008</v>
+        <v>49967</v>
       </c>
       <c r="E204" t="n">
-        <v>112498</v>
+        <v>198595</v>
       </c>
       <c r="F204" t="n">
-        <v>24721</v>
+        <v>50170</v>
       </c>
       <c r="G204" t="n">
-        <v>239915</v>
+        <v>401465</v>
       </c>
       <c r="H204" t="n">
-        <v>50729</v>
+        <v>100137</v>
       </c>
       <c r="I204" t="n">
-        <v>21.14</v>
+        <v>24.94</v>
       </c>
       <c r="J204" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K204" t="n">
         <v>4</v>
       </c>
       <c r="L204" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>신반포</t>
+          <t>양천향교</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9028,40 +9028,40 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>125990</v>
+        <v>289659</v>
       </c>
       <c r="D205" t="n">
-        <v>29239</v>
+        <v>49752</v>
       </c>
       <c r="E205" t="n">
-        <v>124035</v>
+        <v>294136</v>
       </c>
       <c r="F205" t="n">
-        <v>29308</v>
+        <v>49308</v>
       </c>
       <c r="G205" t="n">
-        <v>250025</v>
+        <v>583795</v>
       </c>
       <c r="H205" t="n">
-        <v>58547</v>
+        <v>99060</v>
       </c>
       <c r="I205" t="n">
-        <v>23.42</v>
+        <v>16.97</v>
       </c>
       <c r="J205" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K205" t="n">
         <v>4</v>
       </c>
       <c r="L205" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>신방화</t>
+          <t>염창</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9070,40 +9070,40 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>202870</v>
+        <v>514529</v>
       </c>
       <c r="D206" t="n">
-        <v>49967</v>
+        <v>80870</v>
       </c>
       <c r="E206" t="n">
-        <v>198595</v>
+        <v>492565</v>
       </c>
       <c r="F206" t="n">
-        <v>50170</v>
+        <v>78794</v>
       </c>
       <c r="G206" t="n">
-        <v>401465</v>
+        <v>1007094</v>
       </c>
       <c r="H206" t="n">
-        <v>100137</v>
+        <v>159664</v>
       </c>
       <c r="I206" t="n">
-        <v>24.94</v>
+        <v>15.85</v>
       </c>
       <c r="J206" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K206" t="n">
         <v>4</v>
       </c>
       <c r="L206" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>양천향교</t>
+          <t>증미</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9112,40 +9112,40 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>289659</v>
+        <v>219073</v>
       </c>
       <c r="D207" t="n">
-        <v>49752</v>
+        <v>38743</v>
       </c>
       <c r="E207" t="n">
-        <v>294136</v>
+        <v>210572</v>
       </c>
       <c r="F207" t="n">
-        <v>49308</v>
+        <v>38823</v>
       </c>
       <c r="G207" t="n">
-        <v>583795</v>
+        <v>429645</v>
       </c>
       <c r="H207" t="n">
-        <v>99060</v>
+        <v>77566</v>
       </c>
       <c r="I207" t="n">
-        <v>16.97</v>
+        <v>18.05</v>
       </c>
       <c r="J207" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L207" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>염창</t>
+          <t>흑석</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9154,880 +9154,880 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>514529</v>
+        <v>274749</v>
       </c>
       <c r="D208" t="n">
-        <v>80870</v>
+        <v>60214</v>
       </c>
       <c r="E208" t="n">
-        <v>492565</v>
+        <v>279485</v>
       </c>
       <c r="F208" t="n">
-        <v>78794</v>
+        <v>60496</v>
       </c>
       <c r="G208" t="n">
-        <v>1007094</v>
+        <v>554234</v>
       </c>
       <c r="H208" t="n">
-        <v>159664</v>
+        <v>120710</v>
       </c>
       <c r="I208" t="n">
-        <v>15.85</v>
+        <v>21.78</v>
       </c>
       <c r="J208" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K208" t="n">
         <v>4</v>
       </c>
       <c r="L208" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>증미</t>
+          <t>가락시장</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>219073</v>
+        <v>499142</v>
       </c>
       <c r="D209" t="n">
-        <v>38743</v>
+        <v>149493</v>
       </c>
       <c r="E209" t="n">
-        <v>210572</v>
+        <v>517546</v>
       </c>
       <c r="F209" t="n">
-        <v>38823</v>
+        <v>148748</v>
       </c>
       <c r="G209" t="n">
-        <v>429645</v>
+        <v>1016688</v>
       </c>
       <c r="H209" t="n">
-        <v>77566</v>
+        <v>298241</v>
       </c>
       <c r="I209" t="n">
-        <v>18.05</v>
+        <v>29.33</v>
       </c>
       <c r="J209" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K209" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L209" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>흑석</t>
+          <t>건대입구</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>274749</v>
+        <v>1514545</v>
       </c>
       <c r="D210" t="n">
-        <v>60214</v>
+        <v>160449</v>
       </c>
       <c r="E210" t="n">
-        <v>279485</v>
+        <v>1584989</v>
       </c>
       <c r="F210" t="n">
-        <v>60496</v>
+        <v>158811</v>
       </c>
       <c r="G210" t="n">
-        <v>554234</v>
+        <v>3099534</v>
       </c>
       <c r="H210" t="n">
-        <v>120710</v>
+        <v>319260</v>
       </c>
       <c r="I210" t="n">
-        <v>21.78</v>
+        <v>10.3</v>
       </c>
       <c r="J210" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K210" t="n">
         <v>4</v>
       </c>
       <c r="L210" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>가락시장</t>
+          <t>고속터미널</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>3,7,9</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>499142</v>
+        <v>2526704</v>
       </c>
       <c r="D211" t="n">
-        <v>149493</v>
+        <v>378399</v>
       </c>
       <c r="E211" t="n">
-        <v>517546</v>
+        <v>2523557</v>
       </c>
       <c r="F211" t="n">
-        <v>148748</v>
+        <v>369982</v>
       </c>
       <c r="G211" t="n">
-        <v>1016688</v>
+        <v>5050261</v>
       </c>
       <c r="H211" t="n">
-        <v>298241</v>
+        <v>748381</v>
       </c>
       <c r="I211" t="n">
-        <v>29.33</v>
+        <v>14.82</v>
       </c>
       <c r="J211" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="K211" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L211" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>건대입구</t>
+          <t>공덕</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1514545</v>
+        <v>948702</v>
       </c>
       <c r="D212" t="n">
-        <v>160449</v>
+        <v>133694</v>
       </c>
       <c r="E212" t="n">
-        <v>1584989</v>
+        <v>949611</v>
       </c>
       <c r="F212" t="n">
-        <v>158811</v>
+        <v>125787</v>
       </c>
       <c r="G212" t="n">
-        <v>3099534</v>
+        <v>1898313</v>
       </c>
       <c r="H212" t="n">
-        <v>319260</v>
+        <v>259481</v>
       </c>
       <c r="I212" t="n">
-        <v>10.3</v>
+        <v>13.67</v>
       </c>
       <c r="J212" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K212" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L212" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>고속터미널</t>
+          <t>교대</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3,7,9</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2526704</v>
+        <v>1330717</v>
       </c>
       <c r="D213" t="n">
-        <v>378399</v>
+        <v>237048</v>
       </c>
       <c r="E213" t="n">
-        <v>2523557</v>
+        <v>1305183</v>
       </c>
       <c r="F213" t="n">
-        <v>369982</v>
+        <v>227756</v>
       </c>
       <c r="G213" t="n">
-        <v>5050261</v>
+        <v>2635900</v>
       </c>
       <c r="H213" t="n">
-        <v>748381</v>
+        <v>464804</v>
       </c>
       <c r="I213" t="n">
-        <v>14.82</v>
+        <v>17.63</v>
       </c>
       <c r="J213" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L213" t="n">
-        <v>87</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>공덕</t>
+          <t>군자</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>948702</v>
+        <v>785877</v>
       </c>
       <c r="D214" t="n">
-        <v>133694</v>
+        <v>132473</v>
       </c>
       <c r="E214" t="n">
-        <v>949611</v>
+        <v>726097</v>
       </c>
       <c r="F214" t="n">
-        <v>125787</v>
+        <v>123065</v>
       </c>
       <c r="G214" t="n">
-        <v>1898313</v>
+        <v>1511974</v>
       </c>
       <c r="H214" t="n">
-        <v>259481</v>
+        <v>255538</v>
       </c>
       <c r="I214" t="n">
-        <v>13.67</v>
+        <v>16.9</v>
       </c>
       <c r="J214" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K214" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L214" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>교대</t>
+          <t>김포공항</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1330717</v>
+        <v>530431</v>
       </c>
       <c r="D215" t="n">
-        <v>237048</v>
+        <v>70323</v>
       </c>
       <c r="E215" t="n">
-        <v>1305183</v>
+        <v>557489</v>
       </c>
       <c r="F215" t="n">
-        <v>227756</v>
+        <v>71426</v>
       </c>
       <c r="G215" t="n">
-        <v>2635900</v>
+        <v>1087920</v>
       </c>
       <c r="H215" t="n">
-        <v>464804</v>
+        <v>141749</v>
       </c>
       <c r="I215" t="n">
-        <v>17.63</v>
+        <v>13.03</v>
       </c>
       <c r="J215" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K215" t="n">
         <v>5</v>
       </c>
       <c r="L215" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>군자</t>
+          <t>노원</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>785877</v>
+        <v>1278860</v>
       </c>
       <c r="D216" t="n">
-        <v>132473</v>
+        <v>265098</v>
       </c>
       <c r="E216" t="n">
-        <v>726097</v>
+        <v>1389731</v>
       </c>
       <c r="F216" t="n">
-        <v>123065</v>
+        <v>265470</v>
       </c>
       <c r="G216" t="n">
-        <v>1511974</v>
+        <v>2668591</v>
       </c>
       <c r="H216" t="n">
-        <v>255538</v>
+        <v>530568</v>
       </c>
       <c r="I216" t="n">
-        <v>16.9</v>
+        <v>19.88</v>
       </c>
       <c r="J216" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K216" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L216" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>김포공항</t>
+          <t>당산</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>530431</v>
+        <v>1086434</v>
       </c>
       <c r="D217" t="n">
-        <v>70323</v>
+        <v>134157</v>
       </c>
       <c r="E217" t="n">
-        <v>557489</v>
+        <v>1153742</v>
       </c>
       <c r="F217" t="n">
-        <v>71426</v>
+        <v>134381</v>
       </c>
       <c r="G217" t="n">
-        <v>1087920</v>
+        <v>2240176</v>
       </c>
       <c r="H217" t="n">
-        <v>141749</v>
+        <v>268538</v>
       </c>
       <c r="I217" t="n">
-        <v>13.03</v>
+        <v>11.99</v>
       </c>
       <c r="J217" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K217" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L217" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>노원</t>
+          <t>대림</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1278860</v>
+        <v>989147</v>
       </c>
       <c r="D218" t="n">
-        <v>265098</v>
+        <v>182965</v>
       </c>
       <c r="E218" t="n">
-        <v>1389731</v>
+        <v>1006134</v>
       </c>
       <c r="F218" t="n">
-        <v>265470</v>
+        <v>186565</v>
       </c>
       <c r="G218" t="n">
-        <v>2668591</v>
+        <v>1995281</v>
       </c>
       <c r="H218" t="n">
-        <v>530568</v>
+        <v>369530</v>
       </c>
       <c r="I218" t="n">
-        <v>19.88</v>
+        <v>18.52</v>
       </c>
       <c r="J218" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K218" t="n">
         <v>7</v>
       </c>
       <c r="L218" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>당산</t>
+          <t>동대문</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1086434</v>
+        <v>932876</v>
       </c>
       <c r="D219" t="n">
-        <v>134157</v>
+        <v>279178</v>
       </c>
       <c r="E219" t="n">
-        <v>1153742</v>
+        <v>940024</v>
       </c>
       <c r="F219" t="n">
-        <v>134381</v>
+        <v>274204</v>
       </c>
       <c r="G219" t="n">
-        <v>2240176</v>
+        <v>1872900</v>
       </c>
       <c r="H219" t="n">
-        <v>268538</v>
+        <v>553382</v>
       </c>
       <c r="I219" t="n">
-        <v>11.99</v>
+        <v>29.55</v>
       </c>
       <c r="J219" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K219" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L219" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>대림</t>
+          <t>동대문역사문화공원</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,4,5</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>989147</v>
+        <v>1099733</v>
       </c>
       <c r="D220" t="n">
-        <v>182965</v>
+        <v>133930</v>
       </c>
       <c r="E220" t="n">
-        <v>1006134</v>
+        <v>1106872</v>
       </c>
       <c r="F220" t="n">
-        <v>186565</v>
+        <v>132983</v>
       </c>
       <c r="G220" t="n">
-        <v>1995281</v>
+        <v>2206605</v>
       </c>
       <c r="H220" t="n">
-        <v>369530</v>
+        <v>266913</v>
       </c>
       <c r="I220" t="n">
-        <v>18.52</v>
+        <v>12.1</v>
       </c>
       <c r="J220" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K220" t="n">
         <v>7</v>
       </c>
       <c r="L220" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>동대문</t>
+          <t>동묘앞</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>932876</v>
+        <v>570181</v>
       </c>
       <c r="D221" t="n">
-        <v>279178</v>
+        <v>229441</v>
       </c>
       <c r="E221" t="n">
-        <v>940024</v>
+        <v>579997</v>
       </c>
       <c r="F221" t="n">
-        <v>274204</v>
+        <v>226056</v>
       </c>
       <c r="G221" t="n">
-        <v>1872900</v>
+        <v>1150178</v>
       </c>
       <c r="H221" t="n">
-        <v>553382</v>
+        <v>455497</v>
       </c>
       <c r="I221" t="n">
-        <v>29.55</v>
+        <v>39.6</v>
       </c>
       <c r="J221" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K221" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L221" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>동대문역사문화공원</t>
+          <t>동작</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2,4,5</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1099733</v>
+        <v>109569</v>
       </c>
       <c r="D222" t="n">
-        <v>133930</v>
+        <v>29737</v>
       </c>
       <c r="E222" t="n">
-        <v>1106872</v>
+        <v>104756</v>
       </c>
       <c r="F222" t="n">
-        <v>132983</v>
+        <v>28535</v>
       </c>
       <c r="G222" t="n">
-        <v>2206605</v>
+        <v>214325</v>
       </c>
       <c r="H222" t="n">
-        <v>266913</v>
+        <v>58272</v>
       </c>
       <c r="I222" t="n">
-        <v>12.1</v>
+        <v>27.19</v>
       </c>
       <c r="J222" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K222" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L222" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>동묘앞</t>
+          <t>불광</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>570181</v>
+        <v>628909</v>
       </c>
       <c r="D223" t="n">
-        <v>229441</v>
+        <v>190903</v>
       </c>
       <c r="E223" t="n">
-        <v>579997</v>
+        <v>657152</v>
       </c>
       <c r="F223" t="n">
-        <v>226056</v>
+        <v>198424</v>
       </c>
       <c r="G223" t="n">
-        <v>1150178</v>
+        <v>1286061</v>
       </c>
       <c r="H223" t="n">
-        <v>455497</v>
+        <v>389327</v>
       </c>
       <c r="I223" t="n">
-        <v>39.6</v>
+        <v>30.27</v>
       </c>
       <c r="J223" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K223" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L223" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>동작</t>
+          <t>사당</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>109569</v>
+        <v>1988942</v>
       </c>
       <c r="D224" t="n">
-        <v>29737</v>
+        <v>323350</v>
       </c>
       <c r="E224" t="n">
-        <v>104756</v>
+        <v>2017546</v>
       </c>
       <c r="F224" t="n">
-        <v>28535</v>
+        <v>317669</v>
       </c>
       <c r="G224" t="n">
-        <v>214325</v>
+        <v>4006488</v>
       </c>
       <c r="H224" t="n">
-        <v>58272</v>
+        <v>641019</v>
       </c>
       <c r="I224" t="n">
-        <v>27.19</v>
+        <v>16</v>
       </c>
       <c r="J224" t="n">
         <v>21</v>
       </c>
       <c r="K224" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L224" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>불광</t>
+          <t>삼각지</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>628909</v>
+        <v>860919</v>
       </c>
       <c r="D225" t="n">
-        <v>190903</v>
+        <v>92672</v>
       </c>
       <c r="E225" t="n">
-        <v>657152</v>
+        <v>871584</v>
       </c>
       <c r="F225" t="n">
-        <v>198424</v>
+        <v>88554</v>
       </c>
       <c r="G225" t="n">
-        <v>1286061</v>
+        <v>1732503</v>
       </c>
       <c r="H225" t="n">
-        <v>389327</v>
+        <v>181226</v>
       </c>
       <c r="I225" t="n">
-        <v>30.27</v>
+        <v>20.97</v>
       </c>
       <c r="J225" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K225" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L225" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>사당</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1988942</v>
+        <v>2155185</v>
       </c>
       <c r="D226" t="n">
-        <v>323350</v>
+        <v>271561</v>
       </c>
       <c r="E226" t="n">
-        <v>2017546</v>
+        <v>2358354</v>
       </c>
       <c r="F226" t="n">
-        <v>317669</v>
+        <v>275553</v>
       </c>
       <c r="G226" t="n">
-        <v>4006488</v>
+        <v>4513539</v>
       </c>
       <c r="H226" t="n">
-        <v>641019</v>
+        <v>547114</v>
       </c>
       <c r="I226" t="n">
-        <v>16</v>
+        <v>12.12</v>
       </c>
       <c r="J226" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K226" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L226" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>삼각지</t>
+          <t>시청</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>860919</v>
+        <v>1504288</v>
       </c>
       <c r="D227" t="n">
-        <v>92672</v>
+        <v>170657</v>
       </c>
       <c r="E227" t="n">
-        <v>871584</v>
+        <v>1458576</v>
       </c>
       <c r="F227" t="n">
-        <v>88554</v>
+        <v>162682</v>
       </c>
       <c r="G227" t="n">
-        <v>1732503</v>
+        <v>2962864</v>
       </c>
       <c r="H227" t="n">
-        <v>181226</v>
+        <v>333339</v>
       </c>
       <c r="I227" t="n">
-        <v>20.97</v>
+        <v>11.25</v>
       </c>
       <c r="J227" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K227" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L227" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>신당</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2155185</v>
+        <v>687585</v>
       </c>
       <c r="D228" t="n">
-        <v>271561</v>
+        <v>132734</v>
       </c>
       <c r="E228" t="n">
-        <v>2358354</v>
+        <v>712506</v>
       </c>
       <c r="F228" t="n">
-        <v>275553</v>
+        <v>133571</v>
       </c>
       <c r="G228" t="n">
-        <v>4513539</v>
+        <v>1400091</v>
       </c>
       <c r="H228" t="n">
-        <v>547114</v>
+        <v>266305</v>
       </c>
       <c r="I228" t="n">
-        <v>12.12</v>
+        <v>19.02</v>
       </c>
       <c r="J228" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K228" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L228" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>시청</t>
+          <t>신설동</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10036,124 +10036,124 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1504288</v>
+        <v>525201</v>
       </c>
       <c r="D229" t="n">
-        <v>170657</v>
+        <v>154123</v>
       </c>
       <c r="E229" t="n">
-        <v>1458576</v>
+        <v>508111</v>
       </c>
       <c r="F229" t="n">
-        <v>162682</v>
+        <v>152088</v>
       </c>
       <c r="G229" t="n">
-        <v>2962864</v>
+        <v>1033312</v>
       </c>
       <c r="H229" t="n">
-        <v>333339</v>
+        <v>306211</v>
       </c>
       <c r="I229" t="n">
-        <v>11.25</v>
+        <v>29.63</v>
       </c>
       <c r="J229" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L229" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>신당</t>
+          <t>약수</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>687585</v>
+        <v>485940</v>
       </c>
       <c r="D230" t="n">
-        <v>132734</v>
+        <v>106219</v>
       </c>
       <c r="E230" t="n">
-        <v>712506</v>
+        <v>473228</v>
       </c>
       <c r="F230" t="n">
-        <v>133571</v>
+        <v>100590</v>
       </c>
       <c r="G230" t="n">
-        <v>1400091</v>
+        <v>959168</v>
       </c>
       <c r="H230" t="n">
-        <v>266305</v>
+        <v>206809</v>
       </c>
       <c r="I230" t="n">
-        <v>19.02</v>
+        <v>21.56</v>
       </c>
       <c r="J230" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K230" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L230" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>신설동</t>
+          <t>여의도</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>525201</v>
+        <v>1643461</v>
       </c>
       <c r="D231" t="n">
-        <v>154123</v>
+        <v>114204</v>
       </c>
       <c r="E231" t="n">
-        <v>508111</v>
+        <v>1652659</v>
       </c>
       <c r="F231" t="n">
-        <v>152088</v>
+        <v>107101</v>
       </c>
       <c r="G231" t="n">
-        <v>1033312</v>
+        <v>3296120</v>
       </c>
       <c r="H231" t="n">
-        <v>306211</v>
+        <v>221305</v>
       </c>
       <c r="I231" t="n">
-        <v>29.63</v>
+        <v>6.71</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K231" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L231" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>약수</t>
+          <t>연신내</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10162,124 +10162,124 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>485940</v>
+        <v>1036393</v>
       </c>
       <c r="D232" t="n">
-        <v>106219</v>
+        <v>264167</v>
       </c>
       <c r="E232" t="n">
-        <v>473228</v>
+        <v>985977</v>
       </c>
       <c r="F232" t="n">
-        <v>100590</v>
+        <v>255205</v>
       </c>
       <c r="G232" t="n">
-        <v>959168</v>
+        <v>2022370</v>
       </c>
       <c r="H232" t="n">
-        <v>206809</v>
+        <v>519372</v>
       </c>
       <c r="I232" t="n">
-        <v>21.56</v>
+        <v>25.68</v>
       </c>
       <c r="J232" t="n">
+        <v>10</v>
+      </c>
+      <c r="K232" t="n">
+        <v>3</v>
+      </c>
+      <c r="L232" t="n">
         <v>13</v>
-      </c>
-      <c r="K232" t="n">
-        <v>6</v>
-      </c>
-      <c r="L232" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>여의도</t>
+          <t>영등포구청</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1643461</v>
+        <v>758286</v>
       </c>
       <c r="D233" t="n">
-        <v>114204</v>
+        <v>126191</v>
       </c>
       <c r="E233" t="n">
-        <v>1652659</v>
+        <v>775157</v>
       </c>
       <c r="F233" t="n">
-        <v>107101</v>
+        <v>124777</v>
       </c>
       <c r="G233" t="n">
-        <v>3296120</v>
+        <v>1533443</v>
       </c>
       <c r="H233" t="n">
-        <v>221305</v>
+        <v>250968</v>
       </c>
       <c r="I233" t="n">
-        <v>6.71</v>
+        <v>16.37</v>
       </c>
       <c r="J233" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K233" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L233" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>연신내</t>
+          <t>오금</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1036393</v>
+        <v>291808</v>
       </c>
       <c r="D234" t="n">
-        <v>264167</v>
+        <v>56755</v>
       </c>
       <c r="E234" t="n">
-        <v>985977</v>
+        <v>273271</v>
       </c>
       <c r="F234" t="n">
-        <v>255205</v>
+        <v>54128</v>
       </c>
       <c r="G234" t="n">
-        <v>2022370</v>
+        <v>565079</v>
       </c>
       <c r="H234" t="n">
-        <v>519372</v>
+        <v>110883</v>
       </c>
       <c r="I234" t="n">
-        <v>25.68</v>
+        <v>19.62</v>
       </c>
       <c r="J234" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K234" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L234" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>영등포구청</t>
+          <t>왕십리</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10288,82 +10288,82 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>758286</v>
+        <v>602261</v>
       </c>
       <c r="D235" t="n">
-        <v>126191</v>
+        <v>79888</v>
       </c>
       <c r="E235" t="n">
-        <v>775157</v>
+        <v>577607</v>
       </c>
       <c r="F235" t="n">
-        <v>124777</v>
+        <v>75030</v>
       </c>
       <c r="G235" t="n">
-        <v>1533443</v>
+        <v>1179868</v>
       </c>
       <c r="H235" t="n">
-        <v>250968</v>
+        <v>154918</v>
       </c>
       <c r="I235" t="n">
-        <v>16.37</v>
+        <v>13.13</v>
       </c>
       <c r="J235" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K235" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L235" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>오금</t>
+          <t>을지로3가</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>291808</v>
+        <v>1051252</v>
       </c>
       <c r="D236" t="n">
-        <v>56755</v>
+        <v>125034</v>
       </c>
       <c r="E236" t="n">
-        <v>273271</v>
+        <v>1045244</v>
       </c>
       <c r="F236" t="n">
-        <v>54128</v>
+        <v>121016</v>
       </c>
       <c r="G236" t="n">
-        <v>565079</v>
+        <v>2096496</v>
       </c>
       <c r="H236" t="n">
-        <v>110883</v>
+        <v>246050</v>
       </c>
       <c r="I236" t="n">
-        <v>19.62</v>
+        <v>11.74</v>
       </c>
       <c r="J236" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K236" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L236" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>왕십리</t>
+          <t>을지로4가</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10372,454 +10372,412 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>602261</v>
+        <v>589848</v>
       </c>
       <c r="D237" t="n">
-        <v>79888</v>
+        <v>119702</v>
       </c>
       <c r="E237" t="n">
-        <v>577607</v>
+        <v>592977</v>
       </c>
       <c r="F237" t="n">
-        <v>75030</v>
+        <v>118251</v>
       </c>
       <c r="G237" t="n">
-        <v>1179868</v>
+        <v>1182825</v>
       </c>
       <c r="H237" t="n">
-        <v>154918</v>
+        <v>237953</v>
       </c>
       <c r="I237" t="n">
-        <v>13.13</v>
+        <v>20.12</v>
       </c>
       <c r="J237" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L237" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>을지로3가</t>
+          <t>잠실</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1051252</v>
+        <v>2898750</v>
       </c>
       <c r="D238" t="n">
-        <v>125034</v>
+        <v>309717</v>
       </c>
       <c r="E238" t="n">
-        <v>1045244</v>
+        <v>2944462</v>
       </c>
       <c r="F238" t="n">
-        <v>121016</v>
+        <v>298290</v>
       </c>
       <c r="G238" t="n">
-        <v>2096496</v>
+        <v>5843212</v>
       </c>
       <c r="H238" t="n">
-        <v>246050</v>
+        <v>608007</v>
       </c>
       <c r="I238" t="n">
-        <v>11.74</v>
+        <v>10.41</v>
       </c>
       <c r="J238" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K238" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L238" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>을지로4가</t>
+          <t>종로3가</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>1,3,5</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>589848</v>
+        <v>1557687</v>
       </c>
       <c r="D239" t="n">
-        <v>119702</v>
+        <v>458436</v>
       </c>
       <c r="E239" t="n">
-        <v>592977</v>
+        <v>1539083</v>
       </c>
       <c r="F239" t="n">
-        <v>118251</v>
+        <v>445192</v>
       </c>
       <c r="G239" t="n">
-        <v>1182825</v>
+        <v>3096770</v>
       </c>
       <c r="H239" t="n">
-        <v>237953</v>
+        <v>903628</v>
       </c>
       <c r="I239" t="n">
-        <v>20.12</v>
+        <v>29.18</v>
       </c>
       <c r="J239" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K239" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L239" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>잠실</t>
+          <t>천호</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2898750</v>
+        <v>1055612</v>
       </c>
       <c r="D240" t="n">
-        <v>309717</v>
+        <v>253203</v>
       </c>
       <c r="E240" t="n">
-        <v>2944462</v>
+        <v>1108370</v>
       </c>
       <c r="F240" t="n">
-        <v>298290</v>
+        <v>252351</v>
       </c>
       <c r="G240" t="n">
-        <v>5843212</v>
+        <v>2163982</v>
       </c>
       <c r="H240" t="n">
-        <v>608007</v>
+        <v>505554</v>
       </c>
       <c r="I240" t="n">
-        <v>10.41</v>
+        <v>23.36</v>
       </c>
       <c r="J240" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K240" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L240" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>종로3가</t>
+          <t>청구</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>1,3,5</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1557687</v>
+        <v>219899</v>
       </c>
       <c r="D241" t="n">
-        <v>458436</v>
+        <v>44565</v>
       </c>
       <c r="E241" t="n">
-        <v>1539083</v>
+        <v>211920</v>
       </c>
       <c r="F241" t="n">
-        <v>445192</v>
+        <v>42532</v>
       </c>
       <c r="G241" t="n">
-        <v>3096770</v>
+        <v>431819</v>
       </c>
       <c r="H241" t="n">
-        <v>903628</v>
+        <v>87097</v>
       </c>
       <c r="I241" t="n">
-        <v>29.18</v>
+        <v>20.17</v>
       </c>
       <c r="J241" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K241" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L241" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>천호</t>
+          <t>충무로</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1055612</v>
+        <v>867520</v>
       </c>
       <c r="D242" t="n">
-        <v>253203</v>
+        <v>119883</v>
       </c>
       <c r="E242" t="n">
-        <v>1108370</v>
+        <v>893846</v>
       </c>
       <c r="F242" t="n">
-        <v>252351</v>
+        <v>121889</v>
       </c>
       <c r="G242" t="n">
-        <v>2163982</v>
+        <v>1761366</v>
       </c>
       <c r="H242" t="n">
-        <v>505554</v>
+        <v>241772</v>
       </c>
       <c r="I242" t="n">
-        <v>23.36</v>
+        <v>13.73</v>
       </c>
       <c r="J242" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L242" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>청구</t>
+          <t>충정로</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>219899</v>
+        <v>417744</v>
       </c>
       <c r="D243" t="n">
-        <v>44565</v>
+        <v>63616</v>
       </c>
       <c r="E243" t="n">
-        <v>211920</v>
+        <v>436275</v>
       </c>
       <c r="F243" t="n">
-        <v>42532</v>
+        <v>64124</v>
       </c>
       <c r="G243" t="n">
-        <v>431819</v>
+        <v>854019</v>
       </c>
       <c r="H243" t="n">
-        <v>87097</v>
+        <v>127740</v>
       </c>
       <c r="I243" t="n">
-        <v>20.17</v>
+        <v>14.96</v>
       </c>
       <c r="J243" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L243" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>충무로</t>
+          <t>태릉입구</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>867520</v>
+        <v>438855</v>
       </c>
       <c r="D244" t="n">
-        <v>119883</v>
+        <v>87568</v>
       </c>
       <c r="E244" t="n">
-        <v>893846</v>
+        <v>443702</v>
       </c>
       <c r="F244" t="n">
-        <v>121889</v>
+        <v>85169</v>
       </c>
       <c r="G244" t="n">
-        <v>1761366</v>
+        <v>882557</v>
       </c>
       <c r="H244" t="n">
-        <v>241772</v>
+        <v>172737</v>
       </c>
       <c r="I244" t="n">
-        <v>13.73</v>
+        <v>19.57</v>
       </c>
       <c r="J244" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K244" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L244" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>충정로</t>
+          <t>합정</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>417744</v>
+        <v>1379809</v>
       </c>
       <c r="D245" t="n">
-        <v>63616</v>
+        <v>113748</v>
       </c>
       <c r="E245" t="n">
-        <v>436275</v>
+        <v>1461301</v>
       </c>
       <c r="F245" t="n">
-        <v>64124</v>
+        <v>111461</v>
       </c>
       <c r="G245" t="n">
-        <v>854019</v>
+        <v>2841110</v>
       </c>
       <c r="H245" t="n">
-        <v>127740</v>
+        <v>225209</v>
       </c>
       <c r="I245" t="n">
-        <v>14.96</v>
+        <v>7.93</v>
       </c>
       <c r="J245" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K245" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L245" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>태릉입구</t>
+          <t>이수</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>438855</v>
+        <v>1043396</v>
       </c>
       <c r="D246" t="n">
-        <v>87568</v>
+        <v>244929</v>
       </c>
       <c r="E246" t="n">
-        <v>443702</v>
+        <v>1074046</v>
       </c>
       <c r="F246" t="n">
-        <v>85169</v>
+        <v>248082</v>
       </c>
       <c r="G246" t="n">
-        <v>882557</v>
+        <v>2117442</v>
       </c>
       <c r="H246" t="n">
-        <v>172737</v>
+        <v>493011</v>
       </c>
       <c r="I246" t="n">
-        <v>19.57</v>
+        <v>23.28</v>
       </c>
       <c r="J246" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K246" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L246" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>합정</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>1379809</v>
-      </c>
-      <c r="D247" t="n">
-        <v>113748</v>
-      </c>
-      <c r="E247" t="n">
-        <v>1461301</v>
-      </c>
-      <c r="F247" t="n">
-        <v>111461</v>
-      </c>
-      <c r="G247" t="n">
-        <v>2841110</v>
-      </c>
-      <c r="H247" t="n">
-        <v>225209</v>
-      </c>
-      <c r="I247" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="J247" t="n">
-        <v>16</v>
-      </c>
-      <c r="K247" t="n">
-        <v>7</v>
-      </c>
-      <c r="L247" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/team/subway_merged_base.xlsx
+++ b/data/processed/team/subway_merged_base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L246"/>
+  <dimension ref="A1:L245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,7 +2971,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>지축</t>
+          <t>학여울</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2980,40 +2980,40 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>208998</v>
+        <v>73982</v>
       </c>
       <c r="D61" t="n">
-        <v>36660</v>
+        <v>18231</v>
       </c>
       <c r="E61" t="n">
-        <v>207220</v>
+        <v>75530</v>
       </c>
       <c r="F61" t="n">
-        <v>35500</v>
+        <v>17950</v>
       </c>
       <c r="G61" t="n">
-        <v>416218</v>
+        <v>149512</v>
       </c>
       <c r="H61" t="n">
-        <v>72160</v>
+        <v>36181</v>
       </c>
       <c r="I61" t="n">
-        <v>17.34</v>
+        <v>24.2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>학여울</t>
+          <t>홍제</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3022,82 +3022,82 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>73982</v>
+        <v>530608</v>
       </c>
       <c r="D62" t="n">
-        <v>18231</v>
+        <v>146942</v>
       </c>
       <c r="E62" t="n">
-        <v>75530</v>
+        <v>503869</v>
       </c>
       <c r="F62" t="n">
-        <v>17950</v>
+        <v>144399</v>
       </c>
       <c r="G62" t="n">
-        <v>149512</v>
+        <v>1034477</v>
       </c>
       <c r="H62" t="n">
-        <v>36181</v>
+        <v>291341</v>
       </c>
       <c r="I62" t="n">
-        <v>24.2</v>
+        <v>28.16</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>홍제</t>
+          <t>길음</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>530608</v>
+        <v>628482</v>
       </c>
       <c r="D63" t="n">
-        <v>146942</v>
+        <v>125633</v>
       </c>
       <c r="E63" t="n">
-        <v>503869</v>
+        <v>621129</v>
       </c>
       <c r="F63" t="n">
-        <v>144399</v>
+        <v>125259</v>
       </c>
       <c r="G63" t="n">
-        <v>1034477</v>
+        <v>1249611</v>
       </c>
       <c r="H63" t="n">
-        <v>291341</v>
+        <v>250892</v>
       </c>
       <c r="I63" t="n">
-        <v>28.16</v>
+        <v>20.08</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
         <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>길음</t>
+          <t>남태령</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3106,40 +3106,40 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>628482</v>
+        <v>42171</v>
       </c>
       <c r="D64" t="n">
-        <v>125633</v>
+        <v>8901</v>
       </c>
       <c r="E64" t="n">
-        <v>621129</v>
+        <v>34627</v>
       </c>
       <c r="F64" t="n">
-        <v>125259</v>
+        <v>8196</v>
       </c>
       <c r="G64" t="n">
-        <v>1249611</v>
+        <v>76798</v>
       </c>
       <c r="H64" t="n">
-        <v>250892</v>
+        <v>17097</v>
       </c>
       <c r="I64" t="n">
-        <v>20.08</v>
+        <v>22.26</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
         <v>3</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>남태령</t>
+          <t>명동</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3148,40 +3148,40 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>42171</v>
+        <v>1024787</v>
       </c>
       <c r="D65" t="n">
-        <v>8901</v>
+        <v>80421</v>
       </c>
       <c r="E65" t="n">
-        <v>34627</v>
+        <v>1099284</v>
       </c>
       <c r="F65" t="n">
-        <v>8196</v>
+        <v>83092</v>
       </c>
       <c r="G65" t="n">
-        <v>76798</v>
+        <v>2124071</v>
       </c>
       <c r="H65" t="n">
-        <v>17097</v>
+        <v>163513</v>
       </c>
       <c r="I65" t="n">
-        <v>22.26</v>
+        <v>7.7</v>
       </c>
       <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="n">
-        <v>3</v>
-      </c>
       <c r="L65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>명동</t>
+          <t>미아</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3190,40 +3190,40 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1024787</v>
+        <v>456892</v>
       </c>
       <c r="D66" t="n">
-        <v>80421</v>
+        <v>121117</v>
       </c>
       <c r="E66" t="n">
-        <v>1099284</v>
+        <v>439668</v>
       </c>
       <c r="F66" t="n">
-        <v>83092</v>
+        <v>122900</v>
       </c>
       <c r="G66" t="n">
-        <v>2124071</v>
+        <v>896560</v>
       </c>
       <c r="H66" t="n">
-        <v>163513</v>
+        <v>244017</v>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>27.22</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>미아</t>
+          <t>미아사거리</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3232,40 +3232,40 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>456892</v>
+        <v>779304</v>
       </c>
       <c r="D67" t="n">
-        <v>121117</v>
+        <v>190582</v>
       </c>
       <c r="E67" t="n">
-        <v>439668</v>
+        <v>765423</v>
       </c>
       <c r="F67" t="n">
-        <v>122900</v>
+        <v>190213</v>
       </c>
       <c r="G67" t="n">
-        <v>896560</v>
+        <v>1544727</v>
       </c>
       <c r="H67" t="n">
-        <v>244017</v>
+        <v>380795</v>
       </c>
       <c r="I67" t="n">
-        <v>27.22</v>
+        <v>24.65</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>미아사거리</t>
+          <t>불암산</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3274,40 +3274,40 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>779304</v>
+        <v>289358</v>
       </c>
       <c r="D68" t="n">
-        <v>190582</v>
+        <v>84601</v>
       </c>
       <c r="E68" t="n">
-        <v>765423</v>
+        <v>252956</v>
       </c>
       <c r="F68" t="n">
-        <v>190213</v>
+        <v>83424</v>
       </c>
       <c r="G68" t="n">
-        <v>1544727</v>
+        <v>542314</v>
       </c>
       <c r="H68" t="n">
-        <v>380795</v>
+        <v>168025</v>
       </c>
       <c r="I68" t="n">
-        <v>24.65</v>
+        <v>30.98</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>불암산</t>
+          <t>상계</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3316,40 +3316,40 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>289358</v>
+        <v>567980</v>
       </c>
       <c r="D69" t="n">
-        <v>84601</v>
+        <v>132469</v>
       </c>
       <c r="E69" t="n">
-        <v>252956</v>
+        <v>528993</v>
       </c>
       <c r="F69" t="n">
-        <v>83424</v>
+        <v>129123</v>
       </c>
       <c r="G69" t="n">
-        <v>542314</v>
+        <v>1096973</v>
       </c>
       <c r="H69" t="n">
-        <v>168025</v>
+        <v>261592</v>
       </c>
       <c r="I69" t="n">
-        <v>30.98</v>
+        <v>23.85</v>
       </c>
       <c r="J69" t="n">
         <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>상계</t>
+          <t>성신여대입구</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3358,40 +3358,40 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>567980</v>
+        <v>650518</v>
       </c>
       <c r="D70" t="n">
-        <v>132469</v>
+        <v>92470</v>
       </c>
       <c r="E70" t="n">
-        <v>528993</v>
+        <v>627105</v>
       </c>
       <c r="F70" t="n">
-        <v>129123</v>
+        <v>90891</v>
       </c>
       <c r="G70" t="n">
-        <v>1096973</v>
+        <v>1277623</v>
       </c>
       <c r="H70" t="n">
-        <v>261592</v>
+        <v>183361</v>
       </c>
       <c r="I70" t="n">
-        <v>23.85</v>
+        <v>14.35</v>
       </c>
       <c r="J70" t="n">
         <v>4</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>성신여대입구</t>
+          <t>수유</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3400,40 +3400,40 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>650518</v>
+        <v>1001984</v>
       </c>
       <c r="D71" t="n">
-        <v>92470</v>
+        <v>198968</v>
       </c>
       <c r="E71" t="n">
-        <v>627105</v>
+        <v>1002275</v>
       </c>
       <c r="F71" t="n">
-        <v>90891</v>
+        <v>200056</v>
       </c>
       <c r="G71" t="n">
-        <v>1277623</v>
+        <v>2004259</v>
       </c>
       <c r="H71" t="n">
-        <v>183361</v>
+        <v>399024</v>
       </c>
       <c r="I71" t="n">
-        <v>14.35</v>
+        <v>19.91</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>수유</t>
+          <t>숙대입구</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3442,40 +3442,40 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1001984</v>
+        <v>441015</v>
       </c>
       <c r="D72" t="n">
-        <v>198968</v>
+        <v>56826</v>
       </c>
       <c r="E72" t="n">
-        <v>1002275</v>
+        <v>427018</v>
       </c>
       <c r="F72" t="n">
-        <v>200056</v>
+        <v>53034</v>
       </c>
       <c r="G72" t="n">
-        <v>2004259</v>
+        <v>868033</v>
       </c>
       <c r="H72" t="n">
-        <v>399024</v>
+        <v>109860</v>
       </c>
       <c r="I72" t="n">
-        <v>19.91</v>
+        <v>12.66</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>3</v>
       </c>
       <c r="L72" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>숙대입구</t>
+          <t>신용산</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3484,40 +3484,40 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>441015</v>
+        <v>583290</v>
       </c>
       <c r="D73" t="n">
-        <v>56826</v>
+        <v>58072</v>
       </c>
       <c r="E73" t="n">
-        <v>427018</v>
+        <v>626444</v>
       </c>
       <c r="F73" t="n">
-        <v>53034</v>
+        <v>58695</v>
       </c>
       <c r="G73" t="n">
-        <v>868033</v>
+        <v>1209734</v>
       </c>
       <c r="H73" t="n">
-        <v>109860</v>
+        <v>116767</v>
       </c>
       <c r="I73" t="n">
-        <v>12.66</v>
+        <v>9.65</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>신용산</t>
+          <t>쌍문</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3526,40 +3526,40 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>583290</v>
+        <v>850936</v>
       </c>
       <c r="D74" t="n">
-        <v>58072</v>
+        <v>181630</v>
       </c>
       <c r="E74" t="n">
-        <v>626444</v>
+        <v>787722</v>
       </c>
       <c r="F74" t="n">
-        <v>58695</v>
+        <v>178911</v>
       </c>
       <c r="G74" t="n">
-        <v>1209734</v>
+        <v>1638658</v>
       </c>
       <c r="H74" t="n">
-        <v>116767</v>
+        <v>360541</v>
       </c>
       <c r="I74" t="n">
-        <v>9.65</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" t="n">
         <v>9</v>
-      </c>
-      <c r="K74" t="n">
-        <v>4</v>
-      </c>
-      <c r="L74" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>쌍문</t>
+          <t>이촌</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3568,31 +3568,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>850936</v>
+        <v>291058</v>
       </c>
       <c r="D75" t="n">
-        <v>181630</v>
+        <v>53692</v>
       </c>
       <c r="E75" t="n">
-        <v>787722</v>
+        <v>316137</v>
       </c>
       <c r="F75" t="n">
-        <v>178911</v>
+        <v>56438</v>
       </c>
       <c r="G75" t="n">
-        <v>1638658</v>
+        <v>607195</v>
       </c>
       <c r="H75" t="n">
-        <v>360541</v>
+        <v>110130</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>18.14</v>
       </c>
       <c r="J75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L75" t="n">
         <v>9</v>
@@ -3601,7 +3601,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>이촌</t>
+          <t>창동</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3610,40 +3610,40 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>291058</v>
+        <v>775634</v>
       </c>
       <c r="D76" t="n">
-        <v>53692</v>
+        <v>227917</v>
       </c>
       <c r="E76" t="n">
-        <v>316137</v>
+        <v>815046</v>
       </c>
       <c r="F76" t="n">
-        <v>56438</v>
+        <v>234923</v>
       </c>
       <c r="G76" t="n">
-        <v>607195</v>
+        <v>1590680</v>
       </c>
       <c r="H76" t="n">
-        <v>110130</v>
+        <v>462840</v>
       </c>
       <c r="I76" t="n">
-        <v>18.14</v>
+        <v>29.1</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>창동</t>
+          <t>한성대입구</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3652,40 +3652,40 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>775634</v>
+        <v>422016</v>
       </c>
       <c r="D77" t="n">
-        <v>227917</v>
+        <v>76857</v>
       </c>
       <c r="E77" t="n">
-        <v>815046</v>
+        <v>409204</v>
       </c>
       <c r="F77" t="n">
-        <v>234923</v>
+        <v>75462</v>
       </c>
       <c r="G77" t="n">
-        <v>1590680</v>
+        <v>831220</v>
       </c>
       <c r="H77" t="n">
-        <v>462840</v>
+        <v>152319</v>
       </c>
       <c r="I77" t="n">
-        <v>29.1</v>
+        <v>18.32</v>
       </c>
       <c r="J77" t="n">
         <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한성대입구</t>
+          <t>혜화</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3694,40 +3694,40 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>422016</v>
+        <v>1093159</v>
       </c>
       <c r="D78" t="n">
-        <v>76857</v>
+        <v>134964</v>
       </c>
       <c r="E78" t="n">
-        <v>409204</v>
+        <v>1101259</v>
       </c>
       <c r="F78" t="n">
-        <v>75462</v>
+        <v>132704</v>
       </c>
       <c r="G78" t="n">
-        <v>831220</v>
+        <v>2194418</v>
       </c>
       <c r="H78" t="n">
-        <v>152319</v>
+        <v>267668</v>
       </c>
       <c r="I78" t="n">
-        <v>18.32</v>
+        <v>12.2</v>
       </c>
       <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
         <v>2</v>
       </c>
-      <c r="K78" t="n">
-        <v>3</v>
-      </c>
       <c r="L78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>혜화</t>
+          <t>회현</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3736,82 +3736,82 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1093159</v>
+        <v>790571</v>
       </c>
       <c r="D79" t="n">
-        <v>134964</v>
+        <v>203810</v>
       </c>
       <c r="E79" t="n">
-        <v>1101259</v>
+        <v>821961</v>
       </c>
       <c r="F79" t="n">
-        <v>132704</v>
+        <v>203499</v>
       </c>
       <c r="G79" t="n">
-        <v>2194418</v>
+        <v>1612532</v>
       </c>
       <c r="H79" t="n">
-        <v>267668</v>
+        <v>407309</v>
       </c>
       <c r="I79" t="n">
-        <v>12.2</v>
+        <v>25.26</v>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
         <v>2</v>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>회현</t>
+          <t>강동</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>790571</v>
+        <v>533364</v>
       </c>
       <c r="D80" t="n">
-        <v>203810</v>
+        <v>114472</v>
       </c>
       <c r="E80" t="n">
-        <v>821961</v>
+        <v>516922</v>
       </c>
       <c r="F80" t="n">
-        <v>203499</v>
+        <v>111842</v>
       </c>
       <c r="G80" t="n">
-        <v>1612532</v>
+        <v>1050286</v>
       </c>
       <c r="H80" t="n">
-        <v>407309</v>
+        <v>226314</v>
       </c>
       <c r="I80" t="n">
-        <v>25.26</v>
+        <v>21.55</v>
       </c>
       <c r="J80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강동</t>
+          <t>강일</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3820,40 +3820,40 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>533364</v>
+        <v>170232</v>
       </c>
       <c r="D81" t="n">
-        <v>114472</v>
+        <v>45780</v>
       </c>
       <c r="E81" t="n">
-        <v>516922</v>
+        <v>156100</v>
       </c>
       <c r="F81" t="n">
-        <v>111842</v>
+        <v>43927</v>
       </c>
       <c r="G81" t="n">
-        <v>1050286</v>
+        <v>326332</v>
       </c>
       <c r="H81" t="n">
-        <v>226314</v>
+        <v>89707</v>
       </c>
       <c r="I81" t="n">
-        <v>21.55</v>
+        <v>27.49</v>
       </c>
       <c r="J81" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L81" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강일</t>
+          <t>개롱</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3862,40 +3862,40 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>170232</v>
+        <v>190212</v>
       </c>
       <c r="D82" t="n">
-        <v>45780</v>
+        <v>53640</v>
       </c>
       <c r="E82" t="n">
-        <v>156100</v>
+        <v>196781</v>
       </c>
       <c r="F82" t="n">
-        <v>43927</v>
+        <v>55256</v>
       </c>
       <c r="G82" t="n">
-        <v>326332</v>
+        <v>386993</v>
       </c>
       <c r="H82" t="n">
-        <v>89707</v>
+        <v>108896</v>
       </c>
       <c r="I82" t="n">
-        <v>27.49</v>
+        <v>28.14</v>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L82" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>개롱</t>
+          <t>개화산</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3904,40 +3904,40 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>190212</v>
+        <v>172565</v>
       </c>
       <c r="D83" t="n">
-        <v>53640</v>
+        <v>43852</v>
       </c>
       <c r="E83" t="n">
-        <v>196781</v>
+        <v>164917</v>
       </c>
       <c r="F83" t="n">
-        <v>55256</v>
+        <v>42730</v>
       </c>
       <c r="G83" t="n">
-        <v>386993</v>
+        <v>337482</v>
       </c>
       <c r="H83" t="n">
-        <v>108896</v>
+        <v>86582</v>
       </c>
       <c r="I83" t="n">
-        <v>28.14</v>
+        <v>25.66</v>
       </c>
       <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>2</v>
       </c>
-      <c r="K83" t="n">
-        <v>3</v>
-      </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>개화산</t>
+          <t>거여</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3946,40 +3946,40 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>172565</v>
+        <v>291759</v>
       </c>
       <c r="D84" t="n">
-        <v>43852</v>
+        <v>70164</v>
       </c>
       <c r="E84" t="n">
-        <v>164917</v>
+        <v>282342</v>
       </c>
       <c r="F84" t="n">
-        <v>42730</v>
+        <v>68179</v>
       </c>
       <c r="G84" t="n">
-        <v>337482</v>
+        <v>574101</v>
       </c>
       <c r="H84" t="n">
-        <v>86582</v>
+        <v>138343</v>
       </c>
       <c r="I84" t="n">
-        <v>25.66</v>
+        <v>24.1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>거여</t>
+          <t>고덕</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3988,40 +3988,40 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>291759</v>
+        <v>299295</v>
       </c>
       <c r="D85" t="n">
-        <v>70164</v>
+        <v>79625</v>
       </c>
       <c r="E85" t="n">
-        <v>282342</v>
+        <v>292521</v>
       </c>
       <c r="F85" t="n">
-        <v>68179</v>
+        <v>78156</v>
       </c>
       <c r="G85" t="n">
-        <v>574101</v>
+        <v>591816</v>
       </c>
       <c r="H85" t="n">
-        <v>138343</v>
+        <v>157781</v>
       </c>
       <c r="I85" t="n">
-        <v>24.1</v>
+        <v>26.66</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>고덕</t>
+          <t>광나루</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4030,40 +4030,40 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>299295</v>
+        <v>375202</v>
       </c>
       <c r="D86" t="n">
-        <v>79625</v>
+        <v>73599</v>
       </c>
       <c r="E86" t="n">
-        <v>292521</v>
+        <v>353884</v>
       </c>
       <c r="F86" t="n">
-        <v>78156</v>
+        <v>71628</v>
       </c>
       <c r="G86" t="n">
-        <v>591816</v>
+        <v>729086</v>
       </c>
       <c r="H86" t="n">
-        <v>157781</v>
+        <v>145227</v>
       </c>
       <c r="I86" t="n">
-        <v>26.66</v>
+        <v>19.92</v>
       </c>
       <c r="J86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K86" t="n">
         <v>4</v>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>광나루</t>
+          <t>광화문</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4072,40 +4072,40 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>375202</v>
+        <v>957048</v>
       </c>
       <c r="D87" t="n">
-        <v>73599</v>
+        <v>100036</v>
       </c>
       <c r="E87" t="n">
-        <v>353884</v>
+        <v>1006443</v>
       </c>
       <c r="F87" t="n">
-        <v>71628</v>
+        <v>99151</v>
       </c>
       <c r="G87" t="n">
-        <v>729086</v>
+        <v>1963491</v>
       </c>
       <c r="H87" t="n">
-        <v>145227</v>
+        <v>199187</v>
       </c>
       <c r="I87" t="n">
-        <v>19.92</v>
+        <v>10.14</v>
       </c>
       <c r="J87" t="n">
         <v>4</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>광화문</t>
+          <t>굽은다리</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4114,40 +4114,40 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>957048</v>
+        <v>288736</v>
       </c>
       <c r="D88" t="n">
-        <v>100036</v>
+        <v>83933</v>
       </c>
       <c r="E88" t="n">
-        <v>1006443</v>
+        <v>275879</v>
       </c>
       <c r="F88" t="n">
-        <v>99151</v>
+        <v>78941</v>
       </c>
       <c r="G88" t="n">
-        <v>1963491</v>
+        <v>564615</v>
       </c>
       <c r="H88" t="n">
-        <v>199187</v>
+        <v>162874</v>
       </c>
       <c r="I88" t="n">
-        <v>10.14</v>
+        <v>28.85</v>
       </c>
       <c r="J88" t="n">
         <v>4</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>굽은다리</t>
+          <t>길동</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4156,40 +4156,40 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>288736</v>
+        <v>247837</v>
       </c>
       <c r="D89" t="n">
-        <v>83933</v>
+        <v>82177</v>
       </c>
       <c r="E89" t="n">
-        <v>275879</v>
+        <v>254202</v>
       </c>
       <c r="F89" t="n">
-        <v>78941</v>
+        <v>83931</v>
       </c>
       <c r="G89" t="n">
-        <v>564615</v>
+        <v>502039</v>
       </c>
       <c r="H89" t="n">
-        <v>162874</v>
+        <v>166108</v>
       </c>
       <c r="I89" t="n">
-        <v>28.85</v>
+        <v>33.09</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K89" t="n">
         <v>3</v>
       </c>
       <c r="L89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>길동</t>
+          <t>까치산</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4198,40 +4198,40 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>247837</v>
+        <v>814059</v>
       </c>
       <c r="D90" t="n">
-        <v>82177</v>
+        <v>164710</v>
       </c>
       <c r="E90" t="n">
-        <v>254202</v>
+        <v>781516</v>
       </c>
       <c r="F90" t="n">
-        <v>83931</v>
+        <v>165992</v>
       </c>
       <c r="G90" t="n">
-        <v>502039</v>
+        <v>1595575</v>
       </c>
       <c r="H90" t="n">
-        <v>166108</v>
+        <v>330702</v>
       </c>
       <c r="I90" t="n">
-        <v>33.09</v>
+        <v>20.73</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>까치산</t>
+          <t>답십리</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4240,40 +4240,40 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>814059</v>
+        <v>458993</v>
       </c>
       <c r="D91" t="n">
-        <v>164710</v>
+        <v>86954</v>
       </c>
       <c r="E91" t="n">
-        <v>781516</v>
+        <v>416125</v>
       </c>
       <c r="F91" t="n">
-        <v>165992</v>
+        <v>83704</v>
       </c>
       <c r="G91" t="n">
-        <v>1595575</v>
+        <v>875118</v>
       </c>
       <c r="H91" t="n">
-        <v>330702</v>
+        <v>170658</v>
       </c>
       <c r="I91" t="n">
-        <v>20.73</v>
+        <v>19.5</v>
       </c>
       <c r="J91" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
       </c>
       <c r="L91" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>답십리</t>
+          <t>둔촌동</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4282,40 +4282,40 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>458993</v>
+        <v>296332</v>
       </c>
       <c r="D92" t="n">
-        <v>86954</v>
+        <v>78666</v>
       </c>
       <c r="E92" t="n">
-        <v>416125</v>
+        <v>294564</v>
       </c>
       <c r="F92" t="n">
-        <v>83704</v>
+        <v>79119</v>
       </c>
       <c r="G92" t="n">
-        <v>875118</v>
+        <v>590896</v>
       </c>
       <c r="H92" t="n">
-        <v>170658</v>
+        <v>157785</v>
       </c>
       <c r="I92" t="n">
-        <v>19.5</v>
+        <v>26.7</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>둔촌동</t>
+          <t>마곡</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4324,40 +4324,40 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>296332</v>
+        <v>347361</v>
       </c>
       <c r="D93" t="n">
-        <v>78666</v>
+        <v>52044</v>
       </c>
       <c r="E93" t="n">
-        <v>294564</v>
+        <v>351461</v>
       </c>
       <c r="F93" t="n">
-        <v>79119</v>
+        <v>50645</v>
       </c>
       <c r="G93" t="n">
-        <v>590896</v>
+        <v>698822</v>
       </c>
       <c r="H93" t="n">
-        <v>157785</v>
+        <v>102689</v>
       </c>
       <c r="I93" t="n">
-        <v>26.7</v>
+        <v>14.69</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>마곡</t>
+          <t>마장</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4366,40 +4366,40 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>347361</v>
+        <v>172049</v>
       </c>
       <c r="D94" t="n">
-        <v>52044</v>
+        <v>43789</v>
       </c>
       <c r="E94" t="n">
-        <v>351461</v>
+        <v>161650</v>
       </c>
       <c r="F94" t="n">
-        <v>50645</v>
+        <v>42637</v>
       </c>
       <c r="G94" t="n">
-        <v>698822</v>
+        <v>333699</v>
       </c>
       <c r="H94" t="n">
-        <v>102689</v>
+        <v>86426</v>
       </c>
       <c r="I94" t="n">
-        <v>14.69</v>
+        <v>25.9</v>
       </c>
       <c r="J94" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>마장</t>
+          <t>마천</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>172049</v>
+        <v>214340</v>
       </c>
       <c r="D95" t="n">
-        <v>43789</v>
+        <v>59538</v>
       </c>
       <c r="E95" t="n">
-        <v>161650</v>
+        <v>198016</v>
       </c>
       <c r="F95" t="n">
-        <v>42637</v>
+        <v>60889</v>
       </c>
       <c r="G95" t="n">
-        <v>333699</v>
+        <v>412356</v>
       </c>
       <c r="H95" t="n">
-        <v>86426</v>
+        <v>120427</v>
       </c>
       <c r="I95" t="n">
-        <v>25.9</v>
+        <v>29.2</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K95" t="n">
         <v>3</v>
       </c>
       <c r="L95" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>마천</t>
+          <t>마포</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4450,40 +4450,40 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>214340</v>
+        <v>415591</v>
       </c>
       <c r="D96" t="n">
-        <v>59538</v>
+        <v>66098</v>
       </c>
       <c r="E96" t="n">
-        <v>198016</v>
+        <v>422710</v>
       </c>
       <c r="F96" t="n">
-        <v>60889</v>
+        <v>65596</v>
       </c>
       <c r="G96" t="n">
-        <v>412356</v>
+        <v>838301</v>
       </c>
       <c r="H96" t="n">
-        <v>120427</v>
+        <v>131694</v>
       </c>
       <c r="I96" t="n">
-        <v>29.2</v>
+        <v>15.71</v>
       </c>
       <c r="J96" t="n">
         <v>10</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>마포</t>
+          <t>명일</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4492,40 +4492,40 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>415591</v>
+        <v>252942</v>
       </c>
       <c r="D97" t="n">
-        <v>66098</v>
+        <v>73518</v>
       </c>
       <c r="E97" t="n">
-        <v>422710</v>
+        <v>255248</v>
       </c>
       <c r="F97" t="n">
-        <v>65596</v>
+        <v>75135</v>
       </c>
       <c r="G97" t="n">
-        <v>838301</v>
+        <v>508190</v>
       </c>
       <c r="H97" t="n">
-        <v>131694</v>
+        <v>148653</v>
       </c>
       <c r="I97" t="n">
-        <v>15.71</v>
+        <v>29.25</v>
       </c>
       <c r="J97" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L97" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>명일</t>
+          <t>목동</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>252942</v>
+        <v>477823</v>
       </c>
       <c r="D98" t="n">
-        <v>73518</v>
+        <v>87895</v>
       </c>
       <c r="E98" t="n">
-        <v>255248</v>
+        <v>509824</v>
       </c>
       <c r="F98" t="n">
-        <v>75135</v>
+        <v>89392</v>
       </c>
       <c r="G98" t="n">
-        <v>508190</v>
+        <v>987647</v>
       </c>
       <c r="H98" t="n">
-        <v>148653</v>
+        <v>177287</v>
       </c>
       <c r="I98" t="n">
-        <v>29.25</v>
+        <v>17.95</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K98" t="n">
         <v>3</v>
       </c>
       <c r="L98" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>목동</t>
+          <t>발산</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4576,40 +4576,40 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>477823</v>
+        <v>646724</v>
       </c>
       <c r="D99" t="n">
-        <v>87895</v>
+        <v>113341</v>
       </c>
       <c r="E99" t="n">
-        <v>509824</v>
+        <v>668751</v>
       </c>
       <c r="F99" t="n">
-        <v>89392</v>
+        <v>109595</v>
       </c>
       <c r="G99" t="n">
-        <v>987647</v>
+        <v>1315475</v>
       </c>
       <c r="H99" t="n">
-        <v>177287</v>
+        <v>222936</v>
       </c>
       <c r="I99" t="n">
-        <v>17.95</v>
+        <v>16.95</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>3</v>
       </c>
       <c r="L99" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>발산</t>
+          <t>방이</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4618,40 +4618,40 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>646724</v>
+        <v>216835</v>
       </c>
       <c r="D100" t="n">
-        <v>113341</v>
+        <v>52521</v>
       </c>
       <c r="E100" t="n">
-        <v>668751</v>
+        <v>221174</v>
       </c>
       <c r="F100" t="n">
-        <v>109595</v>
+        <v>52503</v>
       </c>
       <c r="G100" t="n">
-        <v>1315475</v>
+        <v>438009</v>
       </c>
       <c r="H100" t="n">
-        <v>222936</v>
+        <v>105024</v>
       </c>
       <c r="I100" t="n">
-        <v>16.95</v>
+        <v>23.98</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>방이</t>
+          <t>방화</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4660,40 +4660,40 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>216835</v>
+        <v>203041</v>
       </c>
       <c r="D101" t="n">
-        <v>52521</v>
+        <v>57926</v>
       </c>
       <c r="E101" t="n">
-        <v>221174</v>
+        <v>194670</v>
       </c>
       <c r="F101" t="n">
-        <v>52503</v>
+        <v>56879</v>
       </c>
       <c r="G101" t="n">
-        <v>438009</v>
+        <v>397711</v>
       </c>
       <c r="H101" t="n">
-        <v>105024</v>
+        <v>114805</v>
       </c>
       <c r="I101" t="n">
-        <v>23.98</v>
+        <v>28.87</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>방화</t>
+          <t>상일동</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4702,40 +4702,40 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>203041</v>
+        <v>419058</v>
       </c>
       <c r="D102" t="n">
-        <v>57926</v>
+        <v>96105</v>
       </c>
       <c r="E102" t="n">
-        <v>194670</v>
+        <v>397475</v>
       </c>
       <c r="F102" t="n">
-        <v>56879</v>
+        <v>94654</v>
       </c>
       <c r="G102" t="n">
-        <v>397711</v>
+        <v>816533</v>
       </c>
       <c r="H102" t="n">
-        <v>114805</v>
+        <v>190759</v>
       </c>
       <c r="I102" t="n">
-        <v>28.87</v>
+        <v>23.36</v>
       </c>
       <c r="J102" t="n">
+        <v>16</v>
+      </c>
+      <c r="K102" t="n">
         <v>6</v>
       </c>
-      <c r="K102" t="n">
-        <v>3</v>
-      </c>
       <c r="L102" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>상일동</t>
+          <t>서대문</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4744,40 +4744,40 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>419058</v>
+        <v>549925</v>
       </c>
       <c r="D103" t="n">
-        <v>96105</v>
+        <v>73647</v>
       </c>
       <c r="E103" t="n">
-        <v>397475</v>
+        <v>552121</v>
       </c>
       <c r="F103" t="n">
-        <v>94654</v>
+        <v>69654</v>
       </c>
       <c r="G103" t="n">
-        <v>816533</v>
+        <v>1102046</v>
       </c>
       <c r="H103" t="n">
-        <v>190759</v>
+        <v>143301</v>
       </c>
       <c r="I103" t="n">
-        <v>23.36</v>
+        <v>13</v>
       </c>
       <c r="J103" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>서대문</t>
+          <t>송정</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4786,40 +4786,40 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>549925</v>
+        <v>187616</v>
       </c>
       <c r="D104" t="n">
-        <v>73647</v>
+        <v>51923</v>
       </c>
       <c r="E104" t="n">
-        <v>552121</v>
+        <v>177560</v>
       </c>
       <c r="F104" t="n">
-        <v>69654</v>
+        <v>49900</v>
       </c>
       <c r="G104" t="n">
-        <v>1102046</v>
+        <v>365176</v>
       </c>
       <c r="H104" t="n">
-        <v>143301</v>
+        <v>101823</v>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>27.88</v>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L104" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>송정</t>
+          <t>신금호</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4828,40 +4828,40 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>187616</v>
+        <v>184048</v>
       </c>
       <c r="D105" t="n">
-        <v>51923</v>
+        <v>40032</v>
       </c>
       <c r="E105" t="n">
-        <v>177560</v>
+        <v>194994</v>
       </c>
       <c r="F105" t="n">
-        <v>49900</v>
+        <v>45260</v>
       </c>
       <c r="G105" t="n">
-        <v>365176</v>
+        <v>379042</v>
       </c>
       <c r="H105" t="n">
-        <v>101823</v>
+        <v>85292</v>
       </c>
       <c r="I105" t="n">
-        <v>27.88</v>
+        <v>22.5</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L105" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>신금호</t>
+          <t>신길</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4870,31 +4870,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>184048</v>
+        <v>140429</v>
       </c>
       <c r="D106" t="n">
-        <v>40032</v>
+        <v>12815</v>
       </c>
       <c r="E106" t="n">
-        <v>194994</v>
+        <v>144543</v>
       </c>
       <c r="F106" t="n">
-        <v>45260</v>
+        <v>13241</v>
       </c>
       <c r="G106" t="n">
-        <v>379042</v>
+        <v>284972</v>
       </c>
       <c r="H106" t="n">
-        <v>85292</v>
+        <v>26056</v>
       </c>
       <c r="I106" t="n">
-        <v>22.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L106" t="n">
         <v>15</v>
@@ -4903,7 +4903,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>신길</t>
+          <t>신정</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4912,40 +4912,40 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>140429</v>
+        <v>386339</v>
       </c>
       <c r="D107" t="n">
-        <v>12815</v>
+        <v>67243</v>
       </c>
       <c r="E107" t="n">
-        <v>144543</v>
+        <v>322966</v>
       </c>
       <c r="F107" t="n">
-        <v>13241</v>
+        <v>65125</v>
       </c>
       <c r="G107" t="n">
-        <v>284972</v>
+        <v>709305</v>
       </c>
       <c r="H107" t="n">
-        <v>26056</v>
+        <v>132368</v>
       </c>
       <c r="I107" t="n">
-        <v>9.140000000000001</v>
+        <v>18.66</v>
       </c>
       <c r="J107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L107" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>신정</t>
+          <t>아차산</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4954,40 +4954,40 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>386339</v>
+        <v>443991</v>
       </c>
       <c r="D108" t="n">
-        <v>67243</v>
+        <v>107459</v>
       </c>
       <c r="E108" t="n">
-        <v>322966</v>
+        <v>431490</v>
       </c>
       <c r="F108" t="n">
-        <v>65125</v>
+        <v>104831</v>
       </c>
       <c r="G108" t="n">
-        <v>709305</v>
+        <v>875481</v>
       </c>
       <c r="H108" t="n">
-        <v>132368</v>
+        <v>212290</v>
       </c>
       <c r="I108" t="n">
-        <v>18.66</v>
+        <v>24.25</v>
       </c>
       <c r="J108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>아차산</t>
+          <t>애오개</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4996,31 +4996,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>443991</v>
+        <v>191333</v>
       </c>
       <c r="D109" t="n">
-        <v>107459</v>
+        <v>40245</v>
       </c>
       <c r="E109" t="n">
-        <v>431490</v>
+        <v>187395</v>
       </c>
       <c r="F109" t="n">
-        <v>104831</v>
+        <v>38796</v>
       </c>
       <c r="G109" t="n">
-        <v>875481</v>
+        <v>378728</v>
       </c>
       <c r="H109" t="n">
-        <v>212290</v>
+        <v>79041</v>
       </c>
       <c r="I109" t="n">
-        <v>24.25</v>
+        <v>20.87</v>
       </c>
       <c r="J109" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>11</v>
@@ -5029,7 +5029,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>애오개</t>
+          <t>양평</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5038,31 +5038,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>191333</v>
+        <v>217500</v>
       </c>
       <c r="D110" t="n">
-        <v>40245</v>
+        <v>31548</v>
       </c>
       <c r="E110" t="n">
-        <v>187395</v>
+        <v>211295</v>
       </c>
       <c r="F110" t="n">
-        <v>38796</v>
+        <v>31034</v>
       </c>
       <c r="G110" t="n">
-        <v>378728</v>
+        <v>428795</v>
       </c>
       <c r="H110" t="n">
-        <v>79041</v>
+        <v>62582</v>
       </c>
       <c r="I110" t="n">
-        <v>20.87</v>
+        <v>14.59</v>
       </c>
       <c r="J110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L110" t="n">
         <v>11</v>
@@ -5071,7 +5071,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>양평</t>
+          <t>여의나루</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5080,40 +5080,40 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>217500</v>
+        <v>412094</v>
       </c>
       <c r="D111" t="n">
-        <v>31548</v>
+        <v>33235</v>
       </c>
       <c r="E111" t="n">
-        <v>211295</v>
+        <v>470524</v>
       </c>
       <c r="F111" t="n">
-        <v>31034</v>
+        <v>32782</v>
       </c>
       <c r="G111" t="n">
-        <v>428795</v>
+        <v>882618</v>
       </c>
       <c r="H111" t="n">
-        <v>62582</v>
+        <v>66017</v>
       </c>
       <c r="I111" t="n">
-        <v>14.59</v>
+        <v>7.48</v>
       </c>
       <c r="J111" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K111" t="n">
         <v>3</v>
       </c>
       <c r="L111" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>여의나루</t>
+          <t>영등포시장</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5122,40 +5122,40 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>412094</v>
+        <v>337898</v>
       </c>
       <c r="D112" t="n">
-        <v>33235</v>
+        <v>79894</v>
       </c>
       <c r="E112" t="n">
-        <v>470524</v>
+        <v>342868</v>
       </c>
       <c r="F112" t="n">
-        <v>32782</v>
+        <v>81581</v>
       </c>
       <c r="G112" t="n">
-        <v>882618</v>
+        <v>680766</v>
       </c>
       <c r="H112" t="n">
-        <v>66017</v>
+        <v>161475</v>
       </c>
       <c r="I112" t="n">
-        <v>7.48</v>
+        <v>23.72</v>
       </c>
       <c r="J112" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K112" t="n">
         <v>3</v>
       </c>
       <c r="L112" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>영등포시장</t>
+          <t>오목교</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5164,40 +5164,40 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>337898</v>
+        <v>619344</v>
       </c>
       <c r="D113" t="n">
-        <v>79894</v>
+        <v>93232</v>
       </c>
       <c r="E113" t="n">
-        <v>342868</v>
+        <v>653117</v>
       </c>
       <c r="F113" t="n">
-        <v>81581</v>
+        <v>92509</v>
       </c>
       <c r="G113" t="n">
-        <v>680766</v>
+        <v>1272461</v>
       </c>
       <c r="H113" t="n">
-        <v>161475</v>
+        <v>185741</v>
       </c>
       <c r="I113" t="n">
-        <v>23.72</v>
+        <v>14.6</v>
       </c>
       <c r="J113" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K113" t="n">
         <v>3</v>
       </c>
       <c r="L113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>오목교</t>
+          <t>올림픽공원</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5206,40 +5206,40 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>619344</v>
+        <v>162308</v>
       </c>
       <c r="D114" t="n">
-        <v>93232</v>
+        <v>41571</v>
       </c>
       <c r="E114" t="n">
-        <v>653117</v>
+        <v>144586</v>
       </c>
       <c r="F114" t="n">
-        <v>92509</v>
+        <v>36964</v>
       </c>
       <c r="G114" t="n">
-        <v>1272461</v>
+        <v>306894</v>
       </c>
       <c r="H114" t="n">
-        <v>185741</v>
+        <v>78535</v>
       </c>
       <c r="I114" t="n">
-        <v>14.6</v>
+        <v>25.59</v>
       </c>
       <c r="J114" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K114" t="n">
         <v>3</v>
       </c>
       <c r="L114" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>올림픽공원</t>
+          <t>우장산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5248,25 +5248,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>162308</v>
+        <v>427755</v>
       </c>
       <c r="D115" t="n">
-        <v>41571</v>
+        <v>101202</v>
       </c>
       <c r="E115" t="n">
-        <v>144586</v>
+        <v>423688</v>
       </c>
       <c r="F115" t="n">
-        <v>36964</v>
+        <v>105280</v>
       </c>
       <c r="G115" t="n">
-        <v>306894</v>
+        <v>851443</v>
       </c>
       <c r="H115" t="n">
-        <v>78535</v>
+        <v>206482</v>
       </c>
       <c r="I115" t="n">
-        <v>25.59</v>
+        <v>24.25</v>
       </c>
       <c r="J115" t="n">
         <v>4</v>
@@ -5281,7 +5281,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>우장산</t>
+          <t>장한평</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5290,25 +5290,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>427755</v>
+        <v>551537</v>
       </c>
       <c r="D116" t="n">
-        <v>101202</v>
+        <v>101379</v>
       </c>
       <c r="E116" t="n">
-        <v>423688</v>
+        <v>544629</v>
       </c>
       <c r="F116" t="n">
-        <v>105280</v>
+        <v>103383</v>
       </c>
       <c r="G116" t="n">
-        <v>851443</v>
+        <v>1096166</v>
       </c>
       <c r="H116" t="n">
-        <v>206482</v>
+        <v>204762</v>
       </c>
       <c r="I116" t="n">
-        <v>24.25</v>
+        <v>18.68</v>
       </c>
       <c r="J116" t="n">
         <v>4</v>
@@ -5323,7 +5323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>장한평</t>
+          <t>행당</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5332,40 +5332,40 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>551537</v>
+        <v>233829</v>
       </c>
       <c r="D117" t="n">
-        <v>101379</v>
+        <v>53073</v>
       </c>
       <c r="E117" t="n">
-        <v>544629</v>
+        <v>207738</v>
       </c>
       <c r="F117" t="n">
-        <v>103383</v>
+        <v>48025</v>
       </c>
       <c r="G117" t="n">
-        <v>1096166</v>
+        <v>441567</v>
       </c>
       <c r="H117" t="n">
-        <v>204762</v>
+        <v>101098</v>
       </c>
       <c r="I117" t="n">
-        <v>18.68</v>
+        <v>22.9</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K117" t="n">
         <v>3</v>
       </c>
       <c r="L117" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>행당</t>
+          <t>화곡</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5374,82 +5374,82 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>233829</v>
+        <v>826102</v>
       </c>
       <c r="D118" t="n">
-        <v>53073</v>
+        <v>155956</v>
       </c>
       <c r="E118" t="n">
-        <v>207738</v>
+        <v>769286</v>
       </c>
       <c r="F118" t="n">
-        <v>48025</v>
+        <v>149325</v>
       </c>
       <c r="G118" t="n">
-        <v>441567</v>
+        <v>1595388</v>
       </c>
       <c r="H118" t="n">
-        <v>101098</v>
+        <v>305281</v>
       </c>
       <c r="I118" t="n">
-        <v>22.9</v>
+        <v>19.14</v>
       </c>
       <c r="J118" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L118" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>화곡</t>
+          <t>고려대</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>826102</v>
+        <v>260067</v>
       </c>
       <c r="D119" t="n">
-        <v>155956</v>
+        <v>36577</v>
       </c>
       <c r="E119" t="n">
-        <v>769286</v>
+        <v>249432</v>
       </c>
       <c r="F119" t="n">
-        <v>149325</v>
+        <v>35940</v>
       </c>
       <c r="G119" t="n">
-        <v>1595388</v>
+        <v>509499</v>
       </c>
       <c r="H119" t="n">
-        <v>305281</v>
+        <v>72517</v>
       </c>
       <c r="I119" t="n">
-        <v>19.14</v>
+        <v>14.23</v>
       </c>
       <c r="J119" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L119" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>고려대</t>
+          <t>광흥창</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5458,40 +5458,40 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>260067</v>
+        <v>271530</v>
       </c>
       <c r="D120" t="n">
-        <v>36577</v>
+        <v>56070</v>
       </c>
       <c r="E120" t="n">
-        <v>249432</v>
+        <v>260009</v>
       </c>
       <c r="F120" t="n">
-        <v>35940</v>
+        <v>55268</v>
       </c>
       <c r="G120" t="n">
-        <v>509499</v>
+        <v>531539</v>
       </c>
       <c r="H120" t="n">
-        <v>72517</v>
+        <v>111338</v>
       </c>
       <c r="I120" t="n">
-        <v>14.23</v>
+        <v>20.95</v>
       </c>
       <c r="J120" t="n">
+        <v>9</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3</v>
+      </c>
+      <c r="L120" t="n">
         <v>12</v>
-      </c>
-      <c r="K120" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>광흥창</t>
+          <t>구산</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5500,40 +5500,40 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>271530</v>
+        <v>237080</v>
       </c>
       <c r="D121" t="n">
-        <v>56070</v>
+        <v>57105</v>
       </c>
       <c r="E121" t="n">
-        <v>260009</v>
+        <v>180593</v>
       </c>
       <c r="F121" t="n">
-        <v>55268</v>
+        <v>59481</v>
       </c>
       <c r="G121" t="n">
-        <v>531539</v>
+        <v>417673</v>
       </c>
       <c r="H121" t="n">
-        <v>111338</v>
+        <v>116586</v>
       </c>
       <c r="I121" t="n">
-        <v>20.95</v>
+        <v>27.91</v>
       </c>
       <c r="J121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>구산</t>
+          <t>녹사평</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5542,40 +5542,40 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>237080</v>
+        <v>157571</v>
       </c>
       <c r="D122" t="n">
-        <v>57105</v>
+        <v>18590</v>
       </c>
       <c r="E122" t="n">
-        <v>180593</v>
+        <v>160969</v>
       </c>
       <c r="F122" t="n">
-        <v>59481</v>
+        <v>18149</v>
       </c>
       <c r="G122" t="n">
-        <v>417673</v>
+        <v>318540</v>
       </c>
       <c r="H122" t="n">
-        <v>116586</v>
+        <v>36739</v>
       </c>
       <c r="I122" t="n">
-        <v>27.91</v>
+        <v>11.53</v>
       </c>
       <c r="J122" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>녹사평</t>
+          <t>대흥</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5584,40 +5584,40 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>157571</v>
+        <v>270622</v>
       </c>
       <c r="D123" t="n">
-        <v>18590</v>
+        <v>49384</v>
       </c>
       <c r="E123" t="n">
-        <v>160969</v>
+        <v>281582</v>
       </c>
       <c r="F123" t="n">
-        <v>18149</v>
+        <v>49193</v>
       </c>
       <c r="G123" t="n">
-        <v>318540</v>
+        <v>552204</v>
       </c>
       <c r="H123" t="n">
-        <v>36739</v>
+        <v>98577</v>
       </c>
       <c r="I123" t="n">
-        <v>11.53</v>
+        <v>17.85</v>
       </c>
       <c r="J123" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K123" t="n">
         <v>3</v>
       </c>
       <c r="L123" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>대흥</t>
+          <t>독바위</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5626,40 +5626,40 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>270622</v>
+        <v>80401</v>
       </c>
       <c r="D124" t="n">
-        <v>49384</v>
+        <v>21437</v>
       </c>
       <c r="E124" t="n">
-        <v>281582</v>
+        <v>84959</v>
       </c>
       <c r="F124" t="n">
-        <v>49193</v>
+        <v>26395</v>
       </c>
       <c r="G124" t="n">
-        <v>552204</v>
+        <v>165360</v>
       </c>
       <c r="H124" t="n">
-        <v>98577</v>
+        <v>47832</v>
       </c>
       <c r="I124" t="n">
-        <v>17.85</v>
+        <v>28.93</v>
       </c>
       <c r="J124" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>독바위</t>
+          <t>돌곶이</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5668,40 +5668,40 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>80401</v>
+        <v>304544</v>
       </c>
       <c r="D125" t="n">
-        <v>21437</v>
+        <v>66060</v>
       </c>
       <c r="E125" t="n">
-        <v>84959</v>
+        <v>280650</v>
       </c>
       <c r="F125" t="n">
-        <v>26395</v>
+        <v>65110</v>
       </c>
       <c r="G125" t="n">
-        <v>165360</v>
+        <v>585194</v>
       </c>
       <c r="H125" t="n">
-        <v>47832</v>
+        <v>131170</v>
       </c>
       <c r="I125" t="n">
-        <v>28.93</v>
+        <v>22.41</v>
       </c>
       <c r="J125" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>돌곶이</t>
+          <t>디지털미디어시티</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5710,40 +5710,40 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>304544</v>
+        <v>414387</v>
       </c>
       <c r="D126" t="n">
-        <v>66060</v>
+        <v>61725</v>
       </c>
       <c r="E126" t="n">
-        <v>280650</v>
+        <v>446335</v>
       </c>
       <c r="F126" t="n">
-        <v>65110</v>
+        <v>62422</v>
       </c>
       <c r="G126" t="n">
-        <v>585194</v>
+        <v>860722</v>
       </c>
       <c r="H126" t="n">
-        <v>131170</v>
+        <v>124147</v>
       </c>
       <c r="I126" t="n">
-        <v>22.41</v>
+        <v>14.42</v>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K126" t="n">
         <v>3</v>
       </c>
       <c r="L126" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>디지털미디어시티</t>
+          <t>마포구청</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5752,40 +5752,40 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>414387</v>
+        <v>424134</v>
       </c>
       <c r="D127" t="n">
-        <v>61725</v>
+        <v>84007</v>
       </c>
       <c r="E127" t="n">
-        <v>446335</v>
+        <v>380124</v>
       </c>
       <c r="F127" t="n">
-        <v>62422</v>
+        <v>76784</v>
       </c>
       <c r="G127" t="n">
-        <v>860722</v>
+        <v>804258</v>
       </c>
       <c r="H127" t="n">
-        <v>124147</v>
+        <v>160791</v>
       </c>
       <c r="I127" t="n">
-        <v>14.42</v>
+        <v>19.99</v>
       </c>
       <c r="J127" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L127" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>마포구청</t>
+          <t>망원</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5794,40 +5794,40 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>424134</v>
+        <v>463783</v>
       </c>
       <c r="D128" t="n">
-        <v>84007</v>
+        <v>85481</v>
       </c>
       <c r="E128" t="n">
-        <v>380124</v>
+        <v>495333</v>
       </c>
       <c r="F128" t="n">
-        <v>76784</v>
+        <v>89100</v>
       </c>
       <c r="G128" t="n">
-        <v>804258</v>
+        <v>959116</v>
       </c>
       <c r="H128" t="n">
-        <v>160791</v>
+        <v>174581</v>
       </c>
       <c r="I128" t="n">
-        <v>19.99</v>
+        <v>18.2</v>
       </c>
       <c r="J128" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L128" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>망원</t>
+          <t>버티고개</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5836,40 +5836,40 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>463783</v>
+        <v>64186</v>
       </c>
       <c r="D129" t="n">
-        <v>85481</v>
+        <v>14604</v>
       </c>
       <c r="E129" t="n">
-        <v>495333</v>
+        <v>64434</v>
       </c>
       <c r="F129" t="n">
-        <v>89100</v>
+        <v>16701</v>
       </c>
       <c r="G129" t="n">
-        <v>959116</v>
+        <v>128620</v>
       </c>
       <c r="H129" t="n">
-        <v>174581</v>
+        <v>31305</v>
       </c>
       <c r="I129" t="n">
-        <v>18.2</v>
+        <v>24.34</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L129" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>버티고개</t>
+          <t>보문</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5878,40 +5878,40 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>64186</v>
+        <v>233704</v>
       </c>
       <c r="D130" t="n">
-        <v>14604</v>
+        <v>33040</v>
       </c>
       <c r="E130" t="n">
-        <v>64434</v>
+        <v>216693</v>
       </c>
       <c r="F130" t="n">
-        <v>16701</v>
+        <v>31271</v>
       </c>
       <c r="G130" t="n">
-        <v>128620</v>
+        <v>450397</v>
       </c>
       <c r="H130" t="n">
-        <v>31305</v>
+        <v>64311</v>
       </c>
       <c r="I130" t="n">
-        <v>24.34</v>
+        <v>14.28</v>
       </c>
       <c r="J130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>보문</t>
+          <t>봉화산</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5920,40 +5920,40 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>233704</v>
+        <v>251693</v>
       </c>
       <c r="D131" t="n">
-        <v>33040</v>
+        <v>52991</v>
       </c>
       <c r="E131" t="n">
-        <v>216693</v>
+        <v>237028</v>
       </c>
       <c r="F131" t="n">
-        <v>31271</v>
+        <v>52273</v>
       </c>
       <c r="G131" t="n">
-        <v>450397</v>
+        <v>488721</v>
       </c>
       <c r="H131" t="n">
-        <v>64311</v>
+        <v>105264</v>
       </c>
       <c r="I131" t="n">
-        <v>14.28</v>
+        <v>21.54</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L131" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>봉화산</t>
+          <t>상수</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5962,40 +5962,40 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>251693</v>
+        <v>309088</v>
       </c>
       <c r="D132" t="n">
-        <v>52991</v>
+        <v>22332</v>
       </c>
       <c r="E132" t="n">
-        <v>237028</v>
+        <v>349342</v>
       </c>
       <c r="F132" t="n">
-        <v>52273</v>
+        <v>22523</v>
       </c>
       <c r="G132" t="n">
-        <v>488721</v>
+        <v>658430</v>
       </c>
       <c r="H132" t="n">
-        <v>105264</v>
+        <v>44855</v>
       </c>
       <c r="I132" t="n">
-        <v>21.54</v>
+        <v>6.81</v>
       </c>
       <c r="J132" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L132" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>상수</t>
+          <t>상월곡</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6004,40 +6004,40 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>309088</v>
+        <v>191565</v>
       </c>
       <c r="D133" t="n">
-        <v>22332</v>
+        <v>43040</v>
       </c>
       <c r="E133" t="n">
-        <v>349342</v>
+        <v>175356</v>
       </c>
       <c r="F133" t="n">
-        <v>22523</v>
+        <v>41637</v>
       </c>
       <c r="G133" t="n">
-        <v>658430</v>
+        <v>366921</v>
       </c>
       <c r="H133" t="n">
-        <v>44855</v>
+        <v>84677</v>
       </c>
       <c r="I133" t="n">
-        <v>6.81</v>
+        <v>23.08</v>
       </c>
       <c r="J133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K133" t="n">
         <v>3</v>
       </c>
       <c r="L133" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>상월곡</t>
+          <t>새절</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6046,40 +6046,40 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>191565</v>
+        <v>370343</v>
       </c>
       <c r="D134" t="n">
-        <v>43040</v>
+        <v>92437</v>
       </c>
       <c r="E134" t="n">
-        <v>175356</v>
+        <v>345979</v>
       </c>
       <c r="F134" t="n">
-        <v>41637</v>
+        <v>92578</v>
       </c>
       <c r="G134" t="n">
-        <v>366921</v>
+        <v>716322</v>
       </c>
       <c r="H134" t="n">
-        <v>84677</v>
+        <v>185015</v>
       </c>
       <c r="I134" t="n">
-        <v>23.08</v>
+        <v>25.83</v>
       </c>
       <c r="J134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K134" t="n">
         <v>3</v>
       </c>
       <c r="L134" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>새절</t>
+          <t>석계</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6088,40 +6088,40 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>370343</v>
+        <v>361930</v>
       </c>
       <c r="D135" t="n">
-        <v>92437</v>
+        <v>83289</v>
       </c>
       <c r="E135" t="n">
-        <v>345979</v>
+        <v>370835</v>
       </c>
       <c r="F135" t="n">
-        <v>92578</v>
+        <v>82848</v>
       </c>
       <c r="G135" t="n">
-        <v>716322</v>
+        <v>732765</v>
       </c>
       <c r="H135" t="n">
-        <v>185015</v>
+        <v>166137</v>
       </c>
       <c r="I135" t="n">
-        <v>25.83</v>
+        <v>22.67</v>
       </c>
       <c r="J135" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L135" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>석계</t>
+          <t>안암</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6130,40 +6130,40 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>361930</v>
+        <v>375092</v>
       </c>
       <c r="D136" t="n">
-        <v>83289</v>
+        <v>38686</v>
       </c>
       <c r="E136" t="n">
-        <v>370835</v>
+        <v>375991</v>
       </c>
       <c r="F136" t="n">
-        <v>82848</v>
+        <v>38045</v>
       </c>
       <c r="G136" t="n">
-        <v>732765</v>
+        <v>751083</v>
       </c>
       <c r="H136" t="n">
-        <v>166137</v>
+        <v>76731</v>
       </c>
       <c r="I136" t="n">
-        <v>22.67</v>
+        <v>10.22</v>
       </c>
       <c r="J136" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L136" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>안암</t>
+          <t>역촌</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6172,40 +6172,40 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>375092</v>
+        <v>111649</v>
       </c>
       <c r="D137" t="n">
-        <v>38686</v>
+        <v>35325</v>
       </c>
       <c r="E137" t="n">
-        <v>375991</v>
+        <v>131103</v>
       </c>
       <c r="F137" t="n">
-        <v>38045</v>
+        <v>34793</v>
       </c>
       <c r="G137" t="n">
-        <v>751083</v>
+        <v>242752</v>
       </c>
       <c r="H137" t="n">
-        <v>76731</v>
+        <v>70118</v>
       </c>
       <c r="I137" t="n">
-        <v>10.22</v>
+        <v>28.88</v>
       </c>
       <c r="J137" t="n">
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>역촌</t>
+          <t>월곡</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6214,40 +6214,40 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>111649</v>
+        <v>348950</v>
       </c>
       <c r="D138" t="n">
-        <v>35325</v>
+        <v>71839</v>
       </c>
       <c r="E138" t="n">
-        <v>131103</v>
+        <v>338516</v>
       </c>
       <c r="F138" t="n">
-        <v>34793</v>
+        <v>71162</v>
       </c>
       <c r="G138" t="n">
-        <v>242752</v>
+        <v>687466</v>
       </c>
       <c r="H138" t="n">
-        <v>70118</v>
+        <v>143001</v>
       </c>
       <c r="I138" t="n">
-        <v>28.88</v>
+        <v>20.8</v>
       </c>
       <c r="J138" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>월곡</t>
+          <t>월드컵경기장</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6256,25 +6256,25 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>348950</v>
+        <v>185256</v>
       </c>
       <c r="D139" t="n">
-        <v>71839</v>
+        <v>59852</v>
       </c>
       <c r="E139" t="n">
-        <v>338516</v>
+        <v>202141</v>
       </c>
       <c r="F139" t="n">
-        <v>71162</v>
+        <v>58781</v>
       </c>
       <c r="G139" t="n">
-        <v>687466</v>
+        <v>387397</v>
       </c>
       <c r="H139" t="n">
-        <v>143001</v>
+        <v>118633</v>
       </c>
       <c r="I139" t="n">
-        <v>20.8</v>
+        <v>30.62</v>
       </c>
       <c r="J139" t="n">
         <v>12</v>
@@ -6289,7 +6289,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>월드컵경기장</t>
+          <t>응암</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6298,40 +6298,40 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>185256</v>
+        <v>516764</v>
       </c>
       <c r="D140" t="n">
-        <v>59852</v>
+        <v>127624</v>
       </c>
       <c r="E140" t="n">
-        <v>202141</v>
+        <v>511157</v>
       </c>
       <c r="F140" t="n">
-        <v>58781</v>
+        <v>126704</v>
       </c>
       <c r="G140" t="n">
-        <v>387397</v>
+        <v>1027921</v>
       </c>
       <c r="H140" t="n">
-        <v>118633</v>
+        <v>254328</v>
       </c>
       <c r="I140" t="n">
-        <v>30.62</v>
+        <v>24.74</v>
       </c>
       <c r="J140" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L140" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>응암</t>
+          <t>이태원</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>516764</v>
+        <v>358734</v>
       </c>
       <c r="D141" t="n">
-        <v>127624</v>
+        <v>31504</v>
       </c>
       <c r="E141" t="n">
-        <v>511157</v>
+        <v>391713</v>
       </c>
       <c r="F141" t="n">
-        <v>126704</v>
+        <v>31889</v>
       </c>
       <c r="G141" t="n">
-        <v>1027921</v>
+        <v>750447</v>
       </c>
       <c r="H141" t="n">
-        <v>254328</v>
+        <v>63393</v>
       </c>
       <c r="I141" t="n">
-        <v>24.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J141" t="n">
         <v>4</v>
@@ -6373,7 +6373,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>이태원</t>
+          <t>증산</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6382,40 +6382,40 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>358734</v>
+        <v>284376</v>
       </c>
       <c r="D142" t="n">
-        <v>31504</v>
+        <v>74103</v>
       </c>
       <c r="E142" t="n">
-        <v>391713</v>
+        <v>282585</v>
       </c>
       <c r="F142" t="n">
-        <v>31889</v>
+        <v>74764</v>
       </c>
       <c r="G142" t="n">
-        <v>750447</v>
+        <v>566961</v>
       </c>
       <c r="H142" t="n">
-        <v>63393</v>
+        <v>148867</v>
       </c>
       <c r="I142" t="n">
-        <v>8.449999999999999</v>
+        <v>26.26</v>
       </c>
       <c r="J142" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>증산</t>
+          <t>창신</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6424,40 +6424,40 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>284376</v>
+        <v>103270</v>
       </c>
       <c r="D143" t="n">
-        <v>74103</v>
+        <v>19926</v>
       </c>
       <c r="E143" t="n">
-        <v>282585</v>
+        <v>87145</v>
       </c>
       <c r="F143" t="n">
-        <v>74764</v>
+        <v>18921</v>
       </c>
       <c r="G143" t="n">
-        <v>566961</v>
+        <v>190415</v>
       </c>
       <c r="H143" t="n">
-        <v>148867</v>
+        <v>38847</v>
       </c>
       <c r="I143" t="n">
-        <v>26.26</v>
+        <v>20.4</v>
       </c>
       <c r="J143" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K143" t="n">
         <v>3</v>
       </c>
       <c r="L143" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>창신</t>
+          <t>한강진</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6466,40 +6466,40 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>103270</v>
+        <v>302426</v>
       </c>
       <c r="D144" t="n">
-        <v>19926</v>
+        <v>20614</v>
       </c>
       <c r="E144" t="n">
-        <v>87145</v>
+        <v>354942</v>
       </c>
       <c r="F144" t="n">
-        <v>18921</v>
+        <v>20632</v>
       </c>
       <c r="G144" t="n">
-        <v>190415</v>
+        <v>657368</v>
       </c>
       <c r="H144" t="n">
-        <v>38847</v>
+        <v>41246</v>
       </c>
       <c r="I144" t="n">
-        <v>20.4</v>
+        <v>6.27</v>
       </c>
       <c r="J144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K144" t="n">
         <v>3</v>
       </c>
       <c r="L144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한강진</t>
+          <t>화랑대</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6508,40 +6508,40 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>302426</v>
+        <v>342753</v>
       </c>
       <c r="D145" t="n">
-        <v>20614</v>
+        <v>51768</v>
       </c>
       <c r="E145" t="n">
-        <v>354942</v>
+        <v>273727</v>
       </c>
       <c r="F145" t="n">
-        <v>20632</v>
+        <v>46797</v>
       </c>
       <c r="G145" t="n">
-        <v>657368</v>
+        <v>616480</v>
       </c>
       <c r="H145" t="n">
-        <v>41246</v>
+        <v>98565</v>
       </c>
       <c r="I145" t="n">
-        <v>6.27</v>
+        <v>15.99</v>
       </c>
       <c r="J145" t="n">
         <v>4</v>
       </c>
       <c r="K145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L145" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>화랑대</t>
+          <t>효창공원앞</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6550,82 +6550,82 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>342753</v>
+        <v>218774</v>
       </c>
       <c r="D146" t="n">
-        <v>51768</v>
+        <v>39969</v>
       </c>
       <c r="E146" t="n">
-        <v>273727</v>
+        <v>199665</v>
       </c>
       <c r="F146" t="n">
-        <v>46797</v>
+        <v>37000</v>
       </c>
       <c r="G146" t="n">
-        <v>616480</v>
+        <v>418439</v>
       </c>
       <c r="H146" t="n">
-        <v>98565</v>
+        <v>76969</v>
       </c>
       <c r="I146" t="n">
-        <v>15.99</v>
+        <v>18.39</v>
       </c>
       <c r="J146" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>효창공원앞</t>
+          <t>가산디지털단지</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>218774</v>
+        <v>1154477</v>
       </c>
       <c r="D147" t="n">
-        <v>39969</v>
+        <v>98985</v>
       </c>
       <c r="E147" t="n">
-        <v>199665</v>
+        <v>1150220</v>
       </c>
       <c r="F147" t="n">
-        <v>37000</v>
+        <v>93082</v>
       </c>
       <c r="G147" t="n">
-        <v>418439</v>
+        <v>2304697</v>
       </c>
       <c r="H147" t="n">
-        <v>76969</v>
+        <v>192067</v>
       </c>
       <c r="I147" t="n">
-        <v>18.39</v>
+        <v>8.33</v>
       </c>
       <c r="J147" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L147" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>가산디지털단지</t>
+          <t>강남구청</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6634,40 +6634,40 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1154477</v>
+        <v>453643</v>
       </c>
       <c r="D148" t="n">
-        <v>98985</v>
+        <v>54065</v>
       </c>
       <c r="E148" t="n">
-        <v>1150220</v>
+        <v>502605</v>
       </c>
       <c r="F148" t="n">
-        <v>93082</v>
+        <v>55199</v>
       </c>
       <c r="G148" t="n">
-        <v>2304697</v>
+        <v>956248</v>
       </c>
       <c r="H148" t="n">
-        <v>192067</v>
+        <v>109264</v>
       </c>
       <c r="I148" t="n">
-        <v>8.33</v>
+        <v>11.43</v>
       </c>
       <c r="J148" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L148" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>강남구청</t>
+          <t>공릉</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6676,40 +6676,40 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>453643</v>
+        <v>359567</v>
       </c>
       <c r="D149" t="n">
-        <v>54065</v>
+        <v>77921</v>
       </c>
       <c r="E149" t="n">
-        <v>502605</v>
+        <v>354017</v>
       </c>
       <c r="F149" t="n">
-        <v>55199</v>
+        <v>78409</v>
       </c>
       <c r="G149" t="n">
-        <v>956248</v>
+        <v>713584</v>
       </c>
       <c r="H149" t="n">
-        <v>109264</v>
+        <v>156330</v>
       </c>
       <c r="I149" t="n">
-        <v>11.43</v>
+        <v>21.91</v>
       </c>
       <c r="J149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>공릉</t>
+          <t>남구로</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6718,40 +6718,40 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>359567</v>
+        <v>420412</v>
       </c>
       <c r="D150" t="n">
-        <v>77921</v>
+        <v>65887</v>
       </c>
       <c r="E150" t="n">
-        <v>354017</v>
+        <v>439155</v>
       </c>
       <c r="F150" t="n">
-        <v>78409</v>
+        <v>66688</v>
       </c>
       <c r="G150" t="n">
-        <v>713584</v>
+        <v>859567</v>
       </c>
       <c r="H150" t="n">
-        <v>156330</v>
+        <v>132575</v>
       </c>
       <c r="I150" t="n">
-        <v>21.91</v>
+        <v>15.42</v>
       </c>
       <c r="J150" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K150" t="n">
         <v>3</v>
       </c>
       <c r="L150" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>남구로</t>
+          <t>남성</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6760,40 +6760,40 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>420412</v>
+        <v>331097</v>
       </c>
       <c r="D151" t="n">
-        <v>65887</v>
+        <v>78978</v>
       </c>
       <c r="E151" t="n">
-        <v>439155</v>
+        <v>313447</v>
       </c>
       <c r="F151" t="n">
-        <v>66688</v>
+        <v>79144</v>
       </c>
       <c r="G151" t="n">
-        <v>859567</v>
+        <v>644544</v>
       </c>
       <c r="H151" t="n">
-        <v>132575</v>
+        <v>158122</v>
       </c>
       <c r="I151" t="n">
-        <v>15.42</v>
+        <v>24.53</v>
       </c>
       <c r="J151" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L151" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>남성</t>
+          <t>내방</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6802,40 +6802,40 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>331097</v>
+        <v>410799</v>
       </c>
       <c r="D152" t="n">
-        <v>78978</v>
+        <v>76953</v>
       </c>
       <c r="E152" t="n">
-        <v>313447</v>
+        <v>413573</v>
       </c>
       <c r="F152" t="n">
-        <v>79144</v>
+        <v>74244</v>
       </c>
       <c r="G152" t="n">
-        <v>644544</v>
+        <v>824372</v>
       </c>
       <c r="H152" t="n">
-        <v>158122</v>
+        <v>151197</v>
       </c>
       <c r="I152" t="n">
-        <v>24.53</v>
+        <v>18.34</v>
       </c>
       <c r="J152" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L152" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>내방</t>
+          <t>논현</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6844,40 +6844,40 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>410799</v>
+        <v>512327</v>
       </c>
       <c r="D153" t="n">
-        <v>76953</v>
+        <v>45626</v>
       </c>
       <c r="E153" t="n">
-        <v>413573</v>
+        <v>531407</v>
       </c>
       <c r="F153" t="n">
-        <v>74244</v>
+        <v>44584</v>
       </c>
       <c r="G153" t="n">
-        <v>824372</v>
+        <v>1043734</v>
       </c>
       <c r="H153" t="n">
-        <v>151197</v>
+        <v>90210</v>
       </c>
       <c r="I153" t="n">
-        <v>18.34</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L153" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>논현</t>
+          <t>도봉산</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6886,40 +6886,40 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>512327</v>
+        <v>263297</v>
       </c>
       <c r="D154" t="n">
-        <v>45626</v>
+        <v>52765</v>
       </c>
       <c r="E154" t="n">
-        <v>531407</v>
+        <v>312768</v>
       </c>
       <c r="F154" t="n">
-        <v>44584</v>
+        <v>74776</v>
       </c>
       <c r="G154" t="n">
-        <v>1043734</v>
+        <v>576065</v>
       </c>
       <c r="H154" t="n">
-        <v>90210</v>
+        <v>127541</v>
       </c>
       <c r="I154" t="n">
-        <v>8.640000000000001</v>
+        <v>22.14</v>
       </c>
       <c r="J154" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L154" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>도봉산</t>
+          <t>마들</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6928,40 +6928,40 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>263297</v>
+        <v>382194</v>
       </c>
       <c r="D155" t="n">
-        <v>52765</v>
+        <v>96782</v>
       </c>
       <c r="E155" t="n">
-        <v>312768</v>
+        <v>358622</v>
       </c>
       <c r="F155" t="n">
-        <v>74776</v>
+        <v>94945</v>
       </c>
       <c r="G155" t="n">
-        <v>576065</v>
+        <v>740816</v>
       </c>
       <c r="H155" t="n">
-        <v>127541</v>
+        <v>191727</v>
       </c>
       <c r="I155" t="n">
-        <v>22.14</v>
+        <v>25.88</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L155" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>마들</t>
+          <t>먹골</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6970,40 +6970,40 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>382194</v>
+        <v>299231</v>
       </c>
       <c r="D156" t="n">
-        <v>96782</v>
+        <v>71685</v>
       </c>
       <c r="E156" t="n">
-        <v>358622</v>
+        <v>295255</v>
       </c>
       <c r="F156" t="n">
-        <v>94945</v>
+        <v>73234</v>
       </c>
       <c r="G156" t="n">
-        <v>740816</v>
+        <v>594486</v>
       </c>
       <c r="H156" t="n">
-        <v>191727</v>
+        <v>144919</v>
       </c>
       <c r="I156" t="n">
-        <v>25.88</v>
+        <v>24.38</v>
       </c>
       <c r="J156" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L156" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>먹골</t>
+          <t>면목</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7012,25 +7012,25 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>299231</v>
+        <v>440555</v>
       </c>
       <c r="D157" t="n">
-        <v>71685</v>
+        <v>101218</v>
       </c>
       <c r="E157" t="n">
-        <v>295255</v>
+        <v>422568</v>
       </c>
       <c r="F157" t="n">
-        <v>73234</v>
+        <v>103791</v>
       </c>
       <c r="G157" t="n">
-        <v>594486</v>
+        <v>863123</v>
       </c>
       <c r="H157" t="n">
-        <v>144919</v>
+        <v>205009</v>
       </c>
       <c r="I157" t="n">
-        <v>24.38</v>
+        <v>23.75</v>
       </c>
       <c r="J157" t="n">
         <v>6</v>
@@ -7045,7 +7045,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>면목</t>
+          <t>반포</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7054,40 +7054,40 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>440555</v>
+        <v>187796</v>
       </c>
       <c r="D158" t="n">
-        <v>101218</v>
+        <v>40370</v>
       </c>
       <c r="E158" t="n">
-        <v>422568</v>
+        <v>180173</v>
       </c>
       <c r="F158" t="n">
-        <v>103791</v>
+        <v>38386</v>
       </c>
       <c r="G158" t="n">
-        <v>863123</v>
+        <v>367969</v>
       </c>
       <c r="H158" t="n">
-        <v>205009</v>
+        <v>78756</v>
       </c>
       <c r="I158" t="n">
-        <v>23.75</v>
+        <v>21.4</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>반포</t>
+          <t>보라매</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7096,40 +7096,40 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>187796</v>
+        <v>198046</v>
       </c>
       <c r="D159" t="n">
-        <v>40370</v>
+        <v>33269</v>
       </c>
       <c r="E159" t="n">
-        <v>180173</v>
+        <v>204920</v>
       </c>
       <c r="F159" t="n">
-        <v>38386</v>
+        <v>34464</v>
       </c>
       <c r="G159" t="n">
-        <v>367969</v>
+        <v>402966</v>
       </c>
       <c r="H159" t="n">
-        <v>78756</v>
+        <v>67733</v>
       </c>
       <c r="I159" t="n">
-        <v>21.4</v>
+        <v>16.81</v>
       </c>
       <c r="J159" t="n">
+        <v>4</v>
+      </c>
+      <c r="K159" t="n">
+        <v>2</v>
+      </c>
+      <c r="L159" t="n">
         <v>6</v>
-      </c>
-      <c r="K159" t="n">
-        <v>4</v>
-      </c>
-      <c r="L159" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>보라매</t>
+          <t>사가정</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7138,40 +7138,40 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>198046</v>
+        <v>470061</v>
       </c>
       <c r="D160" t="n">
-        <v>33269</v>
+        <v>107704</v>
       </c>
       <c r="E160" t="n">
-        <v>204920</v>
+        <v>471938</v>
       </c>
       <c r="F160" t="n">
-        <v>34464</v>
+        <v>108645</v>
       </c>
       <c r="G160" t="n">
-        <v>402966</v>
+        <v>941999</v>
       </c>
       <c r="H160" t="n">
-        <v>67733</v>
+        <v>216349</v>
       </c>
       <c r="I160" t="n">
-        <v>16.81</v>
+        <v>22.97</v>
       </c>
       <c r="J160" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L160" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>사가정</t>
+          <t>상도</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7180,40 +7180,40 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>470061</v>
+        <v>350932</v>
       </c>
       <c r="D161" t="n">
-        <v>107704</v>
+        <v>66852</v>
       </c>
       <c r="E161" t="n">
-        <v>471938</v>
+        <v>342231</v>
       </c>
       <c r="F161" t="n">
-        <v>108645</v>
+        <v>63792</v>
       </c>
       <c r="G161" t="n">
-        <v>941999</v>
+        <v>693163</v>
       </c>
       <c r="H161" t="n">
-        <v>216349</v>
+        <v>130644</v>
       </c>
       <c r="I161" t="n">
-        <v>22.97</v>
+        <v>18.85</v>
       </c>
       <c r="J161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K161" t="n">
         <v>3</v>
       </c>
       <c r="L161" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>상도</t>
+          <t>상봉</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7222,40 +7222,40 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>350932</v>
+        <v>508844</v>
       </c>
       <c r="D162" t="n">
-        <v>66852</v>
+        <v>79993</v>
       </c>
       <c r="E162" t="n">
-        <v>342231</v>
+        <v>490653</v>
       </c>
       <c r="F162" t="n">
-        <v>63792</v>
+        <v>76640</v>
       </c>
       <c r="G162" t="n">
-        <v>693163</v>
+        <v>999497</v>
       </c>
       <c r="H162" t="n">
-        <v>130644</v>
+        <v>156633</v>
       </c>
       <c r="I162" t="n">
-        <v>18.85</v>
+        <v>15.67</v>
       </c>
       <c r="J162" t="n">
+        <v>6</v>
+      </c>
+      <c r="K162" t="n">
+        <v>5</v>
+      </c>
+      <c r="L162" t="n">
         <v>11</v>
-      </c>
-      <c r="K162" t="n">
-        <v>3</v>
-      </c>
-      <c r="L162" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>상봉</t>
+          <t>수락산</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7264,40 +7264,40 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>508844</v>
+        <v>370617</v>
       </c>
       <c r="D163" t="n">
-        <v>79993</v>
+        <v>106791</v>
       </c>
       <c r="E163" t="n">
-        <v>490653</v>
+        <v>364921</v>
       </c>
       <c r="F163" t="n">
-        <v>76640</v>
+        <v>108072</v>
       </c>
       <c r="G163" t="n">
-        <v>999497</v>
+        <v>735538</v>
       </c>
       <c r="H163" t="n">
-        <v>156633</v>
+        <v>214863</v>
       </c>
       <c r="I163" t="n">
-        <v>15.67</v>
+        <v>29.21</v>
       </c>
       <c r="J163" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>수락산</t>
+          <t>숭실대입구</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7306,40 +7306,40 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>370617</v>
+        <v>406478</v>
       </c>
       <c r="D164" t="n">
-        <v>106791</v>
+        <v>66974</v>
       </c>
       <c r="E164" t="n">
-        <v>364921</v>
+        <v>407617</v>
       </c>
       <c r="F164" t="n">
-        <v>108072</v>
+        <v>69178</v>
       </c>
       <c r="G164" t="n">
-        <v>735538</v>
+        <v>814095</v>
       </c>
       <c r="H164" t="n">
-        <v>214863</v>
+        <v>136152</v>
       </c>
       <c r="I164" t="n">
-        <v>29.21</v>
+        <v>16.72</v>
       </c>
       <c r="J164" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L164" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>숭실대입구</t>
+          <t>신대방삼거리</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7348,25 +7348,25 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>406478</v>
+        <v>433269</v>
       </c>
       <c r="D165" t="n">
-        <v>66974</v>
+        <v>95525</v>
       </c>
       <c r="E165" t="n">
-        <v>407617</v>
+        <v>414630</v>
       </c>
       <c r="F165" t="n">
-        <v>69178</v>
+        <v>98119</v>
       </c>
       <c r="G165" t="n">
-        <v>814095</v>
+        <v>847899</v>
       </c>
       <c r="H165" t="n">
-        <v>136152</v>
+        <v>193644</v>
       </c>
       <c r="I165" t="n">
-        <v>16.72</v>
+        <v>22.84</v>
       </c>
       <c r="J165" t="n">
         <v>12</v>
@@ -7381,7 +7381,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>신대방삼거리</t>
+          <t>신풍</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7390,40 +7390,40 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>433269</v>
+        <v>332724</v>
       </c>
       <c r="D166" t="n">
-        <v>95525</v>
+        <v>77373</v>
       </c>
       <c r="E166" t="n">
-        <v>414630</v>
+        <v>312174</v>
       </c>
       <c r="F166" t="n">
-        <v>98119</v>
+        <v>75981</v>
       </c>
       <c r="G166" t="n">
-        <v>847899</v>
+        <v>644898</v>
       </c>
       <c r="H166" t="n">
-        <v>193644</v>
+        <v>153354</v>
       </c>
       <c r="I166" t="n">
-        <v>22.84</v>
+        <v>23.78</v>
       </c>
       <c r="J166" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K166" t="n">
         <v>4</v>
       </c>
       <c r="L166" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>신풍</t>
+          <t>어린이대공원</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7432,40 +7432,40 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>332724</v>
+        <v>472469</v>
       </c>
       <c r="D167" t="n">
-        <v>77373</v>
+        <v>46385</v>
       </c>
       <c r="E167" t="n">
-        <v>312174</v>
+        <v>477982</v>
       </c>
       <c r="F167" t="n">
-        <v>75981</v>
+        <v>46060</v>
       </c>
       <c r="G167" t="n">
-        <v>644898</v>
+        <v>950451</v>
       </c>
       <c r="H167" t="n">
-        <v>153354</v>
+        <v>92445</v>
       </c>
       <c r="I167" t="n">
-        <v>23.78</v>
+        <v>9.73</v>
       </c>
       <c r="J167" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K167" t="n">
         <v>4</v>
       </c>
       <c r="L167" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>어린이대공원</t>
+          <t>온수</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7474,40 +7474,40 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>472469</v>
+        <v>283565</v>
       </c>
       <c r="D168" t="n">
-        <v>46385</v>
+        <v>44422</v>
       </c>
       <c r="E168" t="n">
-        <v>477982</v>
+        <v>262616</v>
       </c>
       <c r="F168" t="n">
-        <v>46060</v>
+        <v>42015</v>
       </c>
       <c r="G168" t="n">
-        <v>950451</v>
+        <v>546181</v>
       </c>
       <c r="H168" t="n">
-        <v>92445</v>
+        <v>86437</v>
       </c>
       <c r="I168" t="n">
-        <v>9.73</v>
+        <v>15.83</v>
       </c>
       <c r="J168" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L168" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>온수</t>
+          <t>용마산</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7516,40 +7516,40 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>283565</v>
+        <v>169622</v>
       </c>
       <c r="D169" t="n">
-        <v>44422</v>
+        <v>37080</v>
       </c>
       <c r="E169" t="n">
-        <v>262616</v>
+        <v>167384</v>
       </c>
       <c r="F169" t="n">
-        <v>42015</v>
+        <v>40314</v>
       </c>
       <c r="G169" t="n">
-        <v>546181</v>
+        <v>337006</v>
       </c>
       <c r="H169" t="n">
-        <v>86437</v>
+        <v>77394</v>
       </c>
       <c r="I169" t="n">
-        <v>15.83</v>
+        <v>22.97</v>
       </c>
       <c r="J169" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K169" t="n">
         <v>3</v>
       </c>
       <c r="L169" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>용마산</t>
+          <t>자양</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7558,40 +7558,40 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>169622</v>
+        <v>310455</v>
       </c>
       <c r="D170" t="n">
-        <v>37080</v>
+        <v>54109</v>
       </c>
       <c r="E170" t="n">
-        <v>167384</v>
+        <v>303841</v>
       </c>
       <c r="F170" t="n">
-        <v>40314</v>
+        <v>53962</v>
       </c>
       <c r="G170" t="n">
-        <v>337006</v>
+        <v>614296</v>
       </c>
       <c r="H170" t="n">
-        <v>77394</v>
+        <v>108071</v>
       </c>
       <c r="I170" t="n">
-        <v>22.97</v>
+        <v>17.59</v>
       </c>
       <c r="J170" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K170" t="n">
         <v>3</v>
       </c>
       <c r="L170" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>자양</t>
+          <t>장승배기</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7600,40 +7600,40 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>310455</v>
+        <v>269643</v>
       </c>
       <c r="D171" t="n">
-        <v>54109</v>
+        <v>71128</v>
       </c>
       <c r="E171" t="n">
-        <v>303841</v>
+        <v>262732</v>
       </c>
       <c r="F171" t="n">
-        <v>53962</v>
+        <v>71963</v>
       </c>
       <c r="G171" t="n">
-        <v>614296</v>
+        <v>532375</v>
       </c>
       <c r="H171" t="n">
-        <v>108071</v>
+        <v>143091</v>
       </c>
       <c r="I171" t="n">
-        <v>17.59</v>
+        <v>26.88</v>
       </c>
       <c r="J171" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K171" t="n">
         <v>3</v>
       </c>
       <c r="L171" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>장승배기</t>
+          <t>장암</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7642,40 +7642,40 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>269643</v>
+        <v>78394</v>
       </c>
       <c r="D172" t="n">
-        <v>71128</v>
+        <v>14236</v>
       </c>
       <c r="E172" t="n">
-        <v>262732</v>
+        <v>36704</v>
       </c>
       <c r="F172" t="n">
-        <v>71963</v>
+        <v>10906</v>
       </c>
       <c r="G172" t="n">
-        <v>532375</v>
+        <v>115098</v>
       </c>
       <c r="H172" t="n">
-        <v>143091</v>
+        <v>25142</v>
       </c>
       <c r="I172" t="n">
-        <v>26.88</v>
+        <v>21.84</v>
       </c>
       <c r="J172" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L172" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>장암</t>
+          <t>중계</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7684,40 +7684,40 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>78394</v>
+        <v>424768</v>
       </c>
       <c r="D173" t="n">
-        <v>14236</v>
+        <v>99732</v>
       </c>
       <c r="E173" t="n">
-        <v>36704</v>
+        <v>390462</v>
       </c>
       <c r="F173" t="n">
-        <v>10906</v>
+        <v>96522</v>
       </c>
       <c r="G173" t="n">
-        <v>115098</v>
+        <v>815230</v>
       </c>
       <c r="H173" t="n">
-        <v>25142</v>
+        <v>196254</v>
       </c>
       <c r="I173" t="n">
-        <v>21.84</v>
+        <v>24.07</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L173" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>중계</t>
+          <t>중곡</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7726,40 +7726,40 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>424768</v>
+        <v>315107</v>
       </c>
       <c r="D174" t="n">
-        <v>99732</v>
+        <v>68009</v>
       </c>
       <c r="E174" t="n">
-        <v>390462</v>
+        <v>296208</v>
       </c>
       <c r="F174" t="n">
-        <v>96522</v>
+        <v>68724</v>
       </c>
       <c r="G174" t="n">
-        <v>815230</v>
+        <v>611315</v>
       </c>
       <c r="H174" t="n">
-        <v>196254</v>
+        <v>136733</v>
       </c>
       <c r="I174" t="n">
-        <v>24.07</v>
+        <v>22.37</v>
       </c>
       <c r="J174" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K174" t="n">
         <v>3</v>
       </c>
       <c r="L174" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>중곡</t>
+          <t>중화</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7768,40 +7768,40 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>315107</v>
+        <v>312055</v>
       </c>
       <c r="D175" t="n">
-        <v>68009</v>
+        <v>68968</v>
       </c>
       <c r="E175" t="n">
-        <v>296208</v>
+        <v>304743</v>
       </c>
       <c r="F175" t="n">
-        <v>68724</v>
+        <v>68653</v>
       </c>
       <c r="G175" t="n">
-        <v>611315</v>
+        <v>616798</v>
       </c>
       <c r="H175" t="n">
-        <v>136733</v>
+        <v>137621</v>
       </c>
       <c r="I175" t="n">
-        <v>22.37</v>
+        <v>22.31</v>
       </c>
       <c r="J175" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K175" t="n">
         <v>3</v>
       </c>
       <c r="L175" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>중화</t>
+          <t>천왕</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7810,40 +7810,40 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>312055</v>
+        <v>330062</v>
       </c>
       <c r="D176" t="n">
-        <v>68968</v>
+        <v>63126</v>
       </c>
       <c r="E176" t="n">
-        <v>304743</v>
+        <v>316349</v>
       </c>
       <c r="F176" t="n">
-        <v>68653</v>
+        <v>63456</v>
       </c>
       <c r="G176" t="n">
-        <v>616798</v>
+        <v>646411</v>
       </c>
       <c r="H176" t="n">
-        <v>137621</v>
+        <v>126582</v>
       </c>
       <c r="I176" t="n">
-        <v>22.31</v>
+        <v>19.58</v>
       </c>
       <c r="J176" t="n">
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L176" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>천왕</t>
+          <t>청담</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7852,40 +7852,40 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>330062</v>
+        <v>524227</v>
       </c>
       <c r="D177" t="n">
-        <v>63126</v>
+        <v>79748</v>
       </c>
       <c r="E177" t="n">
-        <v>316349</v>
+        <v>571186</v>
       </c>
       <c r="F177" t="n">
-        <v>63456</v>
+        <v>76997</v>
       </c>
       <c r="G177" t="n">
-        <v>646411</v>
+        <v>1095413</v>
       </c>
       <c r="H177" t="n">
-        <v>126582</v>
+        <v>156745</v>
       </c>
       <c r="I177" t="n">
-        <v>19.58</v>
+        <v>14.31</v>
       </c>
       <c r="J177" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K177" t="n">
         <v>4</v>
       </c>
       <c r="L177" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>청담</t>
+          <t>하계</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7894,40 +7894,40 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>524227</v>
+        <v>526960</v>
       </c>
       <c r="D178" t="n">
-        <v>79748</v>
+        <v>118719</v>
       </c>
       <c r="E178" t="n">
-        <v>571186</v>
+        <v>493645</v>
       </c>
       <c r="F178" t="n">
-        <v>76997</v>
+        <v>114395</v>
       </c>
       <c r="G178" t="n">
-        <v>1095413</v>
+        <v>1020605</v>
       </c>
       <c r="H178" t="n">
-        <v>156745</v>
+        <v>233114</v>
       </c>
       <c r="I178" t="n">
-        <v>14.31</v>
+        <v>22.84</v>
       </c>
       <c r="J178" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L178" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>하계</t>
+          <t>학동</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7936,82 +7936,82 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>526960</v>
+        <v>637007</v>
       </c>
       <c r="D179" t="n">
-        <v>118719</v>
+        <v>65892</v>
       </c>
       <c r="E179" t="n">
-        <v>493645</v>
+        <v>664655</v>
       </c>
       <c r="F179" t="n">
-        <v>114395</v>
+        <v>62892</v>
       </c>
       <c r="G179" t="n">
-        <v>1020605</v>
+        <v>1301662</v>
       </c>
       <c r="H179" t="n">
-        <v>233114</v>
+        <v>128784</v>
       </c>
       <c r="I179" t="n">
-        <v>22.84</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K179" t="n">
         <v>3</v>
       </c>
       <c r="L179" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>학동</t>
+          <t>강동구청</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>637007</v>
+        <v>301276</v>
       </c>
       <c r="D180" t="n">
-        <v>65892</v>
+        <v>70703</v>
       </c>
       <c r="E180" t="n">
-        <v>664655</v>
+        <v>308602</v>
       </c>
       <c r="F180" t="n">
-        <v>62892</v>
+        <v>71501</v>
       </c>
       <c r="G180" t="n">
-        <v>1301662</v>
+        <v>609878</v>
       </c>
       <c r="H180" t="n">
-        <v>128784</v>
+        <v>142204</v>
       </c>
       <c r="I180" t="n">
-        <v>9.890000000000001</v>
+        <v>23.32</v>
       </c>
       <c r="J180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K180" t="n">
         <v>3</v>
       </c>
       <c r="L180" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>강동구청</t>
+          <t>몽촌토성</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8020,40 +8020,40 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>301276</v>
+        <v>206879</v>
       </c>
       <c r="D181" t="n">
-        <v>70703</v>
+        <v>36663</v>
       </c>
       <c r="E181" t="n">
-        <v>308602</v>
+        <v>210579</v>
       </c>
       <c r="F181" t="n">
-        <v>71501</v>
+        <v>36012</v>
       </c>
       <c r="G181" t="n">
-        <v>609878</v>
+        <v>417458</v>
       </c>
       <c r="H181" t="n">
-        <v>142204</v>
+        <v>72675</v>
       </c>
       <c r="I181" t="n">
-        <v>23.32</v>
+        <v>17.41</v>
       </c>
       <c r="J181" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L181" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>몽촌토성</t>
+          <t>문정</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8062,25 +8062,25 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>206879</v>
+        <v>595690</v>
       </c>
       <c r="D182" t="n">
-        <v>36663</v>
+        <v>66160</v>
       </c>
       <c r="E182" t="n">
-        <v>210579</v>
+        <v>620153</v>
       </c>
       <c r="F182" t="n">
-        <v>36012</v>
+        <v>66019</v>
       </c>
       <c r="G182" t="n">
-        <v>417458</v>
+        <v>1215843</v>
       </c>
       <c r="H182" t="n">
-        <v>72675</v>
+        <v>132179</v>
       </c>
       <c r="I182" t="n">
-        <v>17.41</v>
+        <v>10.87</v>
       </c>
       <c r="J182" t="n">
         <v>8</v>
@@ -8095,7 +8095,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>문정</t>
+          <t>석촌</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8104,40 +8104,40 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>595690</v>
+        <v>244204</v>
       </c>
       <c r="D183" t="n">
-        <v>66160</v>
+        <v>56741</v>
       </c>
       <c r="E183" t="n">
-        <v>620153</v>
+        <v>284699</v>
       </c>
       <c r="F183" t="n">
-        <v>66019</v>
+        <v>59743</v>
       </c>
       <c r="G183" t="n">
-        <v>1215843</v>
+        <v>528903</v>
       </c>
       <c r="H183" t="n">
-        <v>132179</v>
+        <v>116484</v>
       </c>
       <c r="I183" t="n">
-        <v>10.87</v>
+        <v>22.02</v>
       </c>
       <c r="J183" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L183" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>석촌</t>
+          <t>송파</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8146,40 +8146,40 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>244204</v>
+        <v>275169</v>
       </c>
       <c r="D184" t="n">
-        <v>56741</v>
+        <v>69511</v>
       </c>
       <c r="E184" t="n">
-        <v>284699</v>
+        <v>269774</v>
       </c>
       <c r="F184" t="n">
-        <v>59743</v>
+        <v>68579</v>
       </c>
       <c r="G184" t="n">
-        <v>528903</v>
+        <v>544943</v>
       </c>
       <c r="H184" t="n">
-        <v>116484</v>
+        <v>138090</v>
       </c>
       <c r="I184" t="n">
-        <v>22.02</v>
+        <v>25.34</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L184" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>송파</t>
+          <t>암사</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8188,40 +8188,40 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>275169</v>
+        <v>510235</v>
       </c>
       <c r="D185" t="n">
-        <v>69511</v>
+        <v>112483</v>
       </c>
       <c r="E185" t="n">
-        <v>269774</v>
+        <v>461278</v>
       </c>
       <c r="F185" t="n">
-        <v>68579</v>
+        <v>110725</v>
       </c>
       <c r="G185" t="n">
-        <v>544943</v>
+        <v>971513</v>
       </c>
       <c r="H185" t="n">
-        <v>138090</v>
+        <v>223208</v>
       </c>
       <c r="I185" t="n">
-        <v>25.34</v>
+        <v>22.98</v>
       </c>
       <c r="J185" t="n">
         <v>4</v>
       </c>
       <c r="K185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L185" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>암사</t>
+          <t>암사역사공원</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8230,40 +8230,40 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>510235</v>
+        <v>179560</v>
       </c>
       <c r="D186" t="n">
-        <v>112483</v>
+        <v>34333</v>
       </c>
       <c r="E186" t="n">
-        <v>461278</v>
+        <v>159043</v>
       </c>
       <c r="F186" t="n">
-        <v>110725</v>
+        <v>33319</v>
       </c>
       <c r="G186" t="n">
-        <v>971513</v>
+        <v>338603</v>
       </c>
       <c r="H186" t="n">
-        <v>223208</v>
+        <v>67652</v>
       </c>
       <c r="I186" t="n">
-        <v>22.98</v>
+        <v>19.98</v>
       </c>
       <c r="J186" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L186" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>암사역사공원</t>
+          <t>장지</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8272,82 +8272,82 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>179560</v>
+        <v>499917</v>
       </c>
       <c r="D187" t="n">
-        <v>34333</v>
+        <v>90185</v>
       </c>
       <c r="E187" t="n">
-        <v>159043</v>
+        <v>462047</v>
       </c>
       <c r="F187" t="n">
-        <v>33319</v>
+        <v>85257</v>
       </c>
       <c r="G187" t="n">
-        <v>338603</v>
+        <v>961964</v>
       </c>
       <c r="H187" t="n">
-        <v>67652</v>
+        <v>175442</v>
       </c>
       <c r="I187" t="n">
-        <v>19.98</v>
+        <v>18.24</v>
       </c>
       <c r="J187" t="n">
+        <v>8</v>
+      </c>
+      <c r="K187" t="n">
+        <v>4</v>
+      </c>
+      <c r="L187" t="n">
         <v>12</v>
-      </c>
-      <c r="K187" t="n">
-        <v>4</v>
-      </c>
-      <c r="L187" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>장지</t>
+          <t>가양</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>499917</v>
+        <v>640487</v>
       </c>
       <c r="D188" t="n">
-        <v>90185</v>
+        <v>143821</v>
       </c>
       <c r="E188" t="n">
-        <v>462047</v>
+        <v>624800</v>
       </c>
       <c r="F188" t="n">
-        <v>85257</v>
+        <v>140972</v>
       </c>
       <c r="G188" t="n">
-        <v>961964</v>
+        <v>1265287</v>
       </c>
       <c r="H188" t="n">
-        <v>175442</v>
+        <v>284793</v>
       </c>
       <c r="I188" t="n">
-        <v>18.24</v>
+        <v>22.51</v>
       </c>
       <c r="J188" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K188" t="n">
         <v>4</v>
       </c>
       <c r="L188" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>가양</t>
+          <t>개화</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8356,40 +8356,40 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>640487</v>
+        <v>77648</v>
       </c>
       <c r="D189" t="n">
-        <v>143821</v>
+        <v>13560</v>
       </c>
       <c r="E189" t="n">
-        <v>624800</v>
+        <v>53392</v>
       </c>
       <c r="F189" t="n">
-        <v>140972</v>
+        <v>10971</v>
       </c>
       <c r="G189" t="n">
-        <v>1265287</v>
+        <v>131040</v>
       </c>
       <c r="H189" t="n">
-        <v>284793</v>
+        <v>24531</v>
       </c>
       <c r="I189" t="n">
-        <v>22.51</v>
+        <v>18.72</v>
       </c>
       <c r="J189" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L189" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>개화</t>
+          <t>공항시장</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8398,40 +8398,40 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>77648</v>
+        <v>87644</v>
       </c>
       <c r="D190" t="n">
-        <v>13560</v>
+        <v>24745</v>
       </c>
       <c r="E190" t="n">
-        <v>53392</v>
+        <v>93641</v>
       </c>
       <c r="F190" t="n">
-        <v>10971</v>
+        <v>26627</v>
       </c>
       <c r="G190" t="n">
-        <v>131040</v>
+        <v>181285</v>
       </c>
       <c r="H190" t="n">
-        <v>24531</v>
+        <v>51372</v>
       </c>
       <c r="I190" t="n">
-        <v>18.72</v>
+        <v>28.34</v>
       </c>
       <c r="J190" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L190" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>공항시장</t>
+          <t>구반포</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8440,40 +8440,40 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>87644</v>
+        <v>40364</v>
       </c>
       <c r="D191" t="n">
-        <v>24745</v>
+        <v>9863</v>
       </c>
       <c r="E191" t="n">
-        <v>93641</v>
+        <v>38871</v>
       </c>
       <c r="F191" t="n">
-        <v>26627</v>
+        <v>9737</v>
       </c>
       <c r="G191" t="n">
-        <v>181285</v>
+        <v>79235</v>
       </c>
       <c r="H191" t="n">
-        <v>51372</v>
+        <v>19600</v>
       </c>
       <c r="I191" t="n">
-        <v>28.34</v>
+        <v>24.74</v>
       </c>
       <c r="J191" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K191" t="n">
         <v>3</v>
       </c>
       <c r="L191" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>구반포</t>
+          <t>국회의사당</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8482,40 +8482,40 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>40364</v>
+        <v>474200</v>
       </c>
       <c r="D192" t="n">
-        <v>9863</v>
+        <v>64371</v>
       </c>
       <c r="E192" t="n">
-        <v>38871</v>
+        <v>484139</v>
       </c>
       <c r="F192" t="n">
-        <v>9737</v>
+        <v>57952</v>
       </c>
       <c r="G192" t="n">
-        <v>79235</v>
+        <v>958339</v>
       </c>
       <c r="H192" t="n">
-        <v>19600</v>
+        <v>122323</v>
       </c>
       <c r="I192" t="n">
-        <v>24.74</v>
+        <v>12.76</v>
       </c>
       <c r="J192" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L192" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>국회의사당</t>
+          <t>노들</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8524,40 +8524,40 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>474200</v>
+        <v>147810</v>
       </c>
       <c r="D193" t="n">
-        <v>64371</v>
+        <v>34964</v>
       </c>
       <c r="E193" t="n">
-        <v>484139</v>
+        <v>124278</v>
       </c>
       <c r="F193" t="n">
-        <v>57952</v>
+        <v>32133</v>
       </c>
       <c r="G193" t="n">
-        <v>958339</v>
+        <v>272088</v>
       </c>
       <c r="H193" t="n">
-        <v>122323</v>
+        <v>67097</v>
       </c>
       <c r="I193" t="n">
-        <v>12.76</v>
+        <v>24.66</v>
       </c>
       <c r="J193" t="n">
         <v>16</v>
       </c>
       <c r="K193" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L193" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>노들</t>
+          <t>노량진</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8566,40 +8566,40 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>147810</v>
+        <v>773829</v>
       </c>
       <c r="D194" t="n">
-        <v>34964</v>
+        <v>91179</v>
       </c>
       <c r="E194" t="n">
-        <v>124278</v>
+        <v>763448</v>
       </c>
       <c r="F194" t="n">
-        <v>32133</v>
+        <v>90996</v>
       </c>
       <c r="G194" t="n">
-        <v>272088</v>
+        <v>1537277</v>
       </c>
       <c r="H194" t="n">
-        <v>67097</v>
+        <v>182175</v>
       </c>
       <c r="I194" t="n">
-        <v>24.66</v>
+        <v>11.85</v>
       </c>
       <c r="J194" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L194" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>노량진</t>
+          <t>등촌</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8608,40 +8608,40 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>773829</v>
+        <v>349933</v>
       </c>
       <c r="D195" t="n">
-        <v>91179</v>
+        <v>90216</v>
       </c>
       <c r="E195" t="n">
-        <v>763448</v>
+        <v>335943</v>
       </c>
       <c r="F195" t="n">
-        <v>90996</v>
+        <v>91029</v>
       </c>
       <c r="G195" t="n">
-        <v>1537277</v>
+        <v>685876</v>
       </c>
       <c r="H195" t="n">
-        <v>182175</v>
+        <v>181245</v>
       </c>
       <c r="I195" t="n">
-        <v>11.85</v>
+        <v>26.43</v>
       </c>
       <c r="J195" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L195" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>등촌</t>
+          <t>마곡나루</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8650,40 +8650,40 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>349933</v>
+        <v>399673</v>
       </c>
       <c r="D196" t="n">
-        <v>90216</v>
+        <v>40007</v>
       </c>
       <c r="E196" t="n">
-        <v>335943</v>
+        <v>392298</v>
       </c>
       <c r="F196" t="n">
-        <v>91029</v>
+        <v>38995</v>
       </c>
       <c r="G196" t="n">
-        <v>685876</v>
+        <v>791971</v>
       </c>
       <c r="H196" t="n">
-        <v>181245</v>
+        <v>79002</v>
       </c>
       <c r="I196" t="n">
-        <v>26.43</v>
+        <v>9.98</v>
       </c>
       <c r="J196" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L196" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>마곡나루</t>
+          <t>사평</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8692,40 +8692,40 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>399673</v>
+        <v>117034</v>
       </c>
       <c r="D197" t="n">
-        <v>40007</v>
+        <v>25406</v>
       </c>
       <c r="E197" t="n">
-        <v>392298</v>
+        <v>112799</v>
       </c>
       <c r="F197" t="n">
-        <v>38995</v>
+        <v>25429</v>
       </c>
       <c r="G197" t="n">
-        <v>791971</v>
+        <v>229833</v>
       </c>
       <c r="H197" t="n">
-        <v>79002</v>
+        <v>50835</v>
       </c>
       <c r="I197" t="n">
-        <v>9.98</v>
+        <v>22.12</v>
       </c>
       <c r="J197" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K197" t="n">
         <v>4</v>
       </c>
       <c r="L197" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>사평</t>
+          <t>샛강</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8734,40 +8734,40 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>117034</v>
+        <v>183836</v>
       </c>
       <c r="D198" t="n">
-        <v>25406</v>
+        <v>30690</v>
       </c>
       <c r="E198" t="n">
-        <v>112799</v>
+        <v>181903</v>
       </c>
       <c r="F198" t="n">
-        <v>25429</v>
+        <v>30353</v>
       </c>
       <c r="G198" t="n">
-        <v>229833</v>
+        <v>365739</v>
       </c>
       <c r="H198" t="n">
-        <v>50835</v>
+        <v>61043</v>
       </c>
       <c r="I198" t="n">
-        <v>22.12</v>
+        <v>16.69</v>
       </c>
       <c r="J198" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L198" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>샛강</t>
+          <t>선유도</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8776,31 +8776,31 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>183836</v>
+        <v>248011</v>
       </c>
       <c r="D199" t="n">
-        <v>30690</v>
+        <v>33075</v>
       </c>
       <c r="E199" t="n">
-        <v>181903</v>
+        <v>232403</v>
       </c>
       <c r="F199" t="n">
-        <v>30353</v>
+        <v>32261</v>
       </c>
       <c r="G199" t="n">
-        <v>365739</v>
+        <v>480414</v>
       </c>
       <c r="H199" t="n">
-        <v>61043</v>
+        <v>65336</v>
       </c>
       <c r="I199" t="n">
-        <v>16.69</v>
+        <v>13.6</v>
       </c>
       <c r="J199" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L199" t="n">
         <v>17</v>
@@ -8809,7 +8809,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>선유도</t>
+          <t>신논현</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8818,40 +8818,40 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>248011</v>
+        <v>916236</v>
       </c>
       <c r="D200" t="n">
-        <v>33075</v>
+        <v>56569</v>
       </c>
       <c r="E200" t="n">
-        <v>232403</v>
+        <v>916217</v>
       </c>
       <c r="F200" t="n">
-        <v>32261</v>
+        <v>55036</v>
       </c>
       <c r="G200" t="n">
-        <v>480414</v>
+        <v>1832453</v>
       </c>
       <c r="H200" t="n">
-        <v>65336</v>
+        <v>111605</v>
       </c>
       <c r="I200" t="n">
-        <v>13.6</v>
+        <v>6.09</v>
       </c>
       <c r="J200" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K200" t="n">
         <v>4</v>
       </c>
       <c r="L200" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>신논현</t>
+          <t>신목동</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8860,40 +8860,40 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>916236</v>
+        <v>127417</v>
       </c>
       <c r="D201" t="n">
-        <v>56569</v>
+        <v>26008</v>
       </c>
       <c r="E201" t="n">
-        <v>916217</v>
+        <v>112498</v>
       </c>
       <c r="F201" t="n">
-        <v>55036</v>
+        <v>24721</v>
       </c>
       <c r="G201" t="n">
-        <v>1832453</v>
+        <v>239915</v>
       </c>
       <c r="H201" t="n">
-        <v>111605</v>
+        <v>50729</v>
       </c>
       <c r="I201" t="n">
-        <v>6.09</v>
+        <v>21.14</v>
       </c>
       <c r="J201" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K201" t="n">
         <v>4</v>
       </c>
       <c r="L201" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>신목동</t>
+          <t>신반포</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8902,40 +8902,40 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>127417</v>
+        <v>125990</v>
       </c>
       <c r="D202" t="n">
-        <v>26008</v>
+        <v>29239</v>
       </c>
       <c r="E202" t="n">
-        <v>112498</v>
+        <v>124035</v>
       </c>
       <c r="F202" t="n">
-        <v>24721</v>
+        <v>29308</v>
       </c>
       <c r="G202" t="n">
-        <v>239915</v>
+        <v>250025</v>
       </c>
       <c r="H202" t="n">
-        <v>50729</v>
+        <v>58547</v>
       </c>
       <c r="I202" t="n">
-        <v>21.14</v>
+        <v>23.42</v>
       </c>
       <c r="J202" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K202" t="n">
         <v>4</v>
       </c>
       <c r="L202" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>신반포</t>
+          <t>신방화</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8944,40 +8944,40 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>125990</v>
+        <v>202870</v>
       </c>
       <c r="D203" t="n">
-        <v>29239</v>
+        <v>49967</v>
       </c>
       <c r="E203" t="n">
-        <v>124035</v>
+        <v>198595</v>
       </c>
       <c r="F203" t="n">
-        <v>29308</v>
+        <v>50170</v>
       </c>
       <c r="G203" t="n">
-        <v>250025</v>
+        <v>401465</v>
       </c>
       <c r="H203" t="n">
-        <v>58547</v>
+        <v>100137</v>
       </c>
       <c r="I203" t="n">
-        <v>23.42</v>
+        <v>24.94</v>
       </c>
       <c r="J203" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K203" t="n">
         <v>4</v>
       </c>
       <c r="L203" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>신방화</t>
+          <t>양천향교</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8986,40 +8986,40 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>202870</v>
+        <v>289659</v>
       </c>
       <c r="D204" t="n">
-        <v>49967</v>
+        <v>49752</v>
       </c>
       <c r="E204" t="n">
-        <v>198595</v>
+        <v>294136</v>
       </c>
       <c r="F204" t="n">
-        <v>50170</v>
+        <v>49308</v>
       </c>
       <c r="G204" t="n">
-        <v>401465</v>
+        <v>583795</v>
       </c>
       <c r="H204" t="n">
-        <v>100137</v>
+        <v>99060</v>
       </c>
       <c r="I204" t="n">
-        <v>24.94</v>
+        <v>16.97</v>
       </c>
       <c r="J204" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K204" t="n">
         <v>4</v>
       </c>
       <c r="L204" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>양천향교</t>
+          <t>염창</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9028,40 +9028,40 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>289659</v>
+        <v>514529</v>
       </c>
       <c r="D205" t="n">
-        <v>49752</v>
+        <v>80870</v>
       </c>
       <c r="E205" t="n">
-        <v>294136</v>
+        <v>492565</v>
       </c>
       <c r="F205" t="n">
-        <v>49308</v>
+        <v>78794</v>
       </c>
       <c r="G205" t="n">
-        <v>583795</v>
+        <v>1007094</v>
       </c>
       <c r="H205" t="n">
-        <v>99060</v>
+        <v>159664</v>
       </c>
       <c r="I205" t="n">
-        <v>16.97</v>
+        <v>15.85</v>
       </c>
       <c r="J205" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K205" t="n">
         <v>4</v>
       </c>
       <c r="L205" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>염창</t>
+          <t>증미</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9070,40 +9070,40 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>514529</v>
+        <v>219073</v>
       </c>
       <c r="D206" t="n">
-        <v>80870</v>
+        <v>38743</v>
       </c>
       <c r="E206" t="n">
-        <v>492565</v>
+        <v>210572</v>
       </c>
       <c r="F206" t="n">
-        <v>78794</v>
+        <v>38823</v>
       </c>
       <c r="G206" t="n">
-        <v>1007094</v>
+        <v>429645</v>
       </c>
       <c r="H206" t="n">
-        <v>159664</v>
+        <v>77566</v>
       </c>
       <c r="I206" t="n">
-        <v>15.85</v>
+        <v>18.05</v>
       </c>
       <c r="J206" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L206" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>증미</t>
+          <t>흑석</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9112,1671 +9112,1629 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>219073</v>
+        <v>274749</v>
       </c>
       <c r="D207" t="n">
-        <v>38743</v>
+        <v>60214</v>
       </c>
       <c r="E207" t="n">
-        <v>210572</v>
+        <v>279485</v>
       </c>
       <c r="F207" t="n">
-        <v>38823</v>
+        <v>60496</v>
       </c>
       <c r="G207" t="n">
-        <v>429645</v>
+        <v>554234</v>
       </c>
       <c r="H207" t="n">
-        <v>77566</v>
+        <v>120710</v>
       </c>
       <c r="I207" t="n">
-        <v>18.05</v>
+        <v>21.78</v>
       </c>
       <c r="J207" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L207" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>흑석</t>
+          <t>가락시장</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>274749</v>
+        <v>499142</v>
       </c>
       <c r="D208" t="n">
-        <v>60214</v>
+        <v>149493</v>
       </c>
       <c r="E208" t="n">
-        <v>279485</v>
+        <v>517546</v>
       </c>
       <c r="F208" t="n">
-        <v>60496</v>
+        <v>148748</v>
       </c>
       <c r="G208" t="n">
-        <v>554234</v>
+        <v>1016688</v>
       </c>
       <c r="H208" t="n">
-        <v>120710</v>
+        <v>298241</v>
       </c>
       <c r="I208" t="n">
-        <v>21.78</v>
+        <v>29.33</v>
       </c>
       <c r="J208" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K208" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L208" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>가락시장</t>
+          <t>건대입구</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>499142</v>
+        <v>1514545</v>
       </c>
       <c r="D209" t="n">
-        <v>149493</v>
+        <v>160449</v>
       </c>
       <c r="E209" t="n">
-        <v>517546</v>
+        <v>1584989</v>
       </c>
       <c r="F209" t="n">
-        <v>148748</v>
+        <v>158811</v>
       </c>
       <c r="G209" t="n">
-        <v>1016688</v>
+        <v>3099534</v>
       </c>
       <c r="H209" t="n">
-        <v>298241</v>
+        <v>319260</v>
       </c>
       <c r="I209" t="n">
-        <v>29.33</v>
+        <v>10.3</v>
       </c>
       <c r="J209" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="K209" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L209" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>건대입구</t>
+          <t>고속터미널</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,7,9</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1514545</v>
+        <v>2526704</v>
       </c>
       <c r="D210" t="n">
-        <v>160449</v>
+        <v>378399</v>
       </c>
       <c r="E210" t="n">
-        <v>1584989</v>
+        <v>2523557</v>
       </c>
       <c r="F210" t="n">
-        <v>158811</v>
+        <v>369982</v>
       </c>
       <c r="G210" t="n">
-        <v>3099534</v>
+        <v>5050261</v>
       </c>
       <c r="H210" t="n">
-        <v>319260</v>
+        <v>748381</v>
       </c>
       <c r="I210" t="n">
-        <v>10.3</v>
+        <v>14.82</v>
       </c>
       <c r="J210" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="K210" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L210" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>고속터미널</t>
+          <t>공덕</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>3,7,9</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2526704</v>
+        <v>948702</v>
       </c>
       <c r="D211" t="n">
-        <v>378399</v>
+        <v>133694</v>
       </c>
       <c r="E211" t="n">
-        <v>2523557</v>
+        <v>949611</v>
       </c>
       <c r="F211" t="n">
-        <v>369982</v>
+        <v>125787</v>
       </c>
       <c r="G211" t="n">
-        <v>5050261</v>
+        <v>1898313</v>
       </c>
       <c r="H211" t="n">
-        <v>748381</v>
+        <v>259481</v>
       </c>
       <c r="I211" t="n">
-        <v>14.82</v>
+        <v>13.67</v>
       </c>
       <c r="J211" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="K211" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L211" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>공덕</t>
+          <t>교대</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>948702</v>
+        <v>1330717</v>
       </c>
       <c r="D212" t="n">
-        <v>133694</v>
+        <v>237048</v>
       </c>
       <c r="E212" t="n">
-        <v>949611</v>
+        <v>1305183</v>
       </c>
       <c r="F212" t="n">
-        <v>125787</v>
+        <v>227756</v>
       </c>
       <c r="G212" t="n">
-        <v>1898313</v>
+        <v>2635900</v>
       </c>
       <c r="H212" t="n">
-        <v>259481</v>
+        <v>464804</v>
       </c>
       <c r="I212" t="n">
-        <v>13.67</v>
+        <v>17.63</v>
       </c>
       <c r="J212" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K212" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L212" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>교대</t>
+          <t>군자</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1330717</v>
+        <v>785877</v>
       </c>
       <c r="D213" t="n">
-        <v>237048</v>
+        <v>132473</v>
       </c>
       <c r="E213" t="n">
-        <v>1305183</v>
+        <v>726097</v>
       </c>
       <c r="F213" t="n">
-        <v>227756</v>
+        <v>123065</v>
       </c>
       <c r="G213" t="n">
-        <v>2635900</v>
+        <v>1511974</v>
       </c>
       <c r="H213" t="n">
-        <v>464804</v>
+        <v>255538</v>
       </c>
       <c r="I213" t="n">
-        <v>17.63</v>
+        <v>16.9</v>
       </c>
       <c r="J213" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L213" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>군자</t>
+          <t>김포공항</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>785877</v>
+        <v>530431</v>
       </c>
       <c r="D214" t="n">
-        <v>132473</v>
+        <v>70323</v>
       </c>
       <c r="E214" t="n">
-        <v>726097</v>
+        <v>557489</v>
       </c>
       <c r="F214" t="n">
-        <v>123065</v>
+        <v>71426</v>
       </c>
       <c r="G214" t="n">
-        <v>1511974</v>
+        <v>1087920</v>
       </c>
       <c r="H214" t="n">
-        <v>255538</v>
+        <v>141749</v>
       </c>
       <c r="I214" t="n">
-        <v>16.9</v>
+        <v>13.03</v>
       </c>
       <c r="J214" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L214" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>김포공항</t>
+          <t>노원</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>530431</v>
+        <v>1278860</v>
       </c>
       <c r="D215" t="n">
-        <v>70323</v>
+        <v>265098</v>
       </c>
       <c r="E215" t="n">
-        <v>557489</v>
+        <v>1389731</v>
       </c>
       <c r="F215" t="n">
-        <v>71426</v>
+        <v>265470</v>
       </c>
       <c r="G215" t="n">
-        <v>1087920</v>
+        <v>2668591</v>
       </c>
       <c r="H215" t="n">
-        <v>141749</v>
+        <v>530568</v>
       </c>
       <c r="I215" t="n">
-        <v>13.03</v>
+        <v>19.88</v>
       </c>
       <c r="J215" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L215" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>노원</t>
+          <t>당산</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1278860</v>
+        <v>1086434</v>
       </c>
       <c r="D216" t="n">
-        <v>265098</v>
+        <v>134157</v>
       </c>
       <c r="E216" t="n">
-        <v>1389731</v>
+        <v>1153742</v>
       </c>
       <c r="F216" t="n">
-        <v>265470</v>
+        <v>134381</v>
       </c>
       <c r="G216" t="n">
-        <v>2668591</v>
+        <v>2240176</v>
       </c>
       <c r="H216" t="n">
-        <v>530568</v>
+        <v>268538</v>
       </c>
       <c r="I216" t="n">
-        <v>19.88</v>
+        <v>11.99</v>
       </c>
       <c r="J216" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K216" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L216" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>당산</t>
+          <t>대림</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1086434</v>
+        <v>989147</v>
       </c>
       <c r="D217" t="n">
-        <v>134157</v>
+        <v>182965</v>
       </c>
       <c r="E217" t="n">
-        <v>1153742</v>
+        <v>1006134</v>
       </c>
       <c r="F217" t="n">
-        <v>134381</v>
+        <v>186565</v>
       </c>
       <c r="G217" t="n">
-        <v>2240176</v>
+        <v>1995281</v>
       </c>
       <c r="H217" t="n">
-        <v>268538</v>
+        <v>369530</v>
       </c>
       <c r="I217" t="n">
-        <v>11.99</v>
+        <v>18.52</v>
       </c>
       <c r="J217" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K217" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L217" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>대림</t>
+          <t>동대문</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>989147</v>
+        <v>932876</v>
       </c>
       <c r="D218" t="n">
-        <v>182965</v>
+        <v>279178</v>
       </c>
       <c r="E218" t="n">
-        <v>1006134</v>
+        <v>940024</v>
       </c>
       <c r="F218" t="n">
-        <v>186565</v>
+        <v>274204</v>
       </c>
       <c r="G218" t="n">
-        <v>1995281</v>
+        <v>1872900</v>
       </c>
       <c r="H218" t="n">
-        <v>369530</v>
+        <v>553382</v>
       </c>
       <c r="I218" t="n">
-        <v>18.52</v>
+        <v>29.55</v>
       </c>
       <c r="J218" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K218" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L218" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>동대문</t>
+          <t>동대문역사문화공원</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,4,5</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>932876</v>
+        <v>1099733</v>
       </c>
       <c r="D219" t="n">
-        <v>279178</v>
+        <v>133930</v>
       </c>
       <c r="E219" t="n">
-        <v>940024</v>
+        <v>1106872</v>
       </c>
       <c r="F219" t="n">
-        <v>274204</v>
+        <v>132983</v>
       </c>
       <c r="G219" t="n">
-        <v>1872900</v>
+        <v>2206605</v>
       </c>
       <c r="H219" t="n">
-        <v>553382</v>
+        <v>266913</v>
       </c>
       <c r="I219" t="n">
-        <v>29.55</v>
+        <v>12.1</v>
       </c>
       <c r="J219" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K219" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L219" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>동대문역사문화공원</t>
+          <t>동묘앞</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2,4,5</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1099733</v>
+        <v>570181</v>
       </c>
       <c r="D220" t="n">
-        <v>133930</v>
+        <v>229441</v>
       </c>
       <c r="E220" t="n">
-        <v>1106872</v>
+        <v>579997</v>
       </c>
       <c r="F220" t="n">
-        <v>132983</v>
+        <v>226056</v>
       </c>
       <c r="G220" t="n">
-        <v>2206605</v>
+        <v>1150178</v>
       </c>
       <c r="H220" t="n">
-        <v>266913</v>
+        <v>455497</v>
       </c>
       <c r="I220" t="n">
-        <v>12.1</v>
+        <v>39.6</v>
       </c>
       <c r="J220" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K220" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L220" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>동묘앞</t>
+          <t>동작</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>570181</v>
+        <v>109569</v>
       </c>
       <c r="D221" t="n">
-        <v>229441</v>
+        <v>29737</v>
       </c>
       <c r="E221" t="n">
-        <v>579997</v>
+        <v>104756</v>
       </c>
       <c r="F221" t="n">
-        <v>226056</v>
+        <v>28535</v>
       </c>
       <c r="G221" t="n">
-        <v>1150178</v>
+        <v>214325</v>
       </c>
       <c r="H221" t="n">
-        <v>455497</v>
+        <v>58272</v>
       </c>
       <c r="I221" t="n">
-        <v>39.6</v>
+        <v>27.19</v>
       </c>
       <c r="J221" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K221" t="n">
         <v>9</v>
       </c>
       <c r="L221" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>동작</t>
+          <t>불광</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>109569</v>
+        <v>628909</v>
       </c>
       <c r="D222" t="n">
-        <v>29737</v>
+        <v>190903</v>
       </c>
       <c r="E222" t="n">
-        <v>104756</v>
+        <v>657152</v>
       </c>
       <c r="F222" t="n">
-        <v>28535</v>
+        <v>198424</v>
       </c>
       <c r="G222" t="n">
-        <v>214325</v>
+        <v>1286061</v>
       </c>
       <c r="H222" t="n">
-        <v>58272</v>
+        <v>389327</v>
       </c>
       <c r="I222" t="n">
-        <v>27.19</v>
+        <v>30.27</v>
       </c>
       <c r="J222" t="n">
+        <v>14</v>
+      </c>
+      <c r="K222" t="n">
+        <v>7</v>
+      </c>
+      <c r="L222" t="n">
         <v>21</v>
-      </c>
-      <c r="K222" t="n">
-        <v>9</v>
-      </c>
-      <c r="L222" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>불광</t>
+          <t>사당</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>628909</v>
+        <v>1988942</v>
       </c>
       <c r="D223" t="n">
-        <v>190903</v>
+        <v>323350</v>
       </c>
       <c r="E223" t="n">
-        <v>657152</v>
+        <v>2017546</v>
       </c>
       <c r="F223" t="n">
-        <v>198424</v>
+        <v>317669</v>
       </c>
       <c r="G223" t="n">
-        <v>1286061</v>
+        <v>4006488</v>
       </c>
       <c r="H223" t="n">
-        <v>389327</v>
+        <v>641019</v>
       </c>
       <c r="I223" t="n">
-        <v>30.27</v>
+        <v>16</v>
       </c>
       <c r="J223" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K223" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L223" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>사당</t>
+          <t>삼각지</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1988942</v>
+        <v>860919</v>
       </c>
       <c r="D224" t="n">
-        <v>323350</v>
+        <v>92672</v>
       </c>
       <c r="E224" t="n">
-        <v>2017546</v>
+        <v>871584</v>
       </c>
       <c r="F224" t="n">
-        <v>317669</v>
+        <v>88554</v>
       </c>
       <c r="G224" t="n">
-        <v>4006488</v>
+        <v>1732503</v>
       </c>
       <c r="H224" t="n">
-        <v>641019</v>
+        <v>181226</v>
       </c>
       <c r="I224" t="n">
-        <v>16</v>
+        <v>20.97</v>
       </c>
       <c r="J224" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K224" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L224" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>삼각지</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>860919</v>
+        <v>2155185</v>
       </c>
       <c r="D225" t="n">
-        <v>92672</v>
+        <v>271561</v>
       </c>
       <c r="E225" t="n">
-        <v>871584</v>
+        <v>2358354</v>
       </c>
       <c r="F225" t="n">
-        <v>88554</v>
+        <v>275553</v>
       </c>
       <c r="G225" t="n">
-        <v>1732503</v>
+        <v>4513539</v>
       </c>
       <c r="H225" t="n">
-        <v>181226</v>
+        <v>547114</v>
       </c>
       <c r="I225" t="n">
-        <v>20.97</v>
+        <v>12.12</v>
       </c>
       <c r="J225" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K225" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L225" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>시청</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2155185</v>
+        <v>1504288</v>
       </c>
       <c r="D226" t="n">
-        <v>271561</v>
+        <v>170657</v>
       </c>
       <c r="E226" t="n">
-        <v>2358354</v>
+        <v>1458576</v>
       </c>
       <c r="F226" t="n">
-        <v>275553</v>
+        <v>162682</v>
       </c>
       <c r="G226" t="n">
-        <v>4513539</v>
+        <v>2962864</v>
       </c>
       <c r="H226" t="n">
-        <v>547114</v>
+        <v>333339</v>
       </c>
       <c r="I226" t="n">
-        <v>12.12</v>
+        <v>11.25</v>
       </c>
       <c r="J226" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L226" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>시청</t>
+          <t>신당</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1504288</v>
+        <v>687585</v>
       </c>
       <c r="D227" t="n">
-        <v>170657</v>
+        <v>132734</v>
       </c>
       <c r="E227" t="n">
-        <v>1458576</v>
+        <v>712506</v>
       </c>
       <c r="F227" t="n">
-        <v>162682</v>
+        <v>133571</v>
       </c>
       <c r="G227" t="n">
-        <v>2962864</v>
+        <v>1400091</v>
       </c>
       <c r="H227" t="n">
-        <v>333339</v>
+        <v>266305</v>
       </c>
       <c r="I227" t="n">
-        <v>11.25</v>
+        <v>19.02</v>
       </c>
       <c r="J227" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L227" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>신당</t>
+          <t>신설동</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>687585</v>
+        <v>525201</v>
       </c>
       <c r="D228" t="n">
-        <v>132734</v>
+        <v>154123</v>
       </c>
       <c r="E228" t="n">
-        <v>712506</v>
+        <v>508111</v>
       </c>
       <c r="F228" t="n">
-        <v>133571</v>
+        <v>152088</v>
       </c>
       <c r="G228" t="n">
-        <v>1400091</v>
+        <v>1033312</v>
       </c>
       <c r="H228" t="n">
-        <v>266305</v>
+        <v>306211</v>
       </c>
       <c r="I228" t="n">
-        <v>19.02</v>
+        <v>29.63</v>
       </c>
       <c r="J228" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L228" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>신설동</t>
+          <t>약수</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>525201</v>
+        <v>485940</v>
       </c>
       <c r="D229" t="n">
-        <v>154123</v>
+        <v>106219</v>
       </c>
       <c r="E229" t="n">
-        <v>508111</v>
+        <v>473228</v>
       </c>
       <c r="F229" t="n">
-        <v>152088</v>
+        <v>100590</v>
       </c>
       <c r="G229" t="n">
-        <v>1033312</v>
+        <v>959168</v>
       </c>
       <c r="H229" t="n">
-        <v>306211</v>
+        <v>206809</v>
       </c>
       <c r="I229" t="n">
-        <v>29.63</v>
+        <v>21.56</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K229" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L229" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>약수</t>
+          <t>여의도</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>485940</v>
+        <v>1643461</v>
       </c>
       <c r="D230" t="n">
-        <v>106219</v>
+        <v>114204</v>
       </c>
       <c r="E230" t="n">
-        <v>473228</v>
+        <v>1652659</v>
       </c>
       <c r="F230" t="n">
-        <v>100590</v>
+        <v>107101</v>
       </c>
       <c r="G230" t="n">
-        <v>959168</v>
+        <v>3296120</v>
       </c>
       <c r="H230" t="n">
-        <v>206809</v>
+        <v>221305</v>
       </c>
       <c r="I230" t="n">
-        <v>21.56</v>
+        <v>6.71</v>
       </c>
       <c r="J230" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K230" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L230" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>여의도</t>
+          <t>연신내</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1643461</v>
+        <v>1036393</v>
       </c>
       <c r="D231" t="n">
-        <v>114204</v>
+        <v>264167</v>
       </c>
       <c r="E231" t="n">
-        <v>1652659</v>
+        <v>985977</v>
       </c>
       <c r="F231" t="n">
-        <v>107101</v>
+        <v>255205</v>
       </c>
       <c r="G231" t="n">
-        <v>3296120</v>
+        <v>2022370</v>
       </c>
       <c r="H231" t="n">
-        <v>221305</v>
+        <v>519372</v>
       </c>
       <c r="I231" t="n">
-        <v>6.71</v>
+        <v>25.68</v>
       </c>
       <c r="J231" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L231" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>연신내</t>
+          <t>영등포구청</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1036393</v>
+        <v>758286</v>
       </c>
       <c r="D232" t="n">
-        <v>264167</v>
+        <v>126191</v>
       </c>
       <c r="E232" t="n">
-        <v>985977</v>
+        <v>775157</v>
       </c>
       <c r="F232" t="n">
-        <v>255205</v>
+        <v>124777</v>
       </c>
       <c r="G232" t="n">
-        <v>2022370</v>
+        <v>1533443</v>
       </c>
       <c r="H232" t="n">
-        <v>519372</v>
+        <v>250968</v>
       </c>
       <c r="I232" t="n">
-        <v>25.68</v>
+        <v>16.37</v>
       </c>
       <c r="J232" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K232" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L232" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>영등포구청</t>
+          <t>오금</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>758286</v>
+        <v>291808</v>
       </c>
       <c r="D233" t="n">
-        <v>126191</v>
+        <v>56755</v>
       </c>
       <c r="E233" t="n">
-        <v>775157</v>
+        <v>273271</v>
       </c>
       <c r="F233" t="n">
-        <v>124777</v>
+        <v>54128</v>
       </c>
       <c r="G233" t="n">
-        <v>1533443</v>
+        <v>565079</v>
       </c>
       <c r="H233" t="n">
-        <v>250968</v>
+        <v>110883</v>
       </c>
       <c r="I233" t="n">
-        <v>16.37</v>
+        <v>19.62</v>
       </c>
       <c r="J233" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K233" t="n">
         <v>8</v>
       </c>
       <c r="L233" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>오금</t>
+          <t>왕십리</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>291808</v>
+        <v>602261</v>
       </c>
       <c r="D234" t="n">
-        <v>56755</v>
+        <v>79888</v>
       </c>
       <c r="E234" t="n">
-        <v>273271</v>
+        <v>577607</v>
       </c>
       <c r="F234" t="n">
-        <v>54128</v>
+        <v>75030</v>
       </c>
       <c r="G234" t="n">
-        <v>565079</v>
+        <v>1179868</v>
       </c>
       <c r="H234" t="n">
-        <v>110883</v>
+        <v>154918</v>
       </c>
       <c r="I234" t="n">
-        <v>19.62</v>
+        <v>13.13</v>
       </c>
       <c r="J234" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K234" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L234" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>왕십리</t>
+          <t>을지로3가</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>602261</v>
+        <v>1051252</v>
       </c>
       <c r="D235" t="n">
-        <v>79888</v>
+        <v>125034</v>
       </c>
       <c r="E235" t="n">
-        <v>577607</v>
+        <v>1045244</v>
       </c>
       <c r="F235" t="n">
-        <v>75030</v>
+        <v>121016</v>
       </c>
       <c r="G235" t="n">
-        <v>1179868</v>
+        <v>2096496</v>
       </c>
       <c r="H235" t="n">
-        <v>154918</v>
+        <v>246050</v>
       </c>
       <c r="I235" t="n">
-        <v>13.13</v>
+        <v>11.74</v>
       </c>
       <c r="J235" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L235" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>을지로3가</t>
+          <t>을지로4가</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1051252</v>
+        <v>589848</v>
       </c>
       <c r="D236" t="n">
-        <v>125034</v>
+        <v>119702</v>
       </c>
       <c r="E236" t="n">
-        <v>1045244</v>
+        <v>592977</v>
       </c>
       <c r="F236" t="n">
-        <v>121016</v>
+        <v>118251</v>
       </c>
       <c r="G236" t="n">
-        <v>2096496</v>
+        <v>1182825</v>
       </c>
       <c r="H236" t="n">
-        <v>246050</v>
+        <v>237953</v>
       </c>
       <c r="I236" t="n">
-        <v>11.74</v>
+        <v>20.12</v>
       </c>
       <c r="J236" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K236" t="n">
         <v>4</v>
       </c>
       <c r="L236" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>을지로4가</t>
+          <t>잠실</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>589848</v>
+        <v>2898750</v>
       </c>
       <c r="D237" t="n">
-        <v>119702</v>
+        <v>309717</v>
       </c>
       <c r="E237" t="n">
-        <v>592977</v>
+        <v>2944462</v>
       </c>
       <c r="F237" t="n">
-        <v>118251</v>
+        <v>298290</v>
       </c>
       <c r="G237" t="n">
-        <v>1182825</v>
+        <v>5843212</v>
       </c>
       <c r="H237" t="n">
-        <v>237953</v>
+        <v>608007</v>
       </c>
       <c r="I237" t="n">
-        <v>20.12</v>
+        <v>10.41</v>
       </c>
       <c r="J237" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K237" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L237" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>잠실</t>
+          <t>종로3가</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>1,3,5</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2898750</v>
+        <v>1557687</v>
       </c>
       <c r="D238" t="n">
-        <v>309717</v>
+        <v>458436</v>
       </c>
       <c r="E238" t="n">
-        <v>2944462</v>
+        <v>1539083</v>
       </c>
       <c r="F238" t="n">
-        <v>298290</v>
+        <v>445192</v>
       </c>
       <c r="G238" t="n">
-        <v>5843212</v>
+        <v>3096770</v>
       </c>
       <c r="H238" t="n">
-        <v>608007</v>
+        <v>903628</v>
       </c>
       <c r="I238" t="n">
-        <v>10.41</v>
+        <v>29.18</v>
       </c>
       <c r="J238" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K238" t="n">
         <v>7</v>
       </c>
       <c r="L238" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>종로3가</t>
+          <t>천호</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>1,3,5</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1557687</v>
+        <v>1055612</v>
       </c>
       <c r="D239" t="n">
-        <v>458436</v>
+        <v>253203</v>
       </c>
       <c r="E239" t="n">
-        <v>1539083</v>
+        <v>1108370</v>
       </c>
       <c r="F239" t="n">
-        <v>445192</v>
+        <v>252351</v>
       </c>
       <c r="G239" t="n">
-        <v>3096770</v>
+        <v>2163982</v>
       </c>
       <c r="H239" t="n">
-        <v>903628</v>
+        <v>505554</v>
       </c>
       <c r="I239" t="n">
-        <v>29.18</v>
+        <v>23.36</v>
       </c>
       <c r="J239" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K239" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L239" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>천호</t>
+          <t>청구</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1055612</v>
+        <v>219899</v>
       </c>
       <c r="D240" t="n">
-        <v>253203</v>
+        <v>44565</v>
       </c>
       <c r="E240" t="n">
-        <v>1108370</v>
+        <v>211920</v>
       </c>
       <c r="F240" t="n">
-        <v>252351</v>
+        <v>42532</v>
       </c>
       <c r="G240" t="n">
-        <v>2163982</v>
+        <v>431819</v>
       </c>
       <c r="H240" t="n">
-        <v>505554</v>
+        <v>87097</v>
       </c>
       <c r="I240" t="n">
-        <v>23.36</v>
+        <v>20.17</v>
       </c>
       <c r="J240" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L240" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>청구</t>
+          <t>충무로</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>219899</v>
+        <v>867520</v>
       </c>
       <c r="D241" t="n">
-        <v>44565</v>
+        <v>119883</v>
       </c>
       <c r="E241" t="n">
-        <v>211920</v>
+        <v>893846</v>
       </c>
       <c r="F241" t="n">
-        <v>42532</v>
+        <v>121889</v>
       </c>
       <c r="G241" t="n">
-        <v>431819</v>
+        <v>1761366</v>
       </c>
       <c r="H241" t="n">
-        <v>87097</v>
+        <v>241772</v>
       </c>
       <c r="I241" t="n">
-        <v>20.17</v>
+        <v>13.73</v>
       </c>
       <c r="J241" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K241" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L241" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>충무로</t>
+          <t>충정로</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>867520</v>
+        <v>417744</v>
       </c>
       <c r="D242" t="n">
-        <v>119883</v>
+        <v>63616</v>
       </c>
       <c r="E242" t="n">
-        <v>893846</v>
+        <v>436275</v>
       </c>
       <c r="F242" t="n">
-        <v>121889</v>
+        <v>64124</v>
       </c>
       <c r="G242" t="n">
-        <v>1761366</v>
+        <v>854019</v>
       </c>
       <c r="H242" t="n">
-        <v>241772</v>
+        <v>127740</v>
       </c>
       <c r="I242" t="n">
-        <v>13.73</v>
+        <v>14.96</v>
       </c>
       <c r="J242" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K242" t="n">
         <v>4</v>
       </c>
       <c r="L242" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>충정로</t>
+          <t>태릉입구</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>417744</v>
+        <v>438855</v>
       </c>
       <c r="D243" t="n">
-        <v>63616</v>
+        <v>87568</v>
       </c>
       <c r="E243" t="n">
-        <v>436275</v>
+        <v>443702</v>
       </c>
       <c r="F243" t="n">
-        <v>64124</v>
+        <v>85169</v>
       </c>
       <c r="G243" t="n">
-        <v>854019</v>
+        <v>882557</v>
       </c>
       <c r="H243" t="n">
-        <v>127740</v>
+        <v>172737</v>
       </c>
       <c r="I243" t="n">
-        <v>14.96</v>
+        <v>19.57</v>
       </c>
       <c r="J243" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K243" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L243" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>태릉입구</t>
+          <t>합정</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>438855</v>
+        <v>1379809</v>
       </c>
       <c r="D244" t="n">
-        <v>87568</v>
+        <v>113748</v>
       </c>
       <c r="E244" t="n">
-        <v>443702</v>
+        <v>1461301</v>
       </c>
       <c r="F244" t="n">
-        <v>85169</v>
+        <v>111461</v>
       </c>
       <c r="G244" t="n">
-        <v>882557</v>
+        <v>2841110</v>
       </c>
       <c r="H244" t="n">
-        <v>172737</v>
+        <v>225209</v>
       </c>
       <c r="I244" t="n">
-        <v>19.57</v>
+        <v>7.93</v>
       </c>
       <c r="J244" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K244" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L244" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>합정</t>
+          <t>이수</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1379809</v>
+        <v>1043396</v>
       </c>
       <c r="D245" t="n">
-        <v>113748</v>
+        <v>244929</v>
       </c>
       <c r="E245" t="n">
-        <v>1461301</v>
+        <v>1074046</v>
       </c>
       <c r="F245" t="n">
-        <v>111461</v>
+        <v>248082</v>
       </c>
       <c r="G245" t="n">
-        <v>2841110</v>
+        <v>2117442</v>
       </c>
       <c r="H245" t="n">
-        <v>225209</v>
+        <v>493011</v>
       </c>
       <c r="I245" t="n">
-        <v>7.93</v>
+        <v>23.28</v>
       </c>
       <c r="J245" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K245" t="n">
         <v>7</v>
       </c>
       <c r="L245" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>이수</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>4,7</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>1043396</v>
-      </c>
-      <c r="D246" t="n">
-        <v>244929</v>
-      </c>
-      <c r="E246" t="n">
-        <v>1074046</v>
-      </c>
-      <c r="F246" t="n">
-        <v>248082</v>
-      </c>
-      <c r="G246" t="n">
-        <v>2117442</v>
-      </c>
-      <c r="H246" t="n">
-        <v>493011</v>
-      </c>
-      <c r="I246" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="J246" t="n">
-        <v>27</v>
-      </c>
-      <c r="K246" t="n">
-        <v>7</v>
-      </c>
-      <c r="L246" t="n">
         <v>34</v>
       </c>
     </row>

--- a/data/processed/team/subway_merged_base.xlsx
+++ b/data/processed/team/subway_merged_base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L245"/>
+  <dimension ref="A1:M245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>EV</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>시설부하지수</t>
         </is>
       </c>
     </row>
@@ -523,14 +528,17 @@
         <v>55.25</v>
       </c>
       <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
+      <c r="M2" t="n">
+        <v>39979.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,14 +573,17 @@
         <v>13.33</v>
       </c>
       <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
       </c>
+      <c r="M3" t="n">
+        <v>16260.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -607,14 +618,17 @@
         <v>34.61</v>
       </c>
       <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
+      <c r="M4" t="n">
+        <v>40693.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,14 +663,17 @@
         <v>42.58</v>
       </c>
       <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>8</v>
       </c>
+      <c r="M5" t="n">
+        <v>40142.07</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,13 +708,16 @@
         <v>6.64</v>
       </c>
       <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
       <c r="L6" t="n">
         <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18886.94</v>
       </c>
     </row>
     <row r="7">
@@ -741,6 +761,9 @@
       <c r="L7" t="n">
         <v>4</v>
       </c>
+      <c r="M7" t="n">
+        <v>23487</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -783,6 +806,9 @@
       <c r="L8" t="n">
         <v>8</v>
       </c>
+      <c r="M8" t="n">
+        <v>20238.45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -817,14 +843,17 @@
         <v>15.38</v>
       </c>
       <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
         <v>6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
       </c>
+      <c r="M9" t="n">
+        <v>15840.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -859,14 +888,17 @@
         <v>14.17</v>
       </c>
       <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
         <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>11</v>
       </c>
+      <c r="M10" t="n">
+        <v>11303.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -901,14 +933,17 @@
         <v>23.89</v>
       </c>
       <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
         <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
       </c>
+      <c r="M11" t="n">
+        <v>2301.38</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -943,14 +978,17 @@
         <v>8.859999999999999</v>
       </c>
       <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
       </c>
+      <c r="M12" t="n">
+        <v>5361.92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -993,6 +1031,9 @@
       <c r="L13" t="n">
         <v>8</v>
       </c>
+      <c r="M13" t="n">
+        <v>8970.85</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1027,14 +1068,17 @@
         <v>15.76</v>
       </c>
       <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
       </c>
+      <c r="M14" t="n">
+        <v>11084.43</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1069,14 +1113,17 @@
         <v>22.63</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
       </c>
+      <c r="M15" t="n">
+        <v>19288.44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1111,14 +1158,17 @@
         <v>7.53</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>9</v>
       </c>
+      <c r="M16" t="n">
+        <v>9839.459999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1153,14 +1203,17 @@
         <v>16.94</v>
       </c>
       <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
         <v>8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>11</v>
       </c>
+      <c r="M17" t="n">
+        <v>6985.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1195,14 +1248,17 @@
         <v>13.26</v>
       </c>
       <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
         <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
       </c>
       <c r="L18" t="n">
         <v>11</v>
       </c>
+      <c r="M18" t="n">
+        <v>17747.55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1237,14 +1293,17 @@
         <v>14.75</v>
       </c>
       <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
       </c>
+      <c r="M19" t="n">
+        <v>7609.88</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1279,14 +1338,17 @@
         <v>15.04</v>
       </c>
       <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
       </c>
+      <c r="M20" t="n">
+        <v>31454.71</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1321,14 +1383,17 @@
         <v>7.52</v>
       </c>
       <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
         <v>8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
       </c>
+      <c r="M21" t="n">
+        <v>8516.42</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1363,14 +1428,17 @@
         <v>20.14</v>
       </c>
       <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
       </c>
+      <c r="M22" t="n">
+        <v>2507</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1405,14 +1473,17 @@
         <v>18.27</v>
       </c>
       <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>11</v>
       </c>
+      <c r="M23" t="n">
+        <v>13321.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1447,14 +1518,17 @@
         <v>15.48</v>
       </c>
       <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
         <v>9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>13</v>
       </c>
+      <c r="M24" t="n">
+        <v>18065.8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1489,14 +1563,17 @@
         <v>12.7</v>
       </c>
       <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
         <v>8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
       </c>
       <c r="L25" t="n">
         <v>11</v>
       </c>
+      <c r="M25" t="n">
+        <v>20264.45</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1531,14 +1608,17 @@
         <v>25.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>7</v>
       </c>
+      <c r="M26" t="n">
+        <v>9561.25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1581,6 +1661,9 @@
       <c r="L27" t="n">
         <v>8</v>
       </c>
+      <c r="M27" t="n">
+        <v>12357.85</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1615,14 +1698,17 @@
         <v>21.35</v>
       </c>
       <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>6</v>
       </c>
+      <c r="M28" t="n">
+        <v>7322.11</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1657,14 +1743,17 @@
         <v>26.67</v>
       </c>
       <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3</v>
       </c>
       <c r="L29" t="n">
         <v>5</v>
       </c>
+      <c r="M29" t="n">
+        <v>7701</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1699,14 +1788,17 @@
         <v>10.03</v>
       </c>
       <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
         <v>14</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4</v>
       </c>
       <c r="L30" t="n">
         <v>18</v>
       </c>
+      <c r="M30" t="n">
+        <v>9725.530000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1741,14 +1833,17 @@
         <v>20.81</v>
       </c>
       <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
       </c>
+      <c r="M31" t="n">
+        <v>4541.88</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1783,14 +1878,17 @@
         <v>33.98</v>
       </c>
       <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
         <v>12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4</v>
       </c>
       <c r="L32" t="n">
         <v>16</v>
       </c>
+      <c r="M32" t="n">
+        <v>1778.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1825,14 +1923,17 @@
         <v>7.23</v>
       </c>
       <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
         <v>6</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>10</v>
       </c>
+      <c r="M33" t="n">
+        <v>9333.59</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1867,14 +1968,17 @@
         <v>10.23</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
         <v>7</v>
       </c>
+      <c r="M34" t="n">
+        <v>6504.12</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1909,14 +2013,17 @@
         <v>21.48</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>6</v>
       </c>
+      <c r="M35" t="n">
+        <v>14953.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1951,14 +2058,17 @@
         <v>16.77</v>
       </c>
       <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
         <v>11</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>15</v>
       </c>
+      <c r="M36" t="n">
+        <v>8564.74</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1993,14 +2103,17 @@
         <v>13.74</v>
       </c>
       <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
       </c>
       <c r="L37" t="n">
         <v>8</v>
       </c>
+      <c r="M37" t="n">
+        <v>6508.18</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2043,6 +2156,9 @@
       <c r="L38" t="n">
         <v>4</v>
       </c>
+      <c r="M38" t="n">
+        <v>2945.3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2077,14 +2193,17 @@
         <v>4.45</v>
       </c>
       <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
         <v>8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>10</v>
       </c>
+      <c r="M39" t="n">
+        <v>12497.88</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2119,14 +2238,17 @@
         <v>12.54</v>
       </c>
       <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>12</v>
       </c>
+      <c r="M40" t="n">
+        <v>10802.89</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2161,14 +2283,17 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
         <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>24</v>
       </c>
+      <c r="M41" t="n">
+        <v>2572.42</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2203,14 +2328,17 @@
         <v>21.05</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
       </c>
+      <c r="M42" t="n">
+        <v>22065.33</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2245,14 +2373,17 @@
         <v>24.02</v>
       </c>
       <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="n">
         <v>6</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3</v>
       </c>
       <c r="L43" t="n">
         <v>9</v>
       </c>
+      <c r="M43" t="n">
+        <v>6058.44</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2287,14 +2418,17 @@
         <v>14.62</v>
       </c>
       <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" t="n">
         <v>2</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>5</v>
       </c>
+      <c r="M44" t="n">
+        <v>18427.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2329,14 +2463,17 @@
         <v>18.98</v>
       </c>
       <c r="J45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="n">
         <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>3</v>
       </c>
       <c r="L45" t="n">
         <v>5</v>
       </c>
+      <c r="M45" t="n">
+        <v>11535.14</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2371,14 +2508,17 @@
         <v>21.22</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
         <v>7</v>
       </c>
+      <c r="M46" t="n">
+        <v>7880.75</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2413,14 +2553,17 @@
         <v>19.79</v>
       </c>
       <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
         <v>8</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
       </c>
       <c r="L47" t="n">
         <v>10</v>
       </c>
+      <c r="M47" t="n">
+        <v>8868.75</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2455,14 +2598,17 @@
         <v>17.24</v>
       </c>
       <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="n">
         <v>8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
       </c>
       <c r="L48" t="n">
         <v>10</v>
       </c>
+      <c r="M48" t="n">
+        <v>3503.12</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2497,14 +2643,17 @@
         <v>31.4</v>
       </c>
       <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
         <v>8</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>10</v>
       </c>
+      <c r="M49" t="n">
+        <v>9172.059999999999</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2547,6 +2696,9 @@
       <c r="L50" t="n">
         <v>8</v>
       </c>
+      <c r="M50" t="n">
+        <v>4372.55</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2581,14 +2733,17 @@
         <v>20.79</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" t="n">
         <v>7</v>
       </c>
+      <c r="M51" t="n">
+        <v>8990.620000000001</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2623,14 +2778,17 @@
         <v>27.29</v>
       </c>
       <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
+      <c r="M52" t="n">
+        <v>5684.42</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2665,14 +2823,17 @@
         <v>22.06</v>
       </c>
       <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
         <v>12</v>
-      </c>
-      <c r="K53" t="n">
-        <v>4</v>
       </c>
       <c r="L53" t="n">
         <v>16</v>
       </c>
+      <c r="M53" t="n">
+        <v>8668.75</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2707,14 +2868,17 @@
         <v>8.43</v>
       </c>
       <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
         <v>6</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4</v>
       </c>
       <c r="L54" t="n">
         <v>10</v>
       </c>
+      <c r="M54" t="n">
+        <v>6292.73</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2749,14 +2913,17 @@
         <v>13.79</v>
       </c>
       <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>12</v>
       </c>
+      <c r="M55" t="n">
+        <v>12372.72</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2791,14 +2958,17 @@
         <v>14.87</v>
       </c>
       <c r="J56" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" t="n">
         <v>9</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4</v>
       </c>
       <c r="L56" t="n">
         <v>13</v>
       </c>
+      <c r="M56" t="n">
+        <v>11168</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2833,14 +3003,17 @@
         <v>14.21</v>
       </c>
       <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
         <v>2</v>
-      </c>
-      <c r="K57" t="n">
-        <v>5</v>
       </c>
       <c r="L57" t="n">
         <v>7</v>
       </c>
+      <c r="M57" t="n">
+        <v>13968.05</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2875,14 +3048,17 @@
         <v>23.35</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>7</v>
       </c>
+      <c r="M58" t="n">
+        <v>7766.5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2917,14 +3093,17 @@
         <v>23.07</v>
       </c>
       <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
         <v>6</v>
-      </c>
-      <c r="K59" t="n">
-        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>10</v>
       </c>
+      <c r="M59" t="n">
+        <v>6409.5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2959,14 +3138,17 @@
         <v>21.92</v>
       </c>
       <c r="J60" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" t="n">
         <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
       </c>
+      <c r="M60" t="n">
+        <v>5585.83</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3001,14 +3183,17 @@
         <v>24.2</v>
       </c>
       <c r="J61" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" t="n">
         <v>2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3</v>
       </c>
       <c r="L61" t="n">
         <v>5</v>
       </c>
+      <c r="M61" t="n">
+        <v>2584.36</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3043,14 +3228,17 @@
         <v>28.16</v>
       </c>
       <c r="J62" t="n">
+        <v>3</v>
+      </c>
+      <c r="K62" t="n">
         <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>3</v>
       </c>
       <c r="L62" t="n">
         <v>3</v>
       </c>
+      <c r="M62" t="n">
+        <v>24278.42</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3093,6 +3281,9 @@
       <c r="L63" t="n">
         <v>6</v>
       </c>
+      <c r="M63" t="n">
+        <v>16726.13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3127,14 +3318,17 @@
         <v>22.26</v>
       </c>
       <c r="J64" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
         <v>2</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3</v>
       </c>
       <c r="L64" t="n">
         <v>5</v>
       </c>
+      <c r="M64" t="n">
+        <v>1221.21</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3169,14 +3363,17 @@
         <v>7.7</v>
       </c>
       <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
         <v>5</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2</v>
       </c>
       <c r="L65" t="n">
         <v>7</v>
       </c>
+      <c r="M65" t="n">
+        <v>12577.92</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3211,14 +3408,17 @@
         <v>27.22</v>
       </c>
       <c r="J66" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" t="n">
         <v>6</v>
-      </c>
-      <c r="K66" t="n">
-        <v>3</v>
       </c>
       <c r="L66" t="n">
         <v>9</v>
       </c>
+      <c r="M66" t="n">
+        <v>13556.5</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3261,6 +3461,9 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
+      <c r="M67" t="n">
+        <v>38079.5</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3295,14 +3498,17 @@
         <v>30.98</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L68" t="n">
         <v>7</v>
       </c>
+      <c r="M68" t="n">
+        <v>10501.56</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3337,14 +3543,17 @@
         <v>23.85</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L69" t="n">
         <v>5</v>
       </c>
+      <c r="M69" t="n">
+        <v>32699</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3387,6 +3596,9 @@
       <c r="L70" t="n">
         <v>8</v>
       </c>
+      <c r="M70" t="n">
+        <v>9168.049999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3421,14 +3633,17 @@
         <v>19.91</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>7</v>
       </c>
+      <c r="M71" t="n">
+        <v>24939</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3463,14 +3678,17 @@
         <v>12.66</v>
       </c>
       <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
         <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>3</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
       </c>
+      <c r="M72" t="n">
+        <v>9155</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3505,14 +3723,17 @@
         <v>9.65</v>
       </c>
       <c r="J73" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" t="n">
         <v>9</v>
-      </c>
-      <c r="K73" t="n">
-        <v>4</v>
       </c>
       <c r="L73" t="n">
         <v>13</v>
       </c>
+      <c r="M73" t="n">
+        <v>4670.68</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3547,14 +3768,17 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
         <v>6</v>
-      </c>
-      <c r="K74" t="n">
-        <v>3</v>
       </c>
       <c r="L74" t="n">
         <v>9</v>
       </c>
+      <c r="M74" t="n">
+        <v>20030.06</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3589,14 +3813,17 @@
         <v>18.14</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L75" t="n">
         <v>9</v>
       </c>
+      <c r="M75" t="n">
+        <v>4588.75</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3631,14 +3858,17 @@
         <v>29.1</v>
       </c>
       <c r="J76" t="n">
+        <v>8</v>
+      </c>
+      <c r="K76" t="n">
         <v>2</v>
-      </c>
-      <c r="K76" t="n">
-        <v>8</v>
       </c>
       <c r="L76" t="n">
         <v>10</v>
       </c>
+      <c r="M76" t="n">
+        <v>13612.94</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3673,14 +3903,17 @@
         <v>18.32</v>
       </c>
       <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="n">
         <v>2</v>
-      </c>
-      <c r="K77" t="n">
-        <v>3</v>
       </c>
       <c r="L77" t="n">
         <v>5</v>
       </c>
+      <c r="M77" t="n">
+        <v>10879.93</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3715,14 +3948,17 @@
         <v>12.2</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" t="n">
         <v>6</v>
       </c>
+      <c r="M78" t="n">
+        <v>22305.67</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3757,14 +3993,17 @@
         <v>25.26</v>
       </c>
       <c r="J79" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" t="n">
         <v>6</v>
-      </c>
-      <c r="K79" t="n">
-        <v>2</v>
       </c>
       <c r="L79" t="n">
         <v>8</v>
       </c>
+      <c r="M79" t="n">
+        <v>29093.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3799,14 +4038,17 @@
         <v>21.55</v>
       </c>
       <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="n">
         <v>10</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3</v>
       </c>
       <c r="L80" t="n">
         <v>13</v>
       </c>
+      <c r="M80" t="n">
+        <v>10287</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3841,14 +4083,17 @@
         <v>27.49</v>
       </c>
       <c r="J81" t="n">
+        <v>8</v>
+      </c>
+      <c r="K81" t="n">
         <v>16</v>
-      </c>
-      <c r="K81" t="n">
-        <v>8</v>
       </c>
       <c r="L81" t="n">
         <v>24</v>
       </c>
+      <c r="M81" t="n">
+        <v>1868.9</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3883,14 +4128,17 @@
         <v>28.14</v>
       </c>
       <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
         <v>2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3</v>
       </c>
       <c r="L82" t="n">
         <v>5</v>
       </c>
+      <c r="M82" t="n">
+        <v>7778.29</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3925,14 +4173,17 @@
         <v>25.66</v>
       </c>
       <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
         <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>2</v>
       </c>
       <c r="L83" t="n">
         <v>2</v>
       </c>
+      <c r="M83" t="n">
+        <v>10822.75</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3975,6 +4226,9 @@
       <c r="L84" t="n">
         <v>6</v>
       </c>
+      <c r="M84" t="n">
+        <v>9222.870000000001</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4009,14 +4263,17 @@
         <v>26.66</v>
       </c>
       <c r="J85" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" t="n">
         <v>6</v>
-      </c>
-      <c r="K85" t="n">
-        <v>4</v>
       </c>
       <c r="L85" t="n">
         <v>10</v>
       </c>
+      <c r="M85" t="n">
+        <v>7171.86</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4059,6 +4316,9 @@
       <c r="L86" t="n">
         <v>8</v>
       </c>
+      <c r="M86" t="n">
+        <v>7261.35</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4093,14 +4353,17 @@
         <v>10.14</v>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
       </c>
+      <c r="M87" t="n">
+        <v>16598.92</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4135,14 +4398,17 @@
         <v>28.85</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
         <v>7</v>
       </c>
+      <c r="M88" t="n">
+        <v>10179.62</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4185,6 +4451,9 @@
       <c r="L89" t="n">
         <v>6</v>
       </c>
+      <c r="M89" t="n">
+        <v>11073.87</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4219,14 +4488,17 @@
         <v>20.73</v>
       </c>
       <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
         <v>12</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4</v>
       </c>
       <c r="L90" t="n">
         <v>16</v>
       </c>
+      <c r="M90" t="n">
+        <v>11810.79</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4269,6 +4541,9 @@
       <c r="L91" t="n">
         <v>8</v>
       </c>
+      <c r="M91" t="n">
+        <v>8532.9</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4311,6 +4586,9 @@
       <c r="L92" t="n">
         <v>6</v>
       </c>
+      <c r="M92" t="n">
+        <v>10519</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4345,14 +4623,17 @@
         <v>14.69</v>
       </c>
       <c r="J93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" t="n">
         <v>12</v>
-      </c>
-      <c r="K93" t="n">
-        <v>6</v>
       </c>
       <c r="L93" t="n">
         <v>18</v>
       </c>
+      <c r="M93" t="n">
+        <v>2852.47</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4387,14 +4668,17 @@
         <v>25.9</v>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L94" t="n">
         <v>7</v>
       </c>
+      <c r="M94" t="n">
+        <v>5401.62</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4429,14 +4713,17 @@
         <v>29.2</v>
       </c>
       <c r="J95" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
         <v>10</v>
-      </c>
-      <c r="K95" t="n">
-        <v>3</v>
       </c>
       <c r="L95" t="n">
         <v>13</v>
       </c>
+      <c r="M95" t="n">
+        <v>5473.95</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4471,14 +4758,17 @@
         <v>15.71</v>
       </c>
       <c r="J96" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" t="n">
         <v>10</v>
-      </c>
-      <c r="K96" t="n">
-        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>12</v>
       </c>
+      <c r="M96" t="n">
+        <v>7316.33</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4513,14 +4803,17 @@
         <v>29.25</v>
       </c>
       <c r="J97" t="n">
+        <v>3</v>
+      </c>
+      <c r="K97" t="n">
         <v>2</v>
-      </c>
-      <c r="K97" t="n">
-        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>5</v>
       </c>
+      <c r="M97" t="n">
+        <v>10618.07</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4555,14 +4848,17 @@
         <v>17.95</v>
       </c>
       <c r="J98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L98" t="n">
         <v>7</v>
       </c>
+      <c r="M98" t="n">
+        <v>11080.44</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4597,14 +4893,17 @@
         <v>16.95</v>
       </c>
       <c r="J99" t="n">
+        <v>3</v>
+      </c>
+      <c r="K99" t="n">
         <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>3</v>
       </c>
       <c r="L99" t="n">
         <v>3</v>
       </c>
+      <c r="M99" t="n">
+        <v>18578</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4639,14 +4938,17 @@
         <v>23.98</v>
       </c>
       <c r="J100" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" t="n">
         <v>2</v>
-      </c>
-      <c r="K100" t="n">
-        <v>4</v>
       </c>
       <c r="L100" t="n">
         <v>6</v>
       </c>
+      <c r="M100" t="n">
+        <v>5834.67</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4681,14 +4983,17 @@
         <v>28.87</v>
       </c>
       <c r="J101" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" t="n">
         <v>6</v>
-      </c>
-      <c r="K101" t="n">
-        <v>3</v>
       </c>
       <c r="L101" t="n">
         <v>9</v>
       </c>
+      <c r="M101" t="n">
+        <v>6378.06</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4723,14 +5028,17 @@
         <v>23.36</v>
       </c>
       <c r="J102" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" t="n">
         <v>16</v>
-      </c>
-      <c r="K102" t="n">
-        <v>6</v>
       </c>
       <c r="L102" t="n">
         <v>22</v>
       </c>
+      <c r="M102" t="n">
+        <v>4768.98</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4765,14 +5073,17 @@
         <v>13</v>
       </c>
       <c r="J103" t="n">
+        <v>3</v>
+      </c>
+      <c r="K103" t="n">
         <v>10</v>
-      </c>
-      <c r="K103" t="n">
-        <v>3</v>
       </c>
       <c r="L103" t="n">
         <v>13</v>
       </c>
+      <c r="M103" t="n">
+        <v>6513.68</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4815,6 +5126,9 @@
       <c r="L104" t="n">
         <v>8</v>
       </c>
+      <c r="M104" t="n">
+        <v>5091.15</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4849,14 +5163,17 @@
         <v>22.5</v>
       </c>
       <c r="J105" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" t="n">
         <v>12</v>
-      </c>
-      <c r="K105" t="n">
-        <v>3</v>
       </c>
       <c r="L105" t="n">
         <v>15</v>
       </c>
+      <c r="M105" t="n">
+        <v>3553.83</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4891,14 +5208,17 @@
         <v>9.140000000000001</v>
       </c>
       <c r="J106" t="n">
+        <v>6</v>
+      </c>
+      <c r="K106" t="n">
         <v>9</v>
-      </c>
-      <c r="K106" t="n">
-        <v>6</v>
       </c>
       <c r="L106" t="n">
         <v>15</v>
       </c>
+      <c r="M106" t="n">
+        <v>789.58</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4933,14 +5253,17 @@
         <v>18.66</v>
       </c>
       <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
         <v>10</v>
-      </c>
-      <c r="K107" t="n">
-        <v>2</v>
       </c>
       <c r="L107" t="n">
         <v>12</v>
       </c>
+      <c r="M107" t="n">
+        <v>7353.78</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4975,14 +5298,17 @@
         <v>24.25</v>
       </c>
       <c r="J108" t="n">
+        <v>3</v>
+      </c>
+      <c r="K108" t="n">
         <v>8</v>
-      </c>
-      <c r="K108" t="n">
-        <v>3</v>
       </c>
       <c r="L108" t="n">
         <v>11</v>
       </c>
+      <c r="M108" t="n">
+        <v>10614.5</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5017,14 +5343,17 @@
         <v>20.87</v>
       </c>
       <c r="J109" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" t="n">
         <v>6</v>
-      </c>
-      <c r="K109" t="n">
-        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>11</v>
       </c>
+      <c r="M109" t="n">
+        <v>3040.04</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5059,14 +5388,17 @@
         <v>14.59</v>
       </c>
       <c r="J110" t="n">
+        <v>3</v>
+      </c>
+      <c r="K110" t="n">
         <v>8</v>
-      </c>
-      <c r="K110" t="n">
-        <v>3</v>
       </c>
       <c r="L110" t="n">
         <v>11</v>
       </c>
+      <c r="M110" t="n">
+        <v>3129.1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5101,14 +5433,17 @@
         <v>7.48</v>
       </c>
       <c r="J111" t="n">
+        <v>3</v>
+      </c>
+      <c r="K111" t="n">
         <v>11</v>
-      </c>
-      <c r="K111" t="n">
-        <v>3</v>
       </c>
       <c r="L111" t="n">
         <v>14</v>
       </c>
+      <c r="M111" t="n">
+        <v>2870.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5143,14 +5478,17 @@
         <v>23.72</v>
       </c>
       <c r="J112" t="n">
+        <v>3</v>
+      </c>
+      <c r="K112" t="n">
         <v>8</v>
-      </c>
-      <c r="K112" t="n">
-        <v>3</v>
       </c>
       <c r="L112" t="n">
         <v>11</v>
       </c>
+      <c r="M112" t="n">
+        <v>8073.75</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5185,14 +5523,17 @@
         <v>14.6</v>
       </c>
       <c r="J113" t="n">
+        <v>3</v>
+      </c>
+      <c r="K113" t="n">
         <v>10</v>
-      </c>
-      <c r="K113" t="n">
-        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>13</v>
       </c>
+      <c r="M113" t="n">
+        <v>8442.77</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5227,14 +5568,17 @@
         <v>25.59</v>
       </c>
       <c r="J114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L114" t="n">
         <v>7</v>
       </c>
+      <c r="M114" t="n">
+        <v>4908.44</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5269,14 +5613,17 @@
         <v>24.25</v>
       </c>
       <c r="J115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L115" t="n">
         <v>7</v>
       </c>
+      <c r="M115" t="n">
+        <v>12905.12</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5311,14 +5658,17 @@
         <v>18.68</v>
       </c>
       <c r="J116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L116" t="n">
         <v>7</v>
       </c>
+      <c r="M116" t="n">
+        <v>12797.62</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5353,14 +5703,17 @@
         <v>22.9</v>
       </c>
       <c r="J117" t="n">
+        <v>3</v>
+      </c>
+      <c r="K117" t="n">
         <v>8</v>
-      </c>
-      <c r="K117" t="n">
-        <v>3</v>
       </c>
       <c r="L117" t="n">
         <v>11</v>
       </c>
+      <c r="M117" t="n">
+        <v>5054.9</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5395,14 +5748,17 @@
         <v>19.14</v>
       </c>
       <c r="J118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L118" t="n">
         <v>6</v>
       </c>
+      <c r="M118" t="n">
+        <v>25440.08</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5437,14 +5793,17 @@
         <v>14.23</v>
       </c>
       <c r="J119" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" t="n">
         <v>12</v>
-      </c>
-      <c r="K119" t="n">
-        <v>4</v>
       </c>
       <c r="L119" t="n">
         <v>16</v>
       </c>
+      <c r="M119" t="n">
+        <v>2589.89</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5479,14 +5838,17 @@
         <v>20.95</v>
       </c>
       <c r="J120" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" t="n">
         <v>9</v>
-      </c>
-      <c r="K120" t="n">
-        <v>3</v>
       </c>
       <c r="L120" t="n">
         <v>12</v>
       </c>
+      <c r="M120" t="n">
+        <v>5301.81</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5521,14 +5883,17 @@
         <v>27.91</v>
       </c>
       <c r="J121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L121" t="n">
         <v>6</v>
       </c>
+      <c r="M121" t="n">
+        <v>9715.5</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5563,14 +5928,17 @@
         <v>11.53</v>
       </c>
       <c r="J122" t="n">
+        <v>3</v>
+      </c>
+      <c r="K122" t="n">
         <v>13</v>
-      </c>
-      <c r="K122" t="n">
-        <v>3</v>
       </c>
       <c r="L122" t="n">
         <v>16</v>
       </c>
+      <c r="M122" t="n">
+        <v>1469.56</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5605,14 +5973,17 @@
         <v>17.85</v>
       </c>
       <c r="J123" t="n">
+        <v>3</v>
+      </c>
+      <c r="K123" t="n">
         <v>6</v>
-      </c>
-      <c r="K123" t="n">
-        <v>3</v>
       </c>
       <c r="L123" t="n">
         <v>9</v>
       </c>
+      <c r="M123" t="n">
+        <v>5476.5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5647,14 +6018,17 @@
         <v>28.93</v>
       </c>
       <c r="J124" t="n">
+        <v>2</v>
+      </c>
+      <c r="K124" t="n">
         <v>8</v>
-      </c>
-      <c r="K124" t="n">
-        <v>2</v>
       </c>
       <c r="L124" t="n">
         <v>10</v>
       </c>
+      <c r="M124" t="n">
+        <v>2989.5</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5689,14 +6063,17 @@
         <v>22.41</v>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L125" t="n">
         <v>7</v>
       </c>
+      <c r="M125" t="n">
+        <v>8198.120000000001</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5731,14 +6108,17 @@
         <v>14.42</v>
       </c>
       <c r="J126" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" t="n">
         <v>8</v>
-      </c>
-      <c r="K126" t="n">
-        <v>3</v>
       </c>
       <c r="L126" t="n">
         <v>11</v>
       </c>
+      <c r="M126" t="n">
+        <v>6207.35</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5773,14 +6153,17 @@
         <v>19.99</v>
       </c>
       <c r="J127" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" t="n">
         <v>12</v>
-      </c>
-      <c r="K127" t="n">
-        <v>4</v>
       </c>
       <c r="L127" t="n">
         <v>16</v>
       </c>
+      <c r="M127" t="n">
+        <v>5742.54</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5823,6 +6206,9 @@
       <c r="L128" t="n">
         <v>4</v>
       </c>
+      <c r="M128" t="n">
+        <v>17458.1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5857,14 +6243,17 @@
         <v>24.34</v>
       </c>
       <c r="J129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L129" t="n">
         <v>9</v>
       </c>
+      <c r="M129" t="n">
+        <v>1304.38</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5899,14 +6288,17 @@
         <v>14.28</v>
       </c>
       <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
         <v>2</v>
-      </c>
-      <c r="K130" t="n">
-        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
+      <c r="M130" t="n">
+        <v>10718.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5949,6 +6341,9 @@
       <c r="L131" t="n">
         <v>8</v>
       </c>
+      <c r="M131" t="n">
+        <v>5263.2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5983,14 +6378,17 @@
         <v>6.81</v>
       </c>
       <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="n">
         <v>10</v>
-      </c>
-      <c r="K132" t="n">
-        <v>3</v>
       </c>
       <c r="L132" t="n">
         <v>13</v>
       </c>
+      <c r="M132" t="n">
+        <v>2038.86</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6025,14 +6423,17 @@
         <v>23.08</v>
       </c>
       <c r="J133" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" t="n">
         <v>6</v>
-      </c>
-      <c r="K133" t="n">
-        <v>3</v>
       </c>
       <c r="L133" t="n">
         <v>9</v>
       </c>
+      <c r="M133" t="n">
+        <v>4704.28</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6067,14 +6468,17 @@
         <v>25.83</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L134" t="n">
         <v>7</v>
       </c>
+      <c r="M134" t="n">
+        <v>11563.44</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6109,14 +6513,17 @@
         <v>22.67</v>
       </c>
       <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" t="n">
         <v>14</v>
-      </c>
-      <c r="K135" t="n">
-        <v>4</v>
       </c>
       <c r="L135" t="n">
         <v>18</v>
       </c>
+      <c r="M135" t="n">
+        <v>5537.9</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6151,14 +6558,17 @@
         <v>10.22</v>
       </c>
       <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="n">
         <v>6</v>
-      </c>
-      <c r="K136" t="n">
-        <v>3</v>
       </c>
       <c r="L136" t="n">
         <v>9</v>
       </c>
+      <c r="M136" t="n">
+        <v>4262.83</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6193,14 +6603,17 @@
         <v>28.88</v>
       </c>
       <c r="J137" t="n">
+        <v>2</v>
+      </c>
+      <c r="K137" t="n">
         <v>6</v>
-      </c>
-      <c r="K137" t="n">
-        <v>2</v>
       </c>
       <c r="L137" t="n">
         <v>8</v>
       </c>
+      <c r="M137" t="n">
+        <v>5008.43</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6235,14 +6648,17 @@
         <v>20.8</v>
       </c>
       <c r="J138" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" t="n">
         <v>12</v>
-      </c>
-      <c r="K138" t="n">
-        <v>3</v>
       </c>
       <c r="L138" t="n">
         <v>15</v>
       </c>
+      <c r="M138" t="n">
+        <v>5958.38</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6277,14 +6693,17 @@
         <v>30.62</v>
       </c>
       <c r="J139" t="n">
+        <v>3</v>
+      </c>
+      <c r="K139" t="n">
         <v>12</v>
-      </c>
-      <c r="K139" t="n">
-        <v>3</v>
       </c>
       <c r="L139" t="n">
         <v>15</v>
       </c>
+      <c r="M139" t="n">
+        <v>4943.04</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6319,14 +6738,17 @@
         <v>24.74</v>
       </c>
       <c r="J140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L140" t="n">
         <v>6</v>
       </c>
+      <c r="M140" t="n">
+        <v>21194</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6361,14 +6783,17 @@
         <v>8.449999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L141" t="n">
         <v>6</v>
       </c>
+      <c r="M141" t="n">
+        <v>5282.75</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6403,14 +6828,17 @@
         <v>26.26</v>
       </c>
       <c r="J142" t="n">
+        <v>3</v>
+      </c>
+      <c r="K142" t="n">
         <v>6</v>
-      </c>
-      <c r="K142" t="n">
-        <v>3</v>
       </c>
       <c r="L142" t="n">
         <v>9</v>
       </c>
+      <c r="M142" t="n">
+        <v>8270.389999999999</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6453,6 +6881,9 @@
       <c r="L143" t="n">
         <v>6</v>
       </c>
+      <c r="M143" t="n">
+        <v>2589.8</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6487,14 +6918,17 @@
         <v>6.27</v>
       </c>
       <c r="J144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L144" t="n">
         <v>7</v>
       </c>
+      <c r="M144" t="n">
+        <v>2577.88</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6529,14 +6963,17 @@
         <v>15.99</v>
       </c>
       <c r="J145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L145" t="n">
         <v>9</v>
       </c>
+      <c r="M145" t="n">
+        <v>4106.88</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6571,14 +7008,17 @@
         <v>18.39</v>
       </c>
       <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="n">
         <v>6</v>
-      </c>
-      <c r="K146" t="n">
-        <v>2</v>
       </c>
       <c r="L146" t="n">
         <v>8</v>
       </c>
+      <c r="M146" t="n">
+        <v>5497.79</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6613,14 +7053,17 @@
         <v>8.33</v>
       </c>
       <c r="J147" t="n">
+        <v>4</v>
+      </c>
+      <c r="K147" t="n">
         <v>18</v>
-      </c>
-      <c r="K147" t="n">
-        <v>4</v>
       </c>
       <c r="L147" t="n">
         <v>22</v>
       </c>
+      <c r="M147" t="n">
+        <v>5649.03</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6655,14 +7098,17 @@
         <v>11.43</v>
       </c>
       <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="n">
         <v>7</v>
-      </c>
-      <c r="K148" t="n">
-        <v>2</v>
       </c>
       <c r="L148" t="n">
         <v>9</v>
       </c>
+      <c r="M148" t="n">
+        <v>7284.27</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6697,14 +7143,17 @@
         <v>21.91</v>
       </c>
       <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="n">
         <v>8</v>
-      </c>
-      <c r="K149" t="n">
-        <v>3</v>
       </c>
       <c r="L149" t="n">
         <v>11</v>
       </c>
+      <c r="M149" t="n">
+        <v>7816.5</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6739,14 +7188,17 @@
         <v>15.42</v>
       </c>
       <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="n">
         <v>12</v>
-      </c>
-      <c r="K150" t="n">
-        <v>3</v>
       </c>
       <c r="L150" t="n">
         <v>15</v>
       </c>
+      <c r="M150" t="n">
+        <v>5523.96</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6781,14 +7233,17 @@
         <v>24.53</v>
       </c>
       <c r="J151" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" t="n">
         <v>14</v>
-      </c>
-      <c r="K151" t="n">
-        <v>4</v>
       </c>
       <c r="L151" t="n">
         <v>18</v>
       </c>
+      <c r="M151" t="n">
+        <v>5270.73</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6823,14 +7278,17 @@
         <v>18.34</v>
       </c>
       <c r="J152" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" t="n">
         <v>10</v>
-      </c>
-      <c r="K152" t="n">
-        <v>5</v>
       </c>
       <c r="L152" t="n">
         <v>15</v>
       </c>
+      <c r="M152" t="n">
+        <v>5039.9</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6865,14 +7323,17 @@
         <v>8.640000000000001</v>
       </c>
       <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="n">
         <v>19</v>
-      </c>
-      <c r="K153" t="n">
-        <v>3</v>
       </c>
       <c r="L153" t="n">
         <v>22</v>
       </c>
+      <c r="M153" t="n">
+        <v>2910</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6907,14 +7368,17 @@
         <v>22.14</v>
       </c>
       <c r="J154" t="n">
+        <v>5</v>
+      </c>
+      <c r="K154" t="n">
         <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>5</v>
       </c>
       <c r="L154" t="n">
         <v>5</v>
       </c>
+      <c r="M154" t="n">
+        <v>6377.05</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6949,14 +7413,17 @@
         <v>25.88</v>
       </c>
       <c r="J155" t="n">
+        <v>4</v>
+      </c>
+      <c r="K155" t="n">
         <v>8</v>
-      </c>
-      <c r="K155" t="n">
-        <v>4</v>
       </c>
       <c r="L155" t="n">
         <v>12</v>
       </c>
+      <c r="M155" t="n">
+        <v>7988.62</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6991,14 +7458,17 @@
         <v>24.38</v>
       </c>
       <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="n">
         <v>6</v>
-      </c>
-      <c r="K156" t="n">
-        <v>3</v>
       </c>
       <c r="L156" t="n">
         <v>9</v>
       </c>
+      <c r="M156" t="n">
+        <v>8051.06</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7033,14 +7503,17 @@
         <v>23.75</v>
       </c>
       <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="n">
         <v>6</v>
-      </c>
-      <c r="K157" t="n">
-        <v>3</v>
       </c>
       <c r="L157" t="n">
         <v>9</v>
       </c>
+      <c r="M157" t="n">
+        <v>11389.39</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7075,14 +7548,17 @@
         <v>21.4</v>
       </c>
       <c r="J158" t="n">
+        <v>4</v>
+      </c>
+      <c r="K158" t="n">
         <v>6</v>
-      </c>
-      <c r="K158" t="n">
-        <v>4</v>
       </c>
       <c r="L158" t="n">
         <v>10</v>
       </c>
+      <c r="M158" t="n">
+        <v>3579.82</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7117,14 +7593,17 @@
         <v>16.81</v>
       </c>
       <c r="J159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L159" t="n">
         <v>6</v>
       </c>
+      <c r="M159" t="n">
+        <v>5644.42</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7159,14 +7638,17 @@
         <v>22.97</v>
       </c>
       <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="n">
         <v>10</v>
-      </c>
-      <c r="K160" t="n">
-        <v>3</v>
       </c>
       <c r="L160" t="n">
         <v>13</v>
       </c>
+      <c r="M160" t="n">
+        <v>9834.049999999999</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7201,14 +7683,17 @@
         <v>18.85</v>
       </c>
       <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="n">
         <v>11</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3</v>
       </c>
       <c r="L161" t="n">
         <v>14</v>
       </c>
+      <c r="M161" t="n">
+        <v>5680.17</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7243,14 +7728,17 @@
         <v>15.67</v>
       </c>
       <c r="J162" t="n">
+        <v>5</v>
+      </c>
+      <c r="K162" t="n">
         <v>6</v>
-      </c>
-      <c r="K162" t="n">
-        <v>5</v>
       </c>
       <c r="L162" t="n">
         <v>11</v>
       </c>
+      <c r="M162" t="n">
+        <v>6024.35</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7285,14 +7773,17 @@
         <v>29.21</v>
       </c>
       <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="n">
         <v>7</v>
-      </c>
-      <c r="K163" t="n">
-        <v>3</v>
       </c>
       <c r="L163" t="n">
         <v>10</v>
       </c>
+      <c r="M163" t="n">
+        <v>11308.58</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7327,14 +7818,17 @@
         <v>16.72</v>
       </c>
       <c r="J164" t="n">
+        <v>4</v>
+      </c>
+      <c r="K164" t="n">
         <v>12</v>
-      </c>
-      <c r="K164" t="n">
-        <v>4</v>
       </c>
       <c r="L164" t="n">
         <v>16</v>
       </c>
+      <c r="M164" t="n">
+        <v>4862.57</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7369,14 +7863,17 @@
         <v>22.84</v>
       </c>
       <c r="J165" t="n">
+        <v>4</v>
+      </c>
+      <c r="K165" t="n">
         <v>12</v>
-      </c>
-      <c r="K165" t="n">
-        <v>4</v>
       </c>
       <c r="L165" t="n">
         <v>16</v>
       </c>
+      <c r="M165" t="n">
+        <v>6915.86</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7419,6 +7916,9 @@
       <c r="L166" t="n">
         <v>8</v>
       </c>
+      <c r="M166" t="n">
+        <v>7667.7</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7453,14 +7953,17 @@
         <v>9.73</v>
       </c>
       <c r="J167" t="n">
+        <v>4</v>
+      </c>
+      <c r="K167" t="n">
         <v>6</v>
-      </c>
-      <c r="K167" t="n">
-        <v>4</v>
       </c>
       <c r="L167" t="n">
         <v>10</v>
       </c>
+      <c r="M167" t="n">
+        <v>4202.05</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7495,14 +7998,17 @@
         <v>15.83</v>
       </c>
       <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="n">
         <v>16</v>
-      </c>
-      <c r="K168" t="n">
-        <v>3</v>
       </c>
       <c r="L168" t="n">
         <v>19</v>
       </c>
+      <c r="M168" t="n">
+        <v>3087.04</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7537,14 +8043,17 @@
         <v>22.97</v>
       </c>
       <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="n">
         <v>8</v>
-      </c>
-      <c r="K169" t="n">
-        <v>3</v>
       </c>
       <c r="L169" t="n">
         <v>11</v>
       </c>
+      <c r="M169" t="n">
+        <v>3869.7</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7579,14 +8088,17 @@
         <v>17.59</v>
       </c>
       <c r="J170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L170" t="n">
         <v>7</v>
       </c>
+      <c r="M170" t="n">
+        <v>6754.44</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7621,14 +8133,17 @@
         <v>26.88</v>
       </c>
       <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="n">
         <v>14</v>
-      </c>
-      <c r="K171" t="n">
-        <v>3</v>
       </c>
       <c r="L171" t="n">
         <v>17</v>
       </c>
+      <c r="M171" t="n">
+        <v>5503.5</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7663,14 +8178,17 @@
         <v>21.84</v>
       </c>
       <c r="J172" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" t="n">
         <v>0</v>
-      </c>
-      <c r="K172" t="n">
-        <v>2</v>
       </c>
       <c r="L172" t="n">
         <v>2</v>
       </c>
+      <c r="M172" t="n">
+        <v>3142.75</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7705,14 +8223,17 @@
         <v>24.07</v>
       </c>
       <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="n">
         <v>10</v>
-      </c>
-      <c r="K173" t="n">
-        <v>3</v>
       </c>
       <c r="L173" t="n">
         <v>13</v>
       </c>
+      <c r="M173" t="n">
+        <v>8920.639999999999</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7747,14 +8268,17 @@
         <v>22.37</v>
       </c>
       <c r="J174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L174" t="n">
         <v>7</v>
       </c>
+      <c r="M174" t="n">
+        <v>8545.809999999999</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7789,14 +8313,17 @@
         <v>22.31</v>
       </c>
       <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="n">
         <v>6</v>
-      </c>
-      <c r="K175" t="n">
-        <v>3</v>
       </c>
       <c r="L175" t="n">
         <v>9</v>
       </c>
+      <c r="M175" t="n">
+        <v>7645.61</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7831,14 +8358,17 @@
         <v>19.58</v>
       </c>
       <c r="J176" t="n">
+        <v>4</v>
+      </c>
+      <c r="K176" t="n">
         <v>6</v>
-      </c>
-      <c r="K176" t="n">
-        <v>4</v>
       </c>
       <c r="L176" t="n">
         <v>10</v>
       </c>
+      <c r="M176" t="n">
+        <v>5753.73</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7873,14 +8403,17 @@
         <v>14.31</v>
       </c>
       <c r="J177" t="n">
+        <v>4</v>
+      </c>
+      <c r="K177" t="n">
         <v>16</v>
-      </c>
-      <c r="K177" t="n">
-        <v>4</v>
       </c>
       <c r="L177" t="n">
         <v>20</v>
       </c>
+      <c r="M177" t="n">
+        <v>4898.28</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7915,14 +8448,17 @@
         <v>22.84</v>
       </c>
       <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="n">
         <v>6</v>
-      </c>
-      <c r="K178" t="n">
-        <v>3</v>
       </c>
       <c r="L178" t="n">
         <v>9</v>
       </c>
+      <c r="M178" t="n">
+        <v>12950.78</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7957,14 +8493,17 @@
         <v>9.890000000000001</v>
       </c>
       <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="n">
         <v>10</v>
-      </c>
-      <c r="K179" t="n">
-        <v>3</v>
       </c>
       <c r="L179" t="n">
         <v>13</v>
       </c>
+      <c r="M179" t="n">
+        <v>5853.82</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7999,14 +8538,17 @@
         <v>23.32</v>
       </c>
       <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="n">
         <v>5</v>
-      </c>
-      <c r="K180" t="n">
-        <v>3</v>
       </c>
       <c r="L180" t="n">
         <v>8</v>
       </c>
+      <c r="M180" t="n">
+        <v>8364.940000000001</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8041,14 +8583,17 @@
         <v>17.41</v>
       </c>
       <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="n">
         <v>8</v>
-      </c>
-      <c r="K181" t="n">
-        <v>4</v>
       </c>
       <c r="L181" t="n">
         <v>12</v>
       </c>
+      <c r="M181" t="n">
+        <v>3028.12</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8083,14 +8628,17 @@
         <v>10.87</v>
       </c>
       <c r="J182" t="n">
+        <v>4</v>
+      </c>
+      <c r="K182" t="n">
         <v>8</v>
-      </c>
-      <c r="K182" t="n">
-        <v>4</v>
       </c>
       <c r="L182" t="n">
         <v>12</v>
       </c>
+      <c r="M182" t="n">
+        <v>5507.46</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8125,14 +8673,17 @@
         <v>22.02</v>
       </c>
       <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="n">
         <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>3</v>
       </c>
       <c r="L183" t="n">
         <v>3</v>
       </c>
+      <c r="M183" t="n">
+        <v>9707</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8175,6 +8726,9 @@
       <c r="L184" t="n">
         <v>8</v>
       </c>
+      <c r="M184" t="n">
+        <v>6904.5</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8209,14 +8763,17 @@
         <v>22.98</v>
       </c>
       <c r="J185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L185" t="n">
         <v>7</v>
       </c>
+      <c r="M185" t="n">
+        <v>13950.5</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8251,14 +8808,17 @@
         <v>19.98</v>
       </c>
       <c r="J186" t="n">
+        <v>4</v>
+      </c>
+      <c r="K186" t="n">
         <v>12</v>
-      </c>
-      <c r="K186" t="n">
-        <v>4</v>
       </c>
       <c r="L186" t="n">
         <v>16</v>
       </c>
+      <c r="M186" t="n">
+        <v>2416.14</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8293,14 +8853,17 @@
         <v>18.24</v>
       </c>
       <c r="J187" t="n">
+        <v>4</v>
+      </c>
+      <c r="K187" t="n">
         <v>8</v>
-      </c>
-      <c r="K187" t="n">
-        <v>4</v>
       </c>
       <c r="L187" t="n">
         <v>12</v>
       </c>
+      <c r="M187" t="n">
+        <v>7310.08</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8335,14 +8898,17 @@
         <v>22.51</v>
       </c>
       <c r="J188" t="n">
+        <v>4</v>
+      </c>
+      <c r="K188" t="n">
         <v>26</v>
-      </c>
-      <c r="K188" t="n">
-        <v>4</v>
       </c>
       <c r="L188" t="n">
         <v>30</v>
       </c>
+      <c r="M188" t="n">
+        <v>6780.79</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8377,14 +8943,17 @@
         <v>18.72</v>
       </c>
       <c r="J189" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K189" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L189" t="n">
         <v>6</v>
       </c>
+      <c r="M189" t="n">
+        <v>2044.25</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8419,14 +8988,17 @@
         <v>28.34</v>
       </c>
       <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="n">
         <v>18</v>
-      </c>
-      <c r="K190" t="n">
-        <v>3</v>
       </c>
       <c r="L190" t="n">
         <v>21</v>
       </c>
+      <c r="M190" t="n">
+        <v>1712.4</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8461,14 +9033,17 @@
         <v>24.74</v>
       </c>
       <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="n">
         <v>12</v>
-      </c>
-      <c r="K191" t="n">
-        <v>3</v>
       </c>
       <c r="L191" t="n">
         <v>15</v>
       </c>
+      <c r="M191" t="n">
+        <v>816.67</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8503,14 +9078,17 @@
         <v>12.76</v>
       </c>
       <c r="J192" t="n">
+        <v>4</v>
+      </c>
+      <c r="K192" t="n">
         <v>16</v>
-      </c>
-      <c r="K192" t="n">
-        <v>4</v>
       </c>
       <c r="L192" t="n">
         <v>20</v>
       </c>
+      <c r="M192" t="n">
+        <v>3822.59</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8545,14 +9123,17 @@
         <v>24.66</v>
       </c>
       <c r="J193" t="n">
+        <v>6</v>
+      </c>
+      <c r="K193" t="n">
         <v>16</v>
-      </c>
-      <c r="K193" t="n">
-        <v>6</v>
       </c>
       <c r="L193" t="n">
         <v>22</v>
       </c>
+      <c r="M193" t="n">
+        <v>1677.42</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8587,14 +9168,17 @@
         <v>11.85</v>
       </c>
       <c r="J194" t="n">
+        <v>8</v>
+      </c>
+      <c r="K194" t="n">
         <v>26</v>
-      </c>
-      <c r="K194" t="n">
-        <v>8</v>
       </c>
       <c r="L194" t="n">
         <v>34</v>
       </c>
+      <c r="M194" t="n">
+        <v>3140.95</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8629,14 +9213,17 @@
         <v>26.43</v>
       </c>
       <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="n">
         <v>32</v>
-      </c>
-      <c r="K195" t="n">
-        <v>3</v>
       </c>
       <c r="L195" t="n">
         <v>35</v>
       </c>
+      <c r="M195" t="n">
+        <v>4119.2</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8671,14 +9258,17 @@
         <v>9.98</v>
       </c>
       <c r="J196" t="n">
+        <v>4</v>
+      </c>
+      <c r="K196" t="n">
         <v>14</v>
-      </c>
-      <c r="K196" t="n">
-        <v>4</v>
       </c>
       <c r="L196" t="n">
         <v>18</v>
       </c>
+      <c r="M196" t="n">
+        <v>2633.4</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8713,14 +9303,17 @@
         <v>22.12</v>
       </c>
       <c r="J197" t="n">
+        <v>4</v>
+      </c>
+      <c r="K197" t="n">
         <v>18</v>
-      </c>
-      <c r="K197" t="n">
-        <v>4</v>
       </c>
       <c r="L197" t="n">
         <v>22</v>
       </c>
+      <c r="M197" t="n">
+        <v>1495.15</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8755,14 +9348,17 @@
         <v>16.69</v>
       </c>
       <c r="J198" t="n">
+        <v>5</v>
+      </c>
+      <c r="K198" t="n">
         <v>12</v>
-      </c>
-      <c r="K198" t="n">
-        <v>5</v>
       </c>
       <c r="L198" t="n">
         <v>17</v>
       </c>
+      <c r="M198" t="n">
+        <v>1907.59</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8797,14 +9393,17 @@
         <v>13.6</v>
       </c>
       <c r="J199" t="n">
+        <v>4</v>
+      </c>
+      <c r="K199" t="n">
         <v>13</v>
-      </c>
-      <c r="K199" t="n">
-        <v>4</v>
       </c>
       <c r="L199" t="n">
         <v>17</v>
       </c>
+      <c r="M199" t="n">
+        <v>2252.97</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8839,14 +9438,17 @@
         <v>6.09</v>
       </c>
       <c r="J200" t="n">
+        <v>4</v>
+      </c>
+      <c r="K200" t="n">
         <v>22</v>
-      </c>
-      <c r="K200" t="n">
-        <v>4</v>
       </c>
       <c r="L200" t="n">
         <v>26</v>
       </c>
+      <c r="M200" t="n">
+        <v>2936.97</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8881,14 +9483,17 @@
         <v>21.14</v>
       </c>
       <c r="J201" t="n">
+        <v>4</v>
+      </c>
+      <c r="K201" t="n">
         <v>10</v>
-      </c>
-      <c r="K201" t="n">
-        <v>4</v>
       </c>
       <c r="L201" t="n">
         <v>14</v>
       </c>
+      <c r="M201" t="n">
+        <v>1951.12</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8923,14 +9528,17 @@
         <v>23.42</v>
       </c>
       <c r="J202" t="n">
+        <v>4</v>
+      </c>
+      <c r="K202" t="n">
         <v>14</v>
-      </c>
-      <c r="K202" t="n">
-        <v>4</v>
       </c>
       <c r="L202" t="n">
         <v>18</v>
       </c>
+      <c r="M202" t="n">
+        <v>1951.57</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8965,14 +9573,17 @@
         <v>24.94</v>
       </c>
       <c r="J203" t="n">
+        <v>4</v>
+      </c>
+      <c r="K203" t="n">
         <v>22</v>
-      </c>
-      <c r="K203" t="n">
-        <v>4</v>
       </c>
       <c r="L203" t="n">
         <v>26</v>
       </c>
+      <c r="M203" t="n">
+        <v>2635.18</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9007,14 +9618,17 @@
         <v>16.97</v>
       </c>
       <c r="J204" t="n">
+        <v>4</v>
+      </c>
+      <c r="K204" t="n">
         <v>27</v>
-      </c>
-      <c r="K204" t="n">
-        <v>4</v>
       </c>
       <c r="L204" t="n">
         <v>31</v>
       </c>
+      <c r="M204" t="n">
+        <v>2303.72</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9049,14 +9663,17 @@
         <v>15.85</v>
       </c>
       <c r="J205" t="n">
+        <v>4</v>
+      </c>
+      <c r="K205" t="n">
         <v>12</v>
-      </c>
-      <c r="K205" t="n">
-        <v>4</v>
       </c>
       <c r="L205" t="n">
         <v>16</v>
       </c>
+      <c r="M205" t="n">
+        <v>5702.29</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9091,14 +9708,17 @@
         <v>18.05</v>
       </c>
       <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="n">
         <v>18</v>
-      </c>
-      <c r="K206" t="n">
-        <v>3</v>
       </c>
       <c r="L206" t="n">
         <v>21</v>
       </c>
+      <c r="M206" t="n">
+        <v>2585.53</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9133,14 +9753,17 @@
         <v>21.78</v>
       </c>
       <c r="J207" t="n">
+        <v>4</v>
+      </c>
+      <c r="K207" t="n">
         <v>16</v>
-      </c>
-      <c r="K207" t="n">
-        <v>4</v>
       </c>
       <c r="L207" t="n">
         <v>20</v>
       </c>
+      <c r="M207" t="n">
+        <v>3772.19</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9175,14 +9798,17 @@
         <v>29.33</v>
       </c>
       <c r="J208" t="n">
+        <v>9</v>
+      </c>
+      <c r="K208" t="n">
         <v>34</v>
-      </c>
-      <c r="K208" t="n">
-        <v>9</v>
       </c>
       <c r="L208" t="n">
         <v>43</v>
       </c>
+      <c r="M208" t="n">
+        <v>4260.59</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9217,14 +9843,17 @@
         <v>10.3</v>
       </c>
       <c r="J209" t="n">
+        <v>4</v>
+      </c>
+      <c r="K209" t="n">
         <v>13</v>
-      </c>
-      <c r="K209" t="n">
-        <v>4</v>
       </c>
       <c r="L209" t="n">
         <v>17</v>
       </c>
+      <c r="M209" t="n">
+        <v>11008.97</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9259,14 +9888,17 @@
         <v>14.82</v>
       </c>
       <c r="J210" t="n">
+        <v>10</v>
+      </c>
+      <c r="K210" t="n">
         <v>77</v>
-      </c>
-      <c r="K210" t="n">
-        <v>10</v>
       </c>
       <c r="L210" t="n">
         <v>87</v>
       </c>
+      <c r="M210" t="n">
+        <v>6396.42</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9301,14 +9933,17 @@
         <v>13.67</v>
       </c>
       <c r="J211" t="n">
+        <v>7</v>
+      </c>
+      <c r="K211" t="n">
         <v>17</v>
-      </c>
-      <c r="K211" t="n">
-        <v>7</v>
       </c>
       <c r="L211" t="n">
         <v>24</v>
       </c>
+      <c r="M211" t="n">
+        <v>5766.24</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9343,14 +9978,17 @@
         <v>17.63</v>
       </c>
       <c r="J212" t="n">
+        <v>5</v>
+      </c>
+      <c r="K212" t="n">
         <v>6</v>
-      </c>
-      <c r="K212" t="n">
-        <v>5</v>
       </c>
       <c r="L212" t="n">
         <v>11</v>
       </c>
+      <c r="M212" t="n">
+        <v>17877.08</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9385,14 +10023,17 @@
         <v>16.9</v>
       </c>
       <c r="J213" t="n">
+        <v>4</v>
+      </c>
+      <c r="K213" t="n">
         <v>14</v>
-      </c>
-      <c r="K213" t="n">
-        <v>4</v>
       </c>
       <c r="L213" t="n">
         <v>18</v>
       </c>
+      <c r="M213" t="n">
+        <v>8517.93</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9427,14 +10068,17 @@
         <v>13.03</v>
       </c>
       <c r="J214" t="n">
+        <v>5</v>
+      </c>
+      <c r="K214" t="n">
         <v>26</v>
-      </c>
-      <c r="K214" t="n">
-        <v>5</v>
       </c>
       <c r="L214" t="n">
         <v>31</v>
       </c>
+      <c r="M214" t="n">
+        <v>3081.5</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9469,14 +10113,17 @@
         <v>19.88</v>
       </c>
       <c r="J215" t="n">
+        <v>7</v>
+      </c>
+      <c r="K215" t="n">
         <v>25</v>
-      </c>
-      <c r="K215" t="n">
-        <v>7</v>
       </c>
       <c r="L215" t="n">
         <v>32</v>
       </c>
+      <c r="M215" t="n">
+        <v>10010.72</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9511,14 +10158,17 @@
         <v>11.99</v>
       </c>
       <c r="J216" t="n">
+        <v>9</v>
+      </c>
+      <c r="K216" t="n">
         <v>35</v>
-      </c>
-      <c r="K216" t="n">
-        <v>9</v>
       </c>
       <c r="L216" t="n">
         <v>44</v>
       </c>
+      <c r="M216" t="n">
+        <v>3782.23</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9553,14 +10203,17 @@
         <v>18.52</v>
       </c>
       <c r="J217" t="n">
+        <v>7</v>
+      </c>
+      <c r="K217" t="n">
         <v>19</v>
-      </c>
-      <c r="K217" t="n">
-        <v>7</v>
       </c>
       <c r="L217" t="n">
         <v>26</v>
       </c>
+      <c r="M217" t="n">
+        <v>7862.34</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9595,14 +10248,17 @@
         <v>29.55</v>
       </c>
       <c r="J218" t="n">
+        <v>5</v>
+      </c>
+      <c r="K218" t="n">
         <v>11</v>
-      </c>
-      <c r="K218" t="n">
-        <v>5</v>
       </c>
       <c r="L218" t="n">
         <v>16</v>
       </c>
+      <c r="M218" t="n">
+        <v>17851.03</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9637,14 +10293,17 @@
         <v>12.1</v>
       </c>
       <c r="J219" t="n">
+        <v>7</v>
+      </c>
+      <c r="K219" t="n">
         <v>13</v>
-      </c>
-      <c r="K219" t="n">
-        <v>7</v>
       </c>
       <c r="L219" t="n">
         <v>20</v>
       </c>
+      <c r="M219" t="n">
+        <v>6510.07</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9679,14 +10338,17 @@
         <v>39.6</v>
       </c>
       <c r="J220" t="n">
+        <v>9</v>
+      </c>
+      <c r="K220" t="n">
         <v>24</v>
-      </c>
-      <c r="K220" t="n">
-        <v>9</v>
       </c>
       <c r="L220" t="n">
         <v>33</v>
       </c>
+      <c r="M220" t="n">
+        <v>7591.62</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9721,14 +10383,17 @@
         <v>27.19</v>
       </c>
       <c r="J221" t="n">
+        <v>9</v>
+      </c>
+      <c r="K221" t="n">
         <v>21</v>
-      </c>
-      <c r="K221" t="n">
-        <v>9</v>
       </c>
       <c r="L221" t="n">
         <v>30</v>
       </c>
+      <c r="M221" t="n">
+        <v>1022.32</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9763,14 +10428,17 @@
         <v>30.27</v>
       </c>
       <c r="J222" t="n">
+        <v>7</v>
+      </c>
+      <c r="K222" t="n">
         <v>14</v>
-      </c>
-      <c r="K222" t="n">
-        <v>7</v>
       </c>
       <c r="L222" t="n">
         <v>21</v>
       </c>
+      <c r="M222" t="n">
+        <v>9269.690000000001</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9805,14 +10473,17 @@
         <v>16</v>
       </c>
       <c r="J223" t="n">
+        <v>5</v>
+      </c>
+      <c r="K223" t="n">
         <v>21</v>
-      </c>
-      <c r="K223" t="n">
-        <v>5</v>
       </c>
       <c r="L223" t="n">
         <v>26</v>
       </c>
+      <c r="M223" t="n">
+        <v>15634.61</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9847,14 +10518,17 @@
         <v>20.97</v>
       </c>
       <c r="J224" t="n">
+        <v>10</v>
+      </c>
+      <c r="K224" t="n">
         <v>8</v>
-      </c>
-      <c r="K224" t="n">
-        <v>10</v>
       </c>
       <c r="L224" t="n">
         <v>18</v>
       </c>
+      <c r="M224" t="n">
+        <v>3775.54</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9889,14 +10563,17 @@
         <v>12.12</v>
       </c>
       <c r="J225" t="n">
+        <v>6</v>
+      </c>
+      <c r="K225" t="n">
         <v>9</v>
-      </c>
-      <c r="K225" t="n">
-        <v>6</v>
       </c>
       <c r="L225" t="n">
         <v>15</v>
       </c>
+      <c r="M225" t="n">
+        <v>16579.21</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9931,14 +10608,17 @@
         <v>11.25</v>
       </c>
       <c r="J226" t="n">
+        <v>5</v>
+      </c>
+      <c r="K226" t="n">
         <v>7</v>
-      </c>
-      <c r="K226" t="n">
-        <v>5</v>
       </c>
       <c r="L226" t="n">
         <v>12</v>
       </c>
+      <c r="M226" t="n">
+        <v>12345.89</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9973,14 +10653,17 @@
         <v>19.02</v>
       </c>
       <c r="J227" t="n">
+        <v>4</v>
+      </c>
+      <c r="K227" t="n">
         <v>16</v>
-      </c>
-      <c r="K227" t="n">
-        <v>4</v>
       </c>
       <c r="L227" t="n">
         <v>20</v>
       </c>
+      <c r="M227" t="n">
+        <v>8322.030000000001</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10015,14 +10698,17 @@
         <v>29.63</v>
       </c>
       <c r="J228" t="n">
+        <v>8</v>
+      </c>
+      <c r="K228" t="n">
         <v>0</v>
-      </c>
-      <c r="K228" t="n">
-        <v>8</v>
       </c>
       <c r="L228" t="n">
         <v>8</v>
       </c>
+      <c r="M228" t="n">
+        <v>9569.09</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10057,14 +10743,17 @@
         <v>21.56</v>
       </c>
       <c r="J229" t="n">
+        <v>6</v>
+      </c>
+      <c r="K229" t="n">
         <v>13</v>
-      </c>
-      <c r="K229" t="n">
-        <v>6</v>
       </c>
       <c r="L229" t="n">
         <v>19</v>
       </c>
+      <c r="M229" t="n">
+        <v>5589.43</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10099,14 +10788,17 @@
         <v>6.71</v>
       </c>
       <c r="J230" t="n">
+        <v>4</v>
+      </c>
+      <c r="K230" t="n">
         <v>16</v>
-      </c>
-      <c r="K230" t="n">
-        <v>4</v>
       </c>
       <c r="L230" t="n">
         <v>20</v>
       </c>
+      <c r="M230" t="n">
+        <v>6915.78</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10141,14 +10833,17 @@
         <v>25.68</v>
       </c>
       <c r="J231" t="n">
+        <v>3</v>
+      </c>
+      <c r="K231" t="n">
         <v>10</v>
-      </c>
-      <c r="K231" t="n">
-        <v>3</v>
       </c>
       <c r="L231" t="n">
         <v>13</v>
       </c>
+      <c r="M231" t="n">
+        <v>23607.82</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10183,14 +10878,17 @@
         <v>16.37</v>
       </c>
       <c r="J232" t="n">
+        <v>8</v>
+      </c>
+      <c r="K232" t="n">
         <v>18</v>
-      </c>
-      <c r="K232" t="n">
-        <v>8</v>
       </c>
       <c r="L232" t="n">
         <v>26</v>
       </c>
+      <c r="M232" t="n">
+        <v>5019.36</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10225,14 +10923,17 @@
         <v>19.62</v>
       </c>
       <c r="J233" t="n">
+        <v>8</v>
+      </c>
+      <c r="K233" t="n">
         <v>22</v>
-      </c>
-      <c r="K233" t="n">
-        <v>8</v>
       </c>
       <c r="L233" t="n">
         <v>30</v>
       </c>
+      <c r="M233" t="n">
+        <v>2053.39</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10267,14 +10968,17 @@
         <v>13.13</v>
       </c>
       <c r="J234" t="n">
+        <v>5</v>
+      </c>
+      <c r="K234" t="n">
         <v>16</v>
-      </c>
-      <c r="K234" t="n">
-        <v>5</v>
       </c>
       <c r="L234" t="n">
         <v>21</v>
       </c>
+      <c r="M234" t="n">
+        <v>4303.28</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10309,14 +11013,17 @@
         <v>11.74</v>
       </c>
       <c r="J235" t="n">
+        <v>4</v>
+      </c>
+      <c r="K235" t="n">
         <v>2</v>
-      </c>
-      <c r="K235" t="n">
-        <v>4</v>
       </c>
       <c r="L235" t="n">
         <v>6</v>
       </c>
+      <c r="M235" t="n">
+        <v>13669.44</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10351,14 +11058,17 @@
         <v>20.12</v>
       </c>
       <c r="J236" t="n">
+        <v>4</v>
+      </c>
+      <c r="K236" t="n">
         <v>13</v>
-      </c>
-      <c r="K236" t="n">
-        <v>4</v>
       </c>
       <c r="L236" t="n">
         <v>17</v>
       </c>
+      <c r="M236" t="n">
+        <v>8205.280000000001</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10393,14 +11103,17 @@
         <v>10.41</v>
       </c>
       <c r="J237" t="n">
+        <v>7</v>
+      </c>
+      <c r="K237" t="n">
         <v>14</v>
-      </c>
-      <c r="K237" t="n">
-        <v>7</v>
       </c>
       <c r="L237" t="n">
         <v>21</v>
       </c>
+      <c r="M237" t="n">
+        <v>14476.36</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10435,14 +11148,17 @@
         <v>29.18</v>
       </c>
       <c r="J238" t="n">
+        <v>7</v>
+      </c>
+      <c r="K238" t="n">
         <v>20</v>
-      </c>
-      <c r="K238" t="n">
-        <v>7</v>
       </c>
       <c r="L238" t="n">
         <v>27</v>
       </c>
+      <c r="M238" t="n">
+        <v>18825.58</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10477,14 +11193,17 @@
         <v>23.36</v>
       </c>
       <c r="J239" t="n">
+        <v>6</v>
+      </c>
+      <c r="K239" t="n">
         <v>16</v>
-      </c>
-      <c r="K239" t="n">
-        <v>6</v>
       </c>
       <c r="L239" t="n">
         <v>22</v>
       </c>
+      <c r="M239" t="n">
+        <v>12638.85</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10519,14 +11238,17 @@
         <v>20.17</v>
       </c>
       <c r="J240" t="n">
+        <v>5</v>
+      </c>
+      <c r="K240" t="n">
         <v>10</v>
-      </c>
-      <c r="K240" t="n">
-        <v>5</v>
       </c>
       <c r="L240" t="n">
         <v>15</v>
       </c>
+      <c r="M240" t="n">
+        <v>2903.23</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10561,14 +11283,17 @@
         <v>13.73</v>
       </c>
       <c r="J241" t="n">
+        <v>4</v>
+      </c>
+      <c r="K241" t="n">
         <v>23</v>
-      </c>
-      <c r="K241" t="n">
-        <v>4</v>
       </c>
       <c r="L241" t="n">
         <v>27</v>
       </c>
+      <c r="M241" t="n">
+        <v>6199.28</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10603,14 +11328,17 @@
         <v>14.96</v>
       </c>
       <c r="J242" t="n">
+        <v>4</v>
+      </c>
+      <c r="K242" t="n">
         <v>8</v>
-      </c>
-      <c r="K242" t="n">
-        <v>4</v>
       </c>
       <c r="L242" t="n">
         <v>12</v>
       </c>
+      <c r="M242" t="n">
+        <v>5322.5</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10645,14 +11373,17 @@
         <v>19.57</v>
       </c>
       <c r="J243" t="n">
+        <v>6</v>
+      </c>
+      <c r="K243" t="n">
         <v>24</v>
-      </c>
-      <c r="K243" t="n">
-        <v>6</v>
       </c>
       <c r="L243" t="n">
         <v>30</v>
       </c>
+      <c r="M243" t="n">
+        <v>3598.69</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10687,14 +11418,17 @@
         <v>7.93</v>
       </c>
       <c r="J244" t="n">
+        <v>7</v>
+      </c>
+      <c r="K244" t="n">
         <v>16</v>
-      </c>
-      <c r="K244" t="n">
-        <v>7</v>
       </c>
       <c r="L244" t="n">
         <v>23</v>
       </c>
+      <c r="M244" t="n">
+        <v>5118.39</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10729,13 +11463,16 @@
         <v>23.28</v>
       </c>
       <c r="J245" t="n">
+        <v>7</v>
+      </c>
+      <c r="K245" t="n">
         <v>27</v>
-      </c>
-      <c r="K245" t="n">
-        <v>7</v>
       </c>
       <c r="L245" t="n">
         <v>34</v>
+      </c>
+      <c r="M245" t="n">
+        <v>8963.84</v>
       </c>
     </row>
   </sheetData>
